--- a/src/test/resources/POC_data_sheet_v1.1.xlsx
+++ b/src/test/resources/POC_data_sheet_v1.1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SPidugujothi\IdeaProjects\AutomationPOC\src\test\resources\"/>
     </mc:Choice>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="194">
   <si>
     <t>Application</t>
   </si>
@@ -591,12 +591,43 @@
   </si>
   <si>
     <t>13:46:42</t>
+  </si>
+  <si>
+    <t>R32</t>
+  </si>
+  <si>
+    <t>05/12/2025</t>
+  </si>
+  <si>
+    <t>23:42:03</t>
+  </si>
+  <si>
+    <t>R33</t>
+  </si>
+  <si>
+    <t>05/13/2025</t>
+  </si>
+  <si>
+    <t>00:24:19</t>
+  </si>
+  <si>
+    <t>element click intercepted: Element &lt;span class="cart-label"&gt;...&lt;/span&gt; is not clickable at point (10...</t>
+  </si>
+  <si>
+    <t>1987122</t>
+  </si>
+  <si>
+    <t>R34</t>
+  </si>
+  <si>
+    <t>00:26:49</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -672,7 +703,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -743,12 +774,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <top style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -835,6 +884,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="true">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1173,11 +1229,11 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" style="17" customWidth="1"/>
-    <col min="2" max="2" width="31.44140625" customWidth="1"/>
-    <col min="3" max="3" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.109375" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" style="17" width="8.44140625"/>
+    <col min="2" max="2" customWidth="true" width="31.44140625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="21.33203125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.5546875"/>
+    <col min="6" max="6" customWidth="true" width="20.109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
@@ -1254,32 +1310,32 @@
   <dimension ref="A1:R5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.44140625" style="9" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" style="9"/>
-    <col min="3" max="3" width="13.5546875" style="9" customWidth="1"/>
-    <col min="4" max="4" width="26.21875" style="9" customWidth="1"/>
-    <col min="5" max="5" width="40.21875" style="9" customWidth="1"/>
-    <col min="6" max="6" width="7.44140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" style="9" customWidth="1"/>
-    <col min="8" max="8" width="12" style="9" customWidth="1"/>
-    <col min="9" max="9" width="29.21875" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.109375" style="9" customWidth="1"/>
-    <col min="12" max="12" width="7.6640625" style="9" customWidth="1"/>
-    <col min="13" max="13" width="15.77734375" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20" style="9" customWidth="1"/>
-    <col min="16" max="16" width="7.6640625" style="9" customWidth="1"/>
-    <col min="17" max="17" width="12.77734375" style="9" customWidth="1"/>
-    <col min="18" max="18" width="11" style="9" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.77734375" style="9" customWidth="1"/>
-    <col min="20" max="20" width="8.88671875" style="9"/>
-    <col min="21" max="21" width="21.77734375" style="9" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.44140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.21875" style="9" customWidth="1"/>
-    <col min="25" max="25" width="12.5546875" style="9" customWidth="1"/>
-    <col min="26" max="16384" width="8.88671875" style="9"/>
+    <col min="1" max="1" customWidth="true" style="9" width="16.44140625"/>
+    <col min="2" max="2" style="9" width="8.88671875"/>
+    <col min="3" max="3" customWidth="true" style="9" width="13.5546875"/>
+    <col min="4" max="4" customWidth="true" style="9" width="26.21875"/>
+    <col min="5" max="5" customWidth="true" style="9" width="40.21875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="9" width="7.44140625"/>
+    <col min="7" max="7" customWidth="true" style="9" width="10.6640625"/>
+    <col min="8" max="8" customWidth="true" style="9" width="12.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="9" width="29.21875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="9" width="11.5546875"/>
+    <col min="11" max="11" customWidth="true" style="9" width="15.109375"/>
+    <col min="12" max="12" customWidth="true" style="9" width="7.6640625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="9" width="15.77734375"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="9" width="15.109375"/>
+    <col min="15" max="15" customWidth="true" style="9" width="20.0"/>
+    <col min="16" max="16" customWidth="true" style="9" width="7.6640625"/>
+    <col min="17" max="17" customWidth="true" style="9" width="12.77734375"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="9" width="11.0"/>
+    <col min="19" max="19" customWidth="true" style="9" width="12.77734375"/>
+    <col min="20" max="20" style="9" width="8.88671875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="9" width="21.77734375"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="9" width="13.6640625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="9" width="13.44140625"/>
+    <col min="24" max="24" customWidth="true" style="9" width="15.21875"/>
+    <col min="25" max="25" customWidth="true" style="9" width="12.5546875"/>
+    <col min="26" max="16384" style="9" width="8.88671875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="13" customFormat="1" x14ac:dyDescent="0.3">
@@ -1551,16 +1607,16 @@
   <dimension ref="A1:L54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.5546875" customWidth="1"/>
-    <col min="6" max="6" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" customWidth="1"/>
-    <col min="8" max="9" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.44140625" customWidth="1"/>
-    <col min="11" max="11" width="11.88671875" customWidth="1"/>
-    <col min="12" max="12" width="50" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="12.5546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.88671875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="25.77734375"/>
+    <col min="5" max="5" customWidth="true" width="36.5546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="6.77734375"/>
+    <col min="7" max="7" customWidth="true" width="14.5546875"/>
+    <col min="8" max="9" bestFit="true" customWidth="true" width="14.88671875"/>
+    <col min="10" max="10" customWidth="true" width="10.44140625"/>
+    <col min="11" max="11" customWidth="true" width="11.88671875"/>
+    <col min="12" max="12" customWidth="true" width="50.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -2449,10 +2505,18 @@
       <c r="C34" s="20"/>
       <c r="D34" s="20"/>
       <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
+      <c r="F34" t="s" s="32">
+        <v>184</v>
+      </c>
+      <c r="G34" t="s" s="32">
+        <v>185</v>
+      </c>
+      <c r="H34" t="s" s="32">
+        <v>186</v>
+      </c>
+      <c r="I34" t="s" s="32">
+        <v>78</v>
+      </c>
       <c r="J34" s="20"/>
       <c r="K34" s="20"/>
       <c r="L34" s="20"/>
@@ -2465,13 +2529,23 @@
       <c r="E35" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
+      <c r="F35" t="s" s="33">
+        <v>187</v>
+      </c>
+      <c r="G35" t="s" s="33">
+        <v>188</v>
+      </c>
+      <c r="H35" t="s" s="33">
+        <v>189</v>
+      </c>
+      <c r="I35" t="s" s="33">
+        <v>72</v>
+      </c>
       <c r="J35" s="20"/>
       <c r="K35" s="20"/>
-      <c r="L35" s="20"/>
+      <c r="L35" t="s" s="34">
+        <v>190</v>
+      </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="20"/>
@@ -2481,12 +2555,24 @@
       <c r="E36" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="20"/>
-      <c r="K36" s="20"/>
+      <c r="F36" t="s" s="36">
+        <v>192</v>
+      </c>
+      <c r="G36" t="s" s="36">
+        <v>188</v>
+      </c>
+      <c r="H36" t="s" s="36">
+        <v>193</v>
+      </c>
+      <c r="I36" t="s" s="36">
+        <v>78</v>
+      </c>
+      <c r="J36" t="s" s="35">
+        <v>191</v>
+      </c>
+      <c r="K36" t="s" s="35">
+        <v>185</v>
+      </c>
       <c r="L36" s="20"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
@@ -2778,17 +2864,17 @@
   <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" customWidth="1"/>
-    <col min="3" max="3" width="15.77734375" customWidth="1"/>
-    <col min="4" max="4" width="27.109375" customWidth="1"/>
-    <col min="5" max="5" width="34.77734375" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="10.44140625"/>
+    <col min="2" max="2" customWidth="true" width="16.77734375"/>
+    <col min="3" max="3" customWidth="true" width="15.77734375"/>
+    <col min="4" max="4" customWidth="true" width="27.109375"/>
+    <col min="5" max="5" customWidth="true" width="34.77734375"/>
+    <col min="6" max="6" customWidth="true" width="13.5546875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="13.44140625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="13.6640625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="14.88671875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="7.6640625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="9.77734375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">

--- a/src/test/resources/POC_data_sheet_v1.1.xlsx
+++ b/src/test/resources/POC_data_sheet_v1.1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SPidugujothi\IdeaProjects\AutomationPOC\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SPidugujothi\IdeaProjects\MyridiusUAF\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7BBEEF-151C-413D-9409-3D5E1346EBF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33481A8C-BEDC-47BF-A1C4-E6BA37202D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{08B05D20-EDEF-43CA-A5DF-998FB408C439}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="453">
   <si>
     <t>Application</t>
   </si>
@@ -137,9 +137,6 @@
     <t>https://demowebshop.tricentis.com</t>
   </si>
   <si>
-    <t>testUser123</t>
-  </si>
-  <si>
     <t>chrome</t>
   </si>
   <si>
@@ -308,9 +305,6 @@
     <t>Address 12</t>
   </si>
   <si>
-    <t xml:space="preserve">Latest Run ID </t>
-  </si>
-  <si>
     <t>1969024</t>
   </si>
   <si>
@@ -1113,6 +1107,300 @@
   </si>
   <si>
     <t>19:39:25</t>
+  </si>
+  <si>
+    <t>R99</t>
+  </si>
+  <si>
+    <t>07/26/2025</t>
+  </si>
+  <si>
+    <t>23:39:37</t>
+  </si>
+  <si>
+    <t>Cannot invoke "com.MyridiusUAF.pages.RegisterPage.clickRegisterLink()" because "this.registerPage" i...</t>
+  </si>
+  <si>
+    <t>R101</t>
+  </si>
+  <si>
+    <t>23:42:06</t>
+  </si>
+  <si>
+    <t>23:49:19</t>
+  </si>
+  <si>
+    <t>Register Date</t>
+  </si>
+  <si>
+    <t>Register Time</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>R102</t>
+  </si>
+  <si>
+    <t>07/27/2025</t>
+  </si>
+  <si>
+    <t>00:06:32</t>
+  </si>
+  <si>
+    <t>R103</t>
+  </si>
+  <si>
+    <t>00:12:30</t>
+  </si>
+  <si>
+    <t>R104</t>
+  </si>
+  <si>
+    <t>00:20:34</t>
+  </si>
+  <si>
+    <t>Locator must be set</t>
+  </si>
+  <si>
+    <t>R105</t>
+  </si>
+  <si>
+    <t>00:29:03</t>
+  </si>
+  <si>
+    <t>R106</t>
+  </si>
+  <si>
+    <t>00:55:11</t>
+  </si>
+  <si>
+    <t>R108</t>
+  </si>
+  <si>
+    <t>00:59:30</t>
+  </si>
+  <si>
+    <t>01:08:35</t>
+  </si>
+  <si>
+    <t>no such window: target window already closed</t>
+  </si>
+  <si>
+    <t>R109</t>
+  </si>
+  <si>
+    <t>01:10:30</t>
+  </si>
+  <si>
+    <t>Expected condition failed: waiting for visibility of Proxy element for: DefaultElementLocator 'By.cs...</t>
+  </si>
+  <si>
+    <t>R110</t>
+  </si>
+  <si>
+    <t>01:30:59</t>
+  </si>
+  <si>
+    <t>R111</t>
+  </si>
+  <si>
+    <t>01:32:27</t>
+  </si>
+  <si>
+    <t>2057015</t>
+  </si>
+  <si>
+    <t>R112</t>
+  </si>
+  <si>
+    <t>01:37:34</t>
+  </si>
+  <si>
+    <t>R114</t>
+  </si>
+  <si>
+    <t>16:36:32</t>
+  </si>
+  <si>
+    <t>Login was not successful for user: meera.verma452@example.com</t>
+  </si>
+  <si>
+    <t>2057341</t>
+  </si>
+  <si>
+    <t>18:28:06</t>
+  </si>
+  <si>
+    <t>Expected condition failed: waiting for element to be clickable: Proxy element for: DefaultElementLoc…</t>
+  </si>
+  <si>
+    <t>21:26:32</t>
+  </si>
+  <si>
+    <t>21:28:24</t>
+  </si>
+  <si>
+    <t>21:31:25</t>
+  </si>
+  <si>
+    <t>2057437</t>
+  </si>
+  <si>
+    <t>21:45:26</t>
+  </si>
+  <si>
+    <t>2057446</t>
+  </si>
+  <si>
+    <t>22:08:39</t>
+  </si>
+  <si>
+    <t>amit.patel548@gmail.com</t>
+  </si>
+  <si>
+    <t>U7zBhiD7R0</t>
+  </si>
+  <si>
+    <t>22:18:39</t>
+  </si>
+  <si>
+    <t>2057456</t>
+  </si>
+  <si>
+    <t>22:20:24</t>
+  </si>
+  <si>
+    <t>R115</t>
+  </si>
+  <si>
+    <t>07/28/2025</t>
+  </si>
+  <si>
+    <t>12:08:15</t>
+  </si>
+  <si>
+    <t>R116</t>
+  </si>
+  <si>
+    <t>12:24:48</t>
+  </si>
+  <si>
+    <t>R117</t>
+  </si>
+  <si>
+    <t>14:38:57</t>
+  </si>
+  <si>
+    <t>R118</t>
+  </si>
+  <si>
+    <t>14:51:16</t>
+  </si>
+  <si>
+    <t>R119</t>
+  </si>
+  <si>
+    <t>15:09:55</t>
+  </si>
+  <si>
+    <t>R120</t>
+  </si>
+  <si>
+    <t>15:15:38</t>
+  </si>
+  <si>
+    <t>R121</t>
+  </si>
+  <si>
+    <t>15:33:24</t>
+  </si>
+  <si>
+    <t>R122</t>
+  </si>
+  <si>
+    <t>16:02:43</t>
+  </si>
+  <si>
+    <t>R123</t>
+  </si>
+  <si>
+    <t>16:09:59</t>
+  </si>
+  <si>
+    <t>No row found for key: 0 in sheet: Common_TestData (col 0)</t>
+  </si>
+  <si>
+    <t>R124</t>
+  </si>
+  <si>
+    <t>16:17:30</t>
+  </si>
+  <si>
+    <t>R125</t>
+  </si>
+  <si>
+    <t>16:28:47</t>
+  </si>
+  <si>
+    <t>SC1-TC1-E2E-Register</t>
+  </si>
+  <si>
+    <t>SC1-TC1-E2E-Reorder</t>
+  </si>
+  <si>
+    <t>divya.yadav453@yahoo.com</t>
+  </si>
+  <si>
+    <t>dLJv5nFgww</t>
+  </si>
+  <si>
+    <t>2025-07-30</t>
+  </si>
+  <si>
+    <t>16:28:36</t>
+  </si>
+  <si>
+    <t>2061022</t>
+  </si>
+  <si>
+    <t>07/30/2025</t>
+  </si>
+  <si>
+    <t>16:30:53</t>
+  </si>
+  <si>
+    <t>R126</t>
+  </si>
+  <si>
+    <t>18:43:34</t>
+  </si>
+  <si>
+    <t>R127</t>
+  </si>
+  <si>
+    <t>18:44:05</t>
+  </si>
+  <si>
+    <t>rohan.singh229@yahoo.com</t>
+  </si>
+  <si>
+    <t>*MAagSfDyI</t>
+  </si>
+  <si>
+    <t>18:56:09</t>
+  </si>
+  <si>
+    <t>2061138</t>
+  </si>
+  <si>
+    <t>18:58:31</t>
+  </si>
+  <si>
+    <t>R128</t>
+  </si>
+  <si>
+    <t>21:25:14</t>
   </si>
 </sst>
 </file>
@@ -1195,7 +1483,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1340,6 +1628,94 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <top style="thin"/>
     </border>
     <border>
@@ -1362,7 +1738,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1448,6 +1824,33 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1466,87 +1869,18 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="true">
       <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true">
-      <alignment wrapText="true"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1882,7 +2216,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A14D7DB-FAF1-41CF-9284-F20D84BE4920}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="15" width="8.44140625"/>
@@ -1890,9 +2224,11 @@
     <col min="3" max="3" bestFit="true" customWidth="true" width="21.33203125"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="12.5546875"/>
     <col min="6" max="6" customWidth="true" width="20.109375"/>
+    <col min="7" max="7" customWidth="true" width="11.77734375"/>
+    <col min="8" max="8" customWidth="true" width="13.33203125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>28</v>
       </c>
@@ -1900,55 +2236,69 @@
         <v>29</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D1" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="12" t="s">
         <v>38</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>39</v>
       </c>
       <c r="F1" s="12" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" s="37" t="s">
+        <v>362</v>
+      </c>
+      <c r="H1" s="38" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" t="s" s="60">
+        <v>446</v>
+      </c>
+      <c r="D2" t="s" s="60">
+        <v>447</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2" t="s" s="60">
+        <v>437</v>
+      </c>
+      <c r="H2" t="s" s="60">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="F3" s="3"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1995,28 +2345,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="36"/>
-      <c r="R1" s="37"/>
+      <c r="A1" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="49" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="50"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
@@ -2026,7 +2376,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>
@@ -2035,13 +2385,13 @@
         <v>2</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>3</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>4</v>
@@ -2056,7 +2406,7 @@
         <v>7</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N2" s="9" t="s">
         <v>12</v>
@@ -2076,31 +2426,31 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>15</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>18</v>
@@ -2118,7 +2468,7 @@
         <v>27</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P3" s="3" t="s">
         <v>22</v>
@@ -2132,55 +2482,55 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="L4" s="3">
         <v>589556</v>
       </c>
       <c r="M4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="N4" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="O4" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P4" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="Q4" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="R4" s="3">
         <v>8956545222</v>
@@ -2188,22 +2538,22 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G5" s="10" t="s">
         <v>16</v>
@@ -2260,7 +2610,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{087D34EC-64B6-464A-B1FA-1B3B12C5A42D}">
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:L130"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="15.44140625"/>
@@ -2278,23 +2628,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="39" t="s">
-        <v>118</v>
-      </c>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="K1" s="40"/>
+      <c r="A1" s="51" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="52" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="K1" s="53"/>
       <c r="L1" s="17"/>
     </row>
     <row r="2" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2305,13 +2655,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D2" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F2" s="19" t="s">
         <v>13</v>
@@ -2329,45 +2679,45 @@
         <v>23</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L2" s="19" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F3" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="G3" s="17" t="s">
-        <v>66</v>
-      </c>
       <c r="H3" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I3" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="J3" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="J3" s="17" t="s">
-        <v>68</v>
-      </c>
       <c r="K3" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L3" s="17"/>
     </row>
@@ -2377,25 +2727,25 @@
       <c r="C4" s="22"/>
       <c r="D4" s="22"/>
       <c r="E4" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F4" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="G4" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>72</v>
-      </c>
       <c r="I4" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L4" s="17"/>
     </row>
@@ -2405,25 +2755,25 @@
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
       <c r="E5" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F5" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="G5" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>76</v>
-      </c>
       <c r="I5" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="J5" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="J5" s="17" t="s">
-        <v>74</v>
-      </c>
       <c r="K5" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L5" s="17"/>
     </row>
@@ -2433,25 +2783,25 @@
       <c r="C6" s="21"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G6" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="H6" s="17" t="s">
-        <v>92</v>
-      </c>
       <c r="I6" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L6" s="17"/>
     </row>
@@ -2461,25 +2811,25 @@
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K7" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L7" s="17"/>
     </row>
@@ -2489,25 +2839,25 @@
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
       <c r="E8" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J8" s="17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K8" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L8" s="17"/>
     </row>
@@ -2517,25 +2867,25 @@
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
       <c r="E9" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I9" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L9" s="17"/>
     </row>
@@ -2545,25 +2895,25 @@
       <c r="C10" s="17"/>
       <c r="D10" s="17"/>
       <c r="E10" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I10" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J10" s="17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K10" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L10" s="17"/>
     </row>
@@ -2573,25 +2923,25 @@
       <c r="C11" s="17"/>
       <c r="D11" s="17"/>
       <c r="E11" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I11" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J11" s="17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K11" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L11" s="17"/>
     </row>
@@ -2601,25 +2951,25 @@
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
       <c r="E12" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K12" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L12" s="17"/>
     </row>
@@ -2629,25 +2979,25 @@
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
       <c r="E13" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L13" s="17"/>
     </row>
@@ -2657,25 +3007,25 @@
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
       <c r="E14" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I14" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J14" s="17" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L14" s="17"/>
     </row>
@@ -2685,24 +3035,24 @@
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
       <c r="E15" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I15" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J15" s="17"/>
       <c r="K15" s="17"/>
       <c r="L15" s="18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -2711,25 +3061,25 @@
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
       <c r="E16" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I16" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J16" s="17" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K16" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L16" s="17"/>
     </row>
@@ -2739,24 +3089,24 @@
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
       <c r="E17" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F17" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="H17" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="G17" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="H17" s="17" t="s">
-        <v>128</v>
-      </c>
       <c r="I17" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J17" s="17"/>
       <c r="K17" s="17"/>
       <c r="L17" s="18" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
@@ -2765,24 +3115,24 @@
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J18" s="17"/>
       <c r="K18" s="17"/>
       <c r="L18" s="18" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -2791,24 +3141,24 @@
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I19" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J19" s="17"/>
       <c r="K19" s="17"/>
       <c r="L19" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -2817,24 +3167,24 @@
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J20" s="17"/>
       <c r="K20" s="17"/>
       <c r="L20" s="18" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
@@ -2843,25 +3193,25 @@
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J21" s="17" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K21" s="17" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="L21" s="17"/>
     </row>
@@ -2871,25 +3221,25 @@
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J22" s="17" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K22" s="17" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="L22" s="17"/>
     </row>
@@ -2899,24 +3249,24 @@
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
       <c r="E23" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H23" s="17" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I23" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J23" s="17"/>
       <c r="K23" s="17"/>
       <c r="L23" s="18" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
@@ -2925,25 +3275,25 @@
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
       <c r="E24" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G24" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="H24" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="H24" s="17" t="s">
-        <v>151</v>
-      </c>
       <c r="I24" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J24" s="17" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K24" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L24" s="17"/>
     </row>
@@ -2953,25 +3303,25 @@
       <c r="C25" s="17"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I25" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K25" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L25" s="17"/>
     </row>
@@ -2981,24 +3331,24 @@
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J26" s="17"/>
       <c r="K26" s="17"/>
       <c r="L26" s="18" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
@@ -3007,25 +3357,25 @@
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K27" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L27" s="17"/>
     </row>
@@ -3035,25 +3385,25 @@
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I28" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J28" s="17" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K28" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L28" s="17"/>
     </row>
@@ -3063,25 +3413,25 @@
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I29" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K29" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L29" s="17"/>
     </row>
@@ -3091,25 +3441,25 @@
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I30" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J30" s="17" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K30" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L30" s="17"/>
     </row>
@@ -3119,25 +3469,25 @@
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J31" s="17" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K31" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L31" s="17"/>
     </row>
@@ -3147,25 +3497,25 @@
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
       <c r="E32" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I32" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J32" s="17" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K32" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L32" s="17"/>
     </row>
@@ -3175,25 +3525,25 @@
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
       <c r="E33" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I33" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="K33" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L33" s="17"/>
     </row>
@@ -3203,19 +3553,19 @@
       <c r="C34" s="17"/>
       <c r="D34" s="17"/>
       <c r="E34" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F34" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="G34" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="H34" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="G34" s="22" t="s">
-        <v>180</v>
-      </c>
-      <c r="H34" s="22" t="s">
-        <v>181</v>
-      </c>
       <c r="I34" s="22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J34" s="17"/>
       <c r="K34" s="17"/>
@@ -3227,24 +3577,24 @@
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
       <c r="E35" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F35" s="22" t="s">
+        <v>180</v>
+      </c>
+      <c r="G35" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="H35" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="G35" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="H35" s="22" t="s">
-        <v>184</v>
-      </c>
       <c r="I35" s="22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J35" s="17"/>
       <c r="K35" s="17"/>
       <c r="L35" s="23" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
@@ -3253,25 +3603,25 @@
       <c r="C36" s="28"/>
       <c r="D36" s="28"/>
       <c r="E36" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F36" s="22" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G36" s="22" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I36" s="22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J36" s="22" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K36" s="22" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="L36" s="17"/>
     </row>
@@ -3281,24 +3631,24 @@
       <c r="C37" s="28"/>
       <c r="D37" s="28"/>
       <c r="E37" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F37" s="28" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G37" s="28" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H37" s="28" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I37" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J37" s="22"/>
       <c r="K37" s="22"/>
       <c r="L37" s="29" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -3307,24 +3657,24 @@
       <c r="C38" s="28"/>
       <c r="D38" s="28"/>
       <c r="E38" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F38" s="28" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G38" s="28" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H38" s="28" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I38" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J38" s="22"/>
       <c r="K38" s="22"/>
       <c r="L38" s="29" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -3333,24 +3683,24 @@
       <c r="C39" s="22"/>
       <c r="D39" s="22"/>
       <c r="E39" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F39" s="28" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G39" s="28" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H39" s="28" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I39" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J39" s="22"/>
       <c r="K39" s="22"/>
       <c r="L39" s="29" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
@@ -3359,24 +3709,24 @@
       <c r="C40" s="22"/>
       <c r="D40" s="22"/>
       <c r="E40" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F40" s="28" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G40" s="28" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H40" s="28" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I40" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J40" s="22"/>
       <c r="K40" s="22"/>
       <c r="L40" s="29" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
@@ -3385,24 +3735,24 @@
       <c r="C41" s="22"/>
       <c r="D41" s="22"/>
       <c r="E41" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F41" s="28" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G41" s="28" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H41" s="28" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I41" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J41" s="22"/>
       <c r="K41" s="22"/>
       <c r="L41" s="29" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
@@ -3411,19 +3761,19 @@
       <c r="C42" s="22"/>
       <c r="D42" s="22"/>
       <c r="E42" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F42" s="28" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G42" s="28" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H42" s="28" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I42" s="28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J42" s="22"/>
       <c r="K42" s="22"/>
@@ -3435,24 +3785,24 @@
       <c r="C43" s="17"/>
       <c r="D43" s="17"/>
       <c r="E43" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F43" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="G43" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="H43" s="28" t="s">
         <v>199</v>
       </c>
-      <c r="G43" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H43" s="28" t="s">
-        <v>201</v>
-      </c>
       <c r="I43" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J43" s="17"/>
       <c r="K43" s="17"/>
       <c r="L43" s="29" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -3461,24 +3811,24 @@
       <c r="C44" s="17"/>
       <c r="D44" s="17"/>
       <c r="E44" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F44" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="G44" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="H44" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="G44" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="H44" s="28" t="s">
-        <v>204</v>
-      </c>
       <c r="I44" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J44" s="17"/>
       <c r="K44" s="17"/>
       <c r="L44" s="29" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
@@ -3487,25 +3837,25 @@
       <c r="C45" s="17"/>
       <c r="D45" s="17"/>
       <c r="E45" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F45" s="28" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G45" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="H45" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="I45" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="J45" s="28" t="s">
         <v>203</v>
       </c>
-      <c r="H45" s="28" t="s">
-        <v>207</v>
-      </c>
-      <c r="I45" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="J45" s="28" t="s">
-        <v>205</v>
-      </c>
       <c r="K45" s="28" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="L45" s="17"/>
     </row>
@@ -3515,24 +3865,24 @@
       <c r="C46" s="17"/>
       <c r="D46" s="17"/>
       <c r="E46" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F46" s="28" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G46" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H46" s="28" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I46" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J46" s="17"/>
       <c r="K46" s="17"/>
       <c r="L46" s="29" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
@@ -3541,25 +3891,25 @@
       <c r="C47" s="17"/>
       <c r="D47" s="17"/>
       <c r="E47" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F47" s="28" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G47" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H47" s="28" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I47" s="28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J47" s="28" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K47" s="28" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="L47" s="17"/>
     </row>
@@ -3569,24 +3919,24 @@
       <c r="C48" s="17"/>
       <c r="D48" s="17"/>
       <c r="E48" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F48" s="28" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G48" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H48" s="28" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I48" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J48" s="17"/>
       <c r="K48" s="17"/>
       <c r="L48" s="29" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -3595,24 +3945,24 @@
       <c r="C49" s="17"/>
       <c r="D49" s="17"/>
       <c r="E49" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F49" s="28" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G49" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H49" s="28" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I49" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J49" s="17"/>
       <c r="K49" s="17"/>
       <c r="L49" s="29" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
@@ -3621,24 +3971,24 @@
       <c r="C50" s="17"/>
       <c r="D50" s="17"/>
       <c r="E50" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F50" s="28" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G50" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H50" s="28" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I50" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J50" s="17"/>
       <c r="K50" s="17"/>
       <c r="L50" s="29" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
@@ -3647,25 +3997,25 @@
       <c r="C51" s="17"/>
       <c r="D51" s="17"/>
       <c r="E51" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F51" s="28" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G51" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H51" s="28" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I51" s="28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J51" s="28" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K51" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L51" s="17"/>
     </row>
@@ -3675,24 +4025,24 @@
       <c r="C52" s="17"/>
       <c r="D52" s="17"/>
       <c r="E52" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F52" s="28" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G52" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H52" s="28" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I52" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J52" s="17"/>
       <c r="K52" s="17"/>
       <c r="L52" s="29" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
@@ -3701,25 +4051,25 @@
       <c r="C53" s="17"/>
       <c r="D53" s="17"/>
       <c r="E53" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F53" s="28" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G53" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H53" s="28" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I53" s="28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J53" s="28" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K53" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L53" s="17"/>
     </row>
@@ -3729,24 +4079,24 @@
       <c r="C54" s="17"/>
       <c r="D54" s="17"/>
       <c r="E54" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F54" s="28" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G54" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H54" s="28" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I54" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J54" s="17"/>
       <c r="K54" s="17"/>
       <c r="L54" s="29" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
@@ -3755,24 +4105,24 @@
       <c r="C55" s="17"/>
       <c r="D55" s="17"/>
       <c r="E55" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F55" s="28" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G55" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H55" s="28" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="I55" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J55" s="17"/>
       <c r="K55" s="17"/>
       <c r="L55" s="29" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -3781,24 +4131,24 @@
       <c r="C56" s="17"/>
       <c r="D56" s="17"/>
       <c r="E56" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F56" s="28" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G56" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H56" s="28" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I56" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J56" s="17"/>
       <c r="K56" s="17"/>
       <c r="L56" s="29" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -3807,24 +4157,24 @@
       <c r="C57" s="17"/>
       <c r="D57" s="17"/>
       <c r="E57" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F57" s="28" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G57" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H57" s="28" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I57" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J57" s="17"/>
       <c r="K57" s="17"/>
       <c r="L57" s="29" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -3833,24 +4183,24 @@
       <c r="C58" s="17"/>
       <c r="D58" s="17"/>
       <c r="E58" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F58" s="28" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G58" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H58" s="28" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="I58" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J58" s="17"/>
       <c r="K58" s="17"/>
       <c r="L58" s="29" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
@@ -3859,24 +4209,24 @@
       <c r="C59" s="17"/>
       <c r="D59" s="17"/>
       <c r="E59" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F59" s="28" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G59" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H59" s="28" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I59" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J59" s="17"/>
       <c r="K59" s="17"/>
       <c r="L59" s="29" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -3885,24 +4235,24 @@
       <c r="C60" s="17"/>
       <c r="D60" s="17"/>
       <c r="E60" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F60" s="28" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G60" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H60" s="28" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I60" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J60" s="17"/>
       <c r="K60" s="17"/>
       <c r="L60" s="29" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -3911,24 +4261,24 @@
       <c r="C61" s="28"/>
       <c r="D61" s="28"/>
       <c r="E61" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F61" s="28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G61" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H61" s="28" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="I61" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J61" s="28"/>
       <c r="K61" s="28"/>
       <c r="L61" s="29" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -3937,24 +4287,24 @@
       <c r="C62" s="28"/>
       <c r="D62" s="28"/>
       <c r="E62" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F62" s="28" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G62" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H62" s="28" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I62" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J62" s="28"/>
       <c r="K62" s="28"/>
       <c r="L62" s="29" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
@@ -3963,25 +4313,25 @@
       <c r="C63" s="28"/>
       <c r="D63" s="28"/>
       <c r="E63" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F63" s="28" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G63" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H63" s="28" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="I63" s="28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J63" s="28" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K63" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -3990,24 +4340,24 @@
       <c r="C64" s="28"/>
       <c r="D64" s="28"/>
       <c r="E64" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F64" s="28" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G64" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H64" s="28" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I64" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J64" s="28"/>
       <c r="K64" s="28"/>
       <c r="L64" s="29" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -4016,24 +4366,24 @@
       <c r="C65" s="28"/>
       <c r="D65" s="28"/>
       <c r="E65" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F65" s="28" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G65" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H65" s="28" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I65" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J65" s="28"/>
       <c r="K65" s="28"/>
       <c r="L65" s="29" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -4042,24 +4392,24 @@
       <c r="C66" s="28"/>
       <c r="D66" s="28"/>
       <c r="E66" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F66" s="28" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G66" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H66" s="28" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="I66" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J66" s="28"/>
       <c r="K66" s="28"/>
       <c r="L66" s="29" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -4068,24 +4418,24 @@
       <c r="C67" s="28"/>
       <c r="D67" s="28"/>
       <c r="E67" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F67" s="28" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G67" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H67" s="28" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="I67" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J67" s="28"/>
       <c r="K67" s="28"/>
       <c r="L67" s="29" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -4094,24 +4444,24 @@
       <c r="C68" s="28"/>
       <c r="D68" s="28"/>
       <c r="E68" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F68" s="28" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G68" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H68" s="28" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I68" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J68" s="28"/>
       <c r="K68" s="28"/>
       <c r="L68" s="29" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
@@ -4120,25 +4470,25 @@
       <c r="C69" s="28"/>
       <c r="D69" s="28"/>
       <c r="E69" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F69" s="28" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G69" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H69" s="28" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I69" s="28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J69" s="28" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="K69" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L69" s="28"/>
     </row>
@@ -4148,25 +4498,25 @@
       <c r="C70" s="17"/>
       <c r="D70" s="17"/>
       <c r="E70" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F70" s="30" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G70" s="30" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H70" s="30" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I70" s="30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J70" s="30" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="K70" s="30" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L70" s="28"/>
     </row>
@@ -4176,25 +4526,25 @@
       <c r="C71" s="28"/>
       <c r="D71" s="28"/>
       <c r="E71" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F71" s="31" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G71" s="31" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H71" s="31" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I71" s="31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J71" s="31" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K71" s="31" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L71" s="28"/>
     </row>
@@ -4204,25 +4554,25 @@
       <c r="C72" s="28"/>
       <c r="D72" s="28"/>
       <c r="E72" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F72" s="31" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G72" s="31" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H72" s="31" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="I72" s="31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J72" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K72" s="31" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L72" s="28"/>
     </row>
@@ -4232,25 +4582,25 @@
       <c r="C73" s="28"/>
       <c r="D73" s="28"/>
       <c r="E73" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F73" s="31" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G73" s="31" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H73" s="31" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I73" s="31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J73" s="31" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="K73" s="31" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L73" s="28"/>
     </row>
@@ -4260,25 +4610,25 @@
       <c r="C74" s="28"/>
       <c r="D74" s="28"/>
       <c r="E74" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F74" s="31" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G74" s="31" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H74" s="31" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="I74" s="31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J74" s="31" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="K74" s="31" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L74" s="28"/>
     </row>
@@ -4288,24 +4638,24 @@
       <c r="C75" s="28"/>
       <c r="D75" s="28"/>
       <c r="E75" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F75" s="31" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G75" s="31" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H75" s="31" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="I75" s="31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J75" s="28"/>
       <c r="K75" s="28"/>
       <c r="L75" s="32" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
@@ -4314,25 +4664,25 @@
       <c r="C76" s="31"/>
       <c r="D76" s="31"/>
       <c r="E76" s="33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F76" s="31" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G76" s="31" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H76" s="31" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I76" s="31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J76" s="31" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K76" s="31" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L76" s="28"/>
     </row>
@@ -4343,22 +4693,22 @@
       <c r="D77" s="31"/>
       <c r="E77" s="31"/>
       <c r="F77" s="34" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G77" s="34" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H77" s="34" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="I77" s="34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J77" s="34" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="K77" s="34" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L77" s="28"/>
     </row>
@@ -4368,453 +4718,930 @@
       <c r="C78" s="31"/>
       <c r="D78" s="31"/>
       <c r="E78" s="31"/>
-      <c r="F78" t="s" s="41">
+      <c r="F78" s="35" t="s">
+        <v>293</v>
+      </c>
+      <c r="G78" s="35" t="s">
+        <v>294</v>
+      </c>
+      <c r="H78" s="35" t="s">
         <v>295</v>
       </c>
-      <c r="G78" t="s" s="41">
-        <v>296</v>
-      </c>
-      <c r="H78" t="s" s="41">
-        <v>297</v>
-      </c>
-      <c r="I78" t="s" s="41">
-        <v>67</v>
+      <c r="I78" s="35" t="s">
+        <v>66</v>
       </c>
       <c r="J78" s="31"/>
       <c r="K78" s="31"/>
-      <c r="L78" t="s" s="42">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L78" s="36" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="31"/>
       <c r="B79" s="31"/>
       <c r="C79" s="31"/>
       <c r="D79" s="31"/>
       <c r="E79" s="31"/>
-      <c r="F79" t="s" s="43">
+      <c r="F79" s="35" t="s">
+        <v>296</v>
+      </c>
+      <c r="G79" s="35" t="s">
+        <v>297</v>
+      </c>
+      <c r="H79" s="35" t="s">
         <v>298</v>
       </c>
-      <c r="G79" t="s" s="43">
-        <v>299</v>
-      </c>
-      <c r="H79" t="s" s="43">
-        <v>300</v>
-      </c>
-      <c r="I79" t="s" s="43">
-        <v>67</v>
+      <c r="I79" s="35" t="s">
+        <v>66</v>
       </c>
       <c r="J79" s="31"/>
       <c r="K79" s="31"/>
-      <c r="L79" t="s" s="44">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L79" s="36" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A80" s="31"/>
       <c r="B80" s="31"/>
       <c r="C80" s="31"/>
       <c r="D80" s="31"/>
       <c r="E80" s="31"/>
-      <c r="F80" t="s" s="45">
-        <v>302</v>
-      </c>
-      <c r="G80" t="s" s="45">
-        <v>299</v>
-      </c>
-      <c r="H80" t="s" s="45">
-        <v>303</v>
-      </c>
-      <c r="I80" t="s" s="45">
-        <v>67</v>
+      <c r="F80" s="35" t="s">
+        <v>300</v>
+      </c>
+      <c r="G80" s="35" t="s">
+        <v>297</v>
+      </c>
+      <c r="H80" s="35" t="s">
+        <v>301</v>
+      </c>
+      <c r="I80" s="35" t="s">
+        <v>66</v>
       </c>
       <c r="J80" s="31"/>
       <c r="K80" s="31"/>
-      <c r="L80" t="s" s="46">
+      <c r="L80" s="36" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A81" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B81" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C81" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D81" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E81" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F81" s="35" t="s">
+        <v>303</v>
+      </c>
+      <c r="G81" s="35" t="s">
+        <v>297</v>
+      </c>
+      <c r="H81" s="35" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A81" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B81" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="C81" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="D81" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="E81" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="F81" t="s" s="47">
-        <v>305</v>
-      </c>
-      <c r="G81" t="s" s="47">
-        <v>299</v>
-      </c>
-      <c r="H81" t="s" s="47">
-        <v>306</v>
-      </c>
-      <c r="I81" t="s" s="47">
-        <v>67</v>
+      <c r="I81" s="35" t="s">
+        <v>66</v>
       </c>
       <c r="J81" s="31"/>
       <c r="K81" s="31"/>
-      <c r="L81" t="s" s="48">
+      <c r="L81" s="36" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A82" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B82" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C82" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D82" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E82" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F82" s="35" t="s">
+        <v>306</v>
+      </c>
+      <c r="G82" s="35" t="s">
+        <v>297</v>
+      </c>
+      <c r="H82" s="35" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A82" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B82" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="C82" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="D82" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="E82" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="F82" t="s" s="49">
-        <v>308</v>
-      </c>
-      <c r="G82" t="s" s="49">
-        <v>299</v>
-      </c>
-      <c r="H82" t="s" s="49">
-        <v>309</v>
-      </c>
-      <c r="I82" t="s" s="49">
-        <v>67</v>
+      <c r="I82" s="35" t="s">
+        <v>66</v>
       </c>
       <c r="J82" s="31"/>
       <c r="K82" s="31"/>
-      <c r="L82" t="s" s="50">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="F83" t="s" s="51">
+      <c r="L82" s="36" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F83" s="35" t="s">
+        <v>308</v>
+      </c>
+      <c r="G83" s="35" t="s">
+        <v>297</v>
+      </c>
+      <c r="H83" s="35" t="s">
+        <v>309</v>
+      </c>
+      <c r="I83" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="L83" s="36" t="s">
         <v>310</v>
       </c>
-      <c r="G83" t="s" s="51">
-        <v>299</v>
-      </c>
-      <c r="H83" t="s" s="51">
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F84" s="35" t="s">
+        <v>312</v>
+      </c>
+      <c r="G84" s="35" t="s">
+        <v>297</v>
+      </c>
+      <c r="H84" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="I84" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="J84" s="35" t="s">
         <v>311</v>
       </c>
-      <c r="I83" t="s" s="51">
-        <v>67</v>
-      </c>
-      <c r="L83" t="s" s="52">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="F84" t="s" s="54">
+      <c r="K84" s="35" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F85" s="35" t="s">
         <v>314</v>
       </c>
-      <c r="G84" t="s" s="54">
-        <v>299</v>
-      </c>
-      <c r="H84" t="s" s="54">
+      <c r="G85" s="35" t="s">
+        <v>297</v>
+      </c>
+      <c r="H85" s="35" t="s">
         <v>315</v>
       </c>
-      <c r="I84" t="s" s="54">
-        <v>73</v>
-      </c>
-      <c r="J84" t="s" s="53">
-        <v>313</v>
-      </c>
-      <c r="K84" t="s" s="53">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="F85" t="s" s="55">
+      <c r="I85" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="L85" s="36" t="s">
         <v>316</v>
       </c>
-      <c r="G85" t="s" s="55">
-        <v>299</v>
-      </c>
-      <c r="H85" t="s" s="55">
+    </row>
+    <row r="86" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F86" s="35" t="s">
         <v>317</v>
       </c>
-      <c r="I85" t="s" s="55">
-        <v>67</v>
-      </c>
-      <c r="L85" t="s" s="56">
+      <c r="G86" s="35" t="s">
+        <v>297</v>
+      </c>
+      <c r="H86" s="35" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="86">
-      <c r="F86" t="s" s="57">
+      <c r="I86" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="L86" s="36" t="s">
         <v>319</v>
       </c>
-      <c r="G86" t="s" s="57">
-        <v>299</v>
-      </c>
-      <c r="H86" t="s" s="57">
+    </row>
+    <row r="87" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="F87" s="35" t="s">
         <v>320</v>
       </c>
-      <c r="I86" t="s" s="57">
-        <v>67</v>
-      </c>
-      <c r="L86" t="s" s="58">
+      <c r="G87" s="35" t="s">
+        <v>297</v>
+      </c>
+      <c r="H87" s="35" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="87">
-      <c r="F87" t="s" s="59">
+      <c r="I87" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="L87" s="36" t="s">
         <v>322</v>
       </c>
-      <c r="G87" t="s" s="59">
-        <v>299</v>
-      </c>
-      <c r="H87" t="s" s="59">
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F88" s="35" t="s">
         <v>323</v>
       </c>
-      <c r="I87" t="s" s="59">
-        <v>67</v>
-      </c>
-      <c r="L87" t="s" s="60">
+      <c r="G88" s="35" t="s">
+        <v>297</v>
+      </c>
+      <c r="H88" s="35" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="88">
-      <c r="F88" t="s" s="61">
+      <c r="I88" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="L88" s="36" t="s">
         <v>325</v>
       </c>
-      <c r="G88" t="s" s="61">
-        <v>299</v>
-      </c>
-      <c r="H88" t="s" s="61">
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F89" s="35" t="s">
+        <v>327</v>
+      </c>
+      <c r="G89" s="35" t="s">
+        <v>297</v>
+      </c>
+      <c r="H89" s="35" t="s">
+        <v>328</v>
+      </c>
+      <c r="I89" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="J89" s="35" t="s">
         <v>326</v>
       </c>
-      <c r="I88" t="s" s="61">
-        <v>67</v>
-      </c>
-      <c r="L88" t="s" s="62">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="F89" t="s" s="64">
+      <c r="K89" s="35" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F90" s="35" t="s">
         <v>329</v>
       </c>
-      <c r="G89" t="s" s="64">
-        <v>299</v>
-      </c>
-      <c r="H89" t="s" s="64">
+      <c r="G90" s="35" t="s">
         <v>330</v>
       </c>
-      <c r="I89" t="s" s="64">
-        <v>73</v>
-      </c>
-      <c r="J89" t="s" s="63">
-        <v>328</v>
-      </c>
-      <c r="K89" t="s" s="63">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="F90" t="s" s="65">
+      <c r="H90" s="35" t="s">
         <v>331</v>
       </c>
-      <c r="G90" t="s" s="65">
+      <c r="I90" s="35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F91" s="35" t="s">
+        <v>333</v>
+      </c>
+      <c r="G91" s="35" t="s">
+        <v>330</v>
+      </c>
+      <c r="H91" s="35" t="s">
+        <v>334</v>
+      </c>
+      <c r="I91" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="J91" s="35" t="s">
         <v>332</v>
       </c>
-      <c r="H90" t="s" s="65">
-        <v>333</v>
-      </c>
-      <c r="I90" t="s" s="65">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="F91" t="s" s="67">
+      <c r="K91" s="35" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F92" s="35" t="s">
         <v>335</v>
       </c>
-      <c r="G91" t="s" s="67">
-        <v>332</v>
-      </c>
-      <c r="H91" t="s" s="67">
+      <c r="G92" s="35" t="s">
+        <v>330</v>
+      </c>
+      <c r="H92" s="35" t="s">
         <v>336</v>
       </c>
-      <c r="I91" t="s" s="67">
-        <v>73</v>
-      </c>
-      <c r="J91" t="s" s="66">
-        <v>334</v>
-      </c>
-      <c r="K91" t="s" s="66">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="F92" t="s" s="68">
+      <c r="I92" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="L92" s="36" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F93" s="35" t="s">
+        <v>338</v>
+      </c>
+      <c r="G93" s="35" t="s">
+        <v>330</v>
+      </c>
+      <c r="H93" s="35" t="s">
+        <v>339</v>
+      </c>
+      <c r="I93" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="J93" s="35" t="s">
         <v>337</v>
       </c>
-      <c r="G92" t="s" s="68">
-        <v>332</v>
-      </c>
-      <c r="H92" t="s" s="68">
-        <v>338</v>
-      </c>
-      <c r="I92" t="s" s="68">
-        <v>67</v>
-      </c>
-      <c r="L92" t="s" s="69">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="F93" t="s" s="71">
+      <c r="K93" s="35" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F94" s="35" t="s">
         <v>340</v>
       </c>
-      <c r="G93" t="s" s="71">
-        <v>332</v>
-      </c>
-      <c r="H93" t="s" s="71">
+      <c r="G94" s="35" t="s">
+        <v>330</v>
+      </c>
+      <c r="H94" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="I93" t="s" s="71">
-        <v>73</v>
-      </c>
-      <c r="J93" t="s" s="70">
-        <v>339</v>
-      </c>
-      <c r="K93" t="s" s="70">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="F94" t="s" s="72">
+      <c r="I94" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="L94" s="36" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F95" s="35" t="s">
         <v>342</v>
       </c>
-      <c r="G94" t="s" s="72">
-        <v>332</v>
-      </c>
-      <c r="H94" t="s" s="72">
+      <c r="G95" s="35" t="s">
+        <v>330</v>
+      </c>
+      <c r="H95" s="35" t="s">
         <v>343</v>
       </c>
-      <c r="I94" t="s" s="72">
-        <v>67</v>
-      </c>
-      <c r="L94" t="s" s="73">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="F95" t="s" s="74">
+      <c r="I95" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="L95" s="36" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F96" s="35" t="s">
         <v>344</v>
       </c>
-      <c r="G95" t="s" s="74">
-        <v>332</v>
-      </c>
-      <c r="H95" t="s" s="74">
+      <c r="G96" s="35" t="s">
+        <v>330</v>
+      </c>
+      <c r="H96" s="35" t="s">
         <v>345</v>
       </c>
-      <c r="I95" t="s" s="74">
-        <v>67</v>
-      </c>
-      <c r="L95" t="s" s="75">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="F96" t="s" s="76">
+      <c r="I96" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="L96" s="36" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="97" spans="6:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F97" s="35" t="s">
         <v>346</v>
       </c>
-      <c r="G96" t="s" s="76">
-        <v>332</v>
-      </c>
-      <c r="H96" t="s" s="76">
+      <c r="G97" s="35" t="s">
+        <v>330</v>
+      </c>
+      <c r="H97" s="35" t="s">
         <v>347</v>
       </c>
-      <c r="I96" t="s" s="76">
-        <v>67</v>
-      </c>
-      <c r="L96" t="s" s="77">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="F97" t="s" s="78">
+      <c r="I97" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="L97" s="36" t="s">
         <v>348</v>
       </c>
-      <c r="G97" t="s" s="78">
-        <v>332</v>
-      </c>
-      <c r="H97" t="s" s="78">
+    </row>
+    <row r="98" spans="6:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F98" s="35" t="s">
         <v>349</v>
       </c>
-      <c r="I97" t="s" s="78">
-        <v>67</v>
-      </c>
-      <c r="L97" t="s" s="79">
+      <c r="G98" s="35" t="s">
+        <v>330</v>
+      </c>
+      <c r="H98" s="35" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="98">
-      <c r="F98" t="s" s="80">
+      <c r="I98" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="L98" s="36" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="99" spans="6:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F99" s="35" t="s">
         <v>351</v>
       </c>
-      <c r="G98" t="s" s="80">
-        <v>332</v>
-      </c>
-      <c r="H98" t="s" s="80">
+      <c r="G99" s="35" t="s">
+        <v>330</v>
+      </c>
+      <c r="H99" s="35" t="s">
         <v>352</v>
       </c>
-      <c r="I98" t="s" s="80">
-        <v>67</v>
-      </c>
-      <c r="L98" t="s" s="81">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="F99" t="s" s="82">
+      <c r="I99" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="L99" s="36" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="100" spans="6:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F100" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="G99" t="s" s="82">
-        <v>332</v>
-      </c>
-      <c r="H99" t="s" s="82">
+      <c r="G100" s="35" t="s">
+        <v>330</v>
+      </c>
+      <c r="H100" s="35" t="s">
         <v>354</v>
       </c>
-      <c r="I99" t="s" s="82">
-        <v>67</v>
-      </c>
-      <c r="L99" t="s" s="83">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="F100" t="s" s="84">
+      <c r="I100" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="L100" s="36" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="101" spans="6:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="F101" s="35" t="s">
         <v>355</v>
       </c>
-      <c r="G100" t="s" s="84">
-        <v>332</v>
-      </c>
-      <c r="H100" t="s" s="84">
+      <c r="G101" s="35" t="s">
         <v>356</v>
       </c>
-      <c r="I100" t="s" s="84">
-        <v>67</v>
-      </c>
-      <c r="L100" t="s" s="85">
-        <v>350</v>
+      <c r="H101" s="35" t="s">
+        <v>357</v>
+      </c>
+      <c r="I101" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="L101" s="36" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="102" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F102" s="35" t="s">
+        <v>359</v>
+      </c>
+      <c r="G102" s="35" t="s">
+        <v>356</v>
+      </c>
+      <c r="H102" s="35" t="s">
+        <v>360</v>
+      </c>
+      <c r="I102" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="L102" s="36" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="103" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F103" s="35" t="s">
+        <v>359</v>
+      </c>
+      <c r="G103" s="35" t="s">
+        <v>356</v>
+      </c>
+      <c r="H103" s="35" t="s">
+        <v>361</v>
+      </c>
+      <c r="I103" s="35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="104" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F104" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="G104" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="H104" s="39" t="s">
+        <v>367</v>
+      </c>
+      <c r="I104" s="39" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="105" spans="6:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F105" s="39" t="s">
+        <v>368</v>
+      </c>
+      <c r="G105" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="H105" s="39" t="s">
+        <v>369</v>
+      </c>
+      <c r="I105" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="L105" s="40" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="106" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F106" s="39" t="s">
+        <v>370</v>
+      </c>
+      <c r="G106" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="H106" s="39" t="s">
+        <v>371</v>
+      </c>
+      <c r="I106" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="L106" s="40" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="107" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F107" s="39" t="s">
+        <v>373</v>
+      </c>
+      <c r="G107" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="H107" s="39" t="s">
+        <v>374</v>
+      </c>
+      <c r="I107" s="39" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="108" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F108" s="39" t="s">
+        <v>375</v>
+      </c>
+      <c r="G108" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="H108" s="39" t="s">
+        <v>376</v>
+      </c>
+      <c r="I108" s="39" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="109" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F109" s="39" t="s">
+        <v>377</v>
+      </c>
+      <c r="G109" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="H109" s="39" t="s">
+        <v>378</v>
+      </c>
+      <c r="I109" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="L109" s="40" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="110" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F110" s="39" t="s">
+        <v>377</v>
+      </c>
+      <c r="G110" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="H110" s="39" t="s">
+        <v>379</v>
+      </c>
+      <c r="I110" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="L110" s="40" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="111" spans="6:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F111" s="39" t="s">
+        <v>381</v>
+      </c>
+      <c r="G111" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="H111" s="39" t="s">
+        <v>382</v>
+      </c>
+      <c r="I111" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="L111" s="40" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="112" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F112" s="39" t="s">
+        <v>384</v>
+      </c>
+      <c r="G112" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="H112" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="I112" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="L112" s="40" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="113" spans="6:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F113" s="39" t="s">
+        <v>386</v>
+      </c>
+      <c r="G113" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="H113" s="39" t="s">
+        <v>387</v>
+      </c>
+      <c r="I113" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="L113" s="40" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="114" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F114" s="39" t="s">
+        <v>389</v>
+      </c>
+      <c r="G114" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="H114" s="39" t="s">
+        <v>390</v>
+      </c>
+      <c r="I114" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="J114" s="39" t="s">
+        <v>388</v>
+      </c>
+      <c r="K114" s="39" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="115" spans="6:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F115" s="39" t="s">
+        <v>391</v>
+      </c>
+      <c r="G115" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="H115" s="39" t="s">
+        <v>392</v>
+      </c>
+      <c r="I115" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="L115" s="40" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="116" spans="6:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F116" s="39" t="s">
+        <v>391</v>
+      </c>
+      <c r="G116" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="H116" s="39" t="s">
+        <v>395</v>
+      </c>
+      <c r="I116" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="J116" s="39" t="s">
+        <v>394</v>
+      </c>
+      <c r="K116" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="L116" s="40" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="117" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F117" s="46" t="s">
+        <v>409</v>
+      </c>
+      <c r="G117" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="H117" s="46" t="s">
+        <v>411</v>
+      </c>
+      <c r="I117" s="46" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="118" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F118" s="46" t="s">
+        <v>412</v>
+      </c>
+      <c r="G118" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="H118" s="46" t="s">
+        <v>413</v>
+      </c>
+      <c r="I118" s="46" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="119" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F119" s="46" t="s">
+        <v>414</v>
+      </c>
+      <c r="G119" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="H119" s="46" t="s">
+        <v>415</v>
+      </c>
+      <c r="I119" s="46" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="120" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F120" s="46" t="s">
+        <v>416</v>
+      </c>
+      <c r="G120" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="H120" s="46" t="s">
+        <v>417</v>
+      </c>
+      <c r="I120" s="46" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="121" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F121" s="46" t="s">
+        <v>418</v>
+      </c>
+      <c r="G121" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="H121" s="46" t="s">
+        <v>419</v>
+      </c>
+      <c r="I121" s="46" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="122" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F122" s="46" t="s">
+        <v>420</v>
+      </c>
+      <c r="G122" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="H122" s="46" t="s">
+        <v>421</v>
+      </c>
+      <c r="I122" s="46" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="123" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F123" s="46" t="s">
+        <v>422</v>
+      </c>
+      <c r="G123" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="H123" s="46" t="s">
+        <v>423</v>
+      </c>
+      <c r="I123" s="46" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="124" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F124" s="46" t="s">
+        <v>424</v>
+      </c>
+      <c r="G124" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="H124" s="46" t="s">
+        <v>425</v>
+      </c>
+      <c r="I124" s="46" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="125" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F125" s="46" t="s">
+        <v>426</v>
+      </c>
+      <c r="G125" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="H125" s="46" t="s">
+        <v>427</v>
+      </c>
+      <c r="I125" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="L125" s="47" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="126" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F126" s="46" t="s">
+        <v>429</v>
+      </c>
+      <c r="G126" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="H126" s="46" t="s">
+        <v>430</v>
+      </c>
+      <c r="I126" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="L126" s="47" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="127" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F127" s="46" t="s">
+        <v>431</v>
+      </c>
+      <c r="G127" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="H127" s="46" t="s">
+        <v>432</v>
+      </c>
+      <c r="I127" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="L127" s="47" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="F128" t="s" s="57">
+        <v>442</v>
+      </c>
+      <c r="G128" t="s" s="57">
+        <v>440</v>
+      </c>
+      <c r="H128" t="s" s="57">
+        <v>443</v>
+      </c>
+      <c r="I128" t="s" s="57">
+        <v>66</v>
+      </c>
+      <c r="L128" t="s" s="58">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="F129" t="s" s="59">
+        <v>444</v>
+      </c>
+      <c r="G129" t="s" s="59">
+        <v>440</v>
+      </c>
+      <c r="H129" t="s" s="59">
+        <v>445</v>
+      </c>
+      <c r="I129" t="s" s="59">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="F130" t="s" s="63">
+        <v>451</v>
+      </c>
+      <c r="G130" t="s" s="63">
+        <v>440</v>
+      </c>
+      <c r="H130" t="s" s="63">
+        <v>452</v>
+      </c>
+      <c r="I130" t="s" s="63">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -4831,7 +5658,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70924E6C-D075-47E0-B0CB-3BEFA71EC108}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="12.77734375"/>
@@ -4845,9 +5672,10 @@
     <col min="9" max="9" bestFit="true" customWidth="true" width="14.88671875"/>
     <col min="10" max="10" bestFit="true" customWidth="true" width="7.88671875"/>
     <col min="11" max="11" bestFit="true" customWidth="true" width="9.77734375"/>
+    <col min="12" max="12" customWidth="true" width="50.0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="27" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="27" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -4855,16 +5683,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D1" s="24" t="s">
         <v>14</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F1" s="25" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="G1" s="24" t="s">
         <v>24</v>
@@ -4878,80 +5706,351 @@
       <c r="J1" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="26" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K1" s="42" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="F2" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="41" t="s">
+        <v>366</v>
+      </c>
+      <c r="H2" s="41" t="s">
+        <v>401</v>
+      </c>
+      <c r="I2" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="J2" s="41" t="s">
+        <v>400</v>
+      </c>
+      <c r="K2" s="43" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>434</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="41" t="s">
+        <v>366</v>
+      </c>
+      <c r="H3" s="41" t="s">
+        <v>397</v>
+      </c>
+      <c r="I3" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="44"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
+        <v>433</v>
+      </c>
+      <c r="F4" s="41" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="41" t="s">
+        <v>366</v>
+      </c>
+      <c r="H4" s="41" t="s">
+        <v>398</v>
+      </c>
+      <c r="I4" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="44"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>366</v>
+      </c>
+      <c r="H5" s="30" t="s">
+        <v>399</v>
+      </c>
+      <c r="I5" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="44"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="F6" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="G6" s="45" t="s">
+        <v>366</v>
+      </c>
+      <c r="H6" s="45" t="s">
+        <v>403</v>
+      </c>
+      <c r="I6" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="J6" s="45" t="s">
+        <v>402</v>
+      </c>
+      <c r="K6" s="45" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="F7" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="G7" s="45" t="s">
+        <v>366</v>
+      </c>
+      <c r="H7" s="45" t="s">
+        <v>408</v>
+      </c>
+      <c r="I7" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="J7" s="45" t="s">
+        <v>407</v>
+      </c>
+      <c r="K7" s="45" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="56" t="s">
+        <v>95</v>
+      </c>
+      <c r="G8" s="56" t="s">
+        <v>440</v>
+      </c>
+      <c r="H8" s="56" t="s">
+        <v>441</v>
+      </c>
+      <c r="I8" s="56" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8" s="55" t="s">
+        <v>439</v>
+      </c>
+      <c r="K8" s="55" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="G9" s="62" t="s">
+        <v>440</v>
+      </c>
+      <c r="H9" s="62" t="s">
+        <v>450</v>
+      </c>
+      <c r="I9" s="62" t="s">
+        <v>72</v>
+      </c>
+      <c r="J9" s="61" t="s">
+        <v>449</v>
+      </c>
+      <c r="K9" s="61" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="41"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="41"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="41"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/test/resources/POC_data_sheet_v1.1.xlsx
+++ b/src/test/resources/POC_data_sheet_v1.1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SPidugujothi\IdeaProjects\MyridiusUAF\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33481A8C-BEDC-47BF-A1C4-E6BA37202D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA79DA60-A14B-4B13-975C-32EA904489EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{08B05D20-EDEF-43CA-A5DF-998FB408C439}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="551">
   <si>
     <t>Application</t>
   </si>
@@ -1136,9 +1136,6 @@
     <t>Register Time</t>
   </si>
   <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
     <t>R102</t>
   </si>
   <si>
@@ -1235,42 +1232,6 @@
     <t>Expected condition failed: waiting for element to be clickable: Proxy element for: DefaultElementLoc…</t>
   </si>
   <si>
-    <t>21:26:32</t>
-  </si>
-  <si>
-    <t>21:28:24</t>
-  </si>
-  <si>
-    <t>21:31:25</t>
-  </si>
-  <si>
-    <t>2057437</t>
-  </si>
-  <si>
-    <t>21:45:26</t>
-  </si>
-  <si>
-    <t>2057446</t>
-  </si>
-  <si>
-    <t>22:08:39</t>
-  </si>
-  <si>
-    <t>amit.patel548@gmail.com</t>
-  </si>
-  <si>
-    <t>U7zBhiD7R0</t>
-  </si>
-  <si>
-    <t>22:18:39</t>
-  </si>
-  <si>
-    <t>2057456</t>
-  </si>
-  <si>
-    <t>22:20:24</t>
-  </si>
-  <si>
     <t>R115</t>
   </si>
   <si>
@@ -1349,27 +1310,9 @@
     <t>SC1-TC1-E2E-Reorder</t>
   </si>
   <si>
-    <t>divya.yadav453@yahoo.com</t>
-  </si>
-  <si>
-    <t>dLJv5nFgww</t>
-  </si>
-  <si>
-    <t>2025-07-30</t>
-  </si>
-  <si>
-    <t>16:28:36</t>
-  </si>
-  <si>
-    <t>2061022</t>
-  </si>
-  <si>
     <t>07/30/2025</t>
   </si>
   <si>
-    <t>16:30:53</t>
-  </si>
-  <si>
     <t>R126</t>
   </si>
   <si>
@@ -1382,25 +1325,376 @@
     <t>18:44:05</t>
   </si>
   <si>
-    <t>rohan.singh229@yahoo.com</t>
-  </si>
-  <si>
-    <t>*MAagSfDyI</t>
-  </si>
-  <si>
-    <t>18:56:09</t>
-  </si>
-  <si>
-    <t>2061138</t>
-  </si>
-  <si>
-    <t>18:58:31</t>
-  </si>
-  <si>
     <t>R128</t>
   </si>
   <si>
     <t>21:25:14</t>
+  </si>
+  <si>
+    <t>R129</t>
+  </si>
+  <si>
+    <t>08/01/2025</t>
+  </si>
+  <si>
+    <t>16:30:43</t>
+  </si>
+  <si>
+    <t>R130</t>
+  </si>
+  <si>
+    <t>20:33:10</t>
+  </si>
+  <si>
+    <t>R131</t>
+  </si>
+  <si>
+    <t>08/02/2025</t>
+  </si>
+  <si>
+    <t>08:28:31</t>
+  </si>
+  <si>
+    <t>R132</t>
+  </si>
+  <si>
+    <t>08:55:41</t>
+  </si>
+  <si>
+    <t>R133</t>
+  </si>
+  <si>
+    <t>09:02:58</t>
+  </si>
+  <si>
+    <t>Login was not successful for user: rohan.singh229@yahoo.com</t>
+  </si>
+  <si>
+    <t>R134</t>
+  </si>
+  <si>
+    <t>09:06:36</t>
+  </si>
+  <si>
+    <t>R135</t>
+  </si>
+  <si>
+    <t>09:14:54</t>
+  </si>
+  <si>
+    <t>R136</t>
+  </si>
+  <si>
+    <t>09:20:15</t>
+  </si>
+  <si>
+    <t>R137</t>
+  </si>
+  <si>
+    <t>10:54:01</t>
+  </si>
+  <si>
+    <t>R138</t>
+  </si>
+  <si>
+    <t>11:04:06</t>
+  </si>
+  <si>
+    <t>R139</t>
+  </si>
+  <si>
+    <t>11:11:54</t>
+  </si>
+  <si>
+    <t>R140</t>
+  </si>
+  <si>
+    <t>11:16:46</t>
+  </si>
+  <si>
+    <t>R141</t>
+  </si>
+  <si>
+    <t>11:22:58</t>
+  </si>
+  <si>
+    <t>R142</t>
+  </si>
+  <si>
+    <t>11:26:28</t>
+  </si>
+  <si>
+    <t>R143</t>
+  </si>
+  <si>
+    <t>08/09/2025</t>
+  </si>
+  <si>
+    <t>23:31:30</t>
+  </si>
+  <si>
+    <t>R144</t>
+  </si>
+  <si>
+    <t>23:41:47</t>
+  </si>
+  <si>
+    <t>R145</t>
+  </si>
+  <si>
+    <t>08/11/2025</t>
+  </si>
+  <si>
+    <t>11:31:36</t>
+  </si>
+  <si>
+    <t>R146</t>
+  </si>
+  <si>
+    <t>11:35:57</t>
+  </si>
+  <si>
+    <t>R147</t>
+  </si>
+  <si>
+    <t>11:46:15</t>
+  </si>
+  <si>
+    <t>R148</t>
+  </si>
+  <si>
+    <t>11:55:18</t>
+  </si>
+  <si>
+    <t>R149</t>
+  </si>
+  <si>
+    <t>12:02:17</t>
+  </si>
+  <si>
+    <t>R150</t>
+  </si>
+  <si>
+    <t>13:28:44</t>
+  </si>
+  <si>
+    <t>R151</t>
+  </si>
+  <si>
+    <t>13:28:53</t>
+  </si>
+  <si>
+    <t>The supplied file was empty (zero bytes long)</t>
+  </si>
+  <si>
+    <t>R152</t>
+  </si>
+  <si>
+    <t>16:09:39</t>
+  </si>
+  <si>
+    <t>R153</t>
+  </si>
+  <si>
+    <t>16:20:50</t>
+  </si>
+  <si>
+    <t>R154</t>
+  </si>
+  <si>
+    <t>16:30:44</t>
+  </si>
+  <si>
+    <t>R155</t>
+  </si>
+  <si>
+    <t>16:35:14</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>R156</t>
+  </si>
+  <si>
+    <t>17:12:55</t>
+  </si>
+  <si>
+    <t>R157</t>
+  </si>
+  <si>
+    <t>17:43:14</t>
+  </si>
+  <si>
+    <t>R158</t>
+  </si>
+  <si>
+    <t>19:03:47</t>
+  </si>
+  <si>
+    <t>R159</t>
+  </si>
+  <si>
+    <t>19:10:51</t>
+  </si>
+  <si>
+    <t>R160</t>
+  </si>
+  <si>
+    <t>19:45:54</t>
+  </si>
+  <si>
+    <t>rahul.reddy917@outlook.com</t>
+  </si>
+  <si>
+    <t>kX6*KwD%cy</t>
+  </si>
+  <si>
+    <t>20:19:03</t>
+  </si>
+  <si>
+    <t>R161</t>
+  </si>
+  <si>
+    <t>20:19:25</t>
+  </si>
+  <si>
+    <t>R162</t>
+  </si>
+  <si>
+    <t>20:22:16</t>
+  </si>
+  <si>
+    <t>Invalid gender: Male89. Allowed: [male, female]</t>
+  </si>
+  <si>
+    <t>R163</t>
+  </si>
+  <si>
+    <t>08/12/2025</t>
+  </si>
+  <si>
+    <t>00:18:06</t>
+  </si>
+  <si>
+    <t>2077088</t>
+  </si>
+  <si>
+    <t>R164</t>
+  </si>
+  <si>
+    <t>09:56:12</t>
+  </si>
+  <si>
+    <t>R165</t>
+  </si>
+  <si>
+    <t>22:04:25</t>
+  </si>
+  <si>
+    <t>08/11/2026</t>
+  </si>
+  <si>
+    <t>R166</t>
+  </si>
+  <si>
+    <t>22:39:50</t>
+  </si>
+  <si>
+    <t>2077781</t>
+  </si>
+  <si>
+    <t>R167</t>
+  </si>
+  <si>
+    <t>22:40:50</t>
+  </si>
+  <si>
+    <t>R168</t>
+  </si>
+  <si>
+    <t>08/12/2026</t>
+  </si>
+  <si>
+    <t>22:40:51</t>
+  </si>
+  <si>
+    <t>R169</t>
+  </si>
+  <si>
+    <t>23:20:37</t>
+  </si>
+  <si>
+    <t>R170</t>
+  </si>
+  <si>
+    <t>23:24:56</t>
+  </si>
+  <si>
+    <t>2077792</t>
+  </si>
+  <si>
+    <t>E2E1</t>
+  </si>
+  <si>
+    <t>23:29:04</t>
+  </si>
+  <si>
+    <t>R171</t>
+  </si>
+  <si>
+    <t>08/13/2025</t>
+  </si>
+  <si>
+    <t>07:24:34</t>
+  </si>
+  <si>
+    <t>2077932</t>
+  </si>
+  <si>
+    <t>R172</t>
+  </si>
+  <si>
+    <t>07:40:21</t>
+  </si>
+  <si>
+    <t>2077943</t>
+  </si>
+  <si>
+    <t>E2E2</t>
+  </si>
+  <si>
+    <t>08:07:26</t>
+  </si>
+  <si>
+    <t>2077988</t>
+  </si>
+  <si>
+    <t>E2E3</t>
+  </si>
+  <si>
+    <t>09:07:32</t>
+  </si>
+  <si>
+    <t>E2E4</t>
+  </si>
+  <si>
+    <t>12:48:04</t>
+  </si>
+  <si>
+    <t>E2E5</t>
+  </si>
+  <si>
+    <t>12:48:28</t>
+  </si>
+  <si>
+    <t>No row found for key: Ip7 in sheet: Synthetic_Data (col 5)</t>
+  </si>
+  <si>
+    <t>E2E6</t>
+  </si>
+  <si>
+    <t>13:04:03</t>
   </si>
 </sst>
 </file>
@@ -1483,7 +1777,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -1716,6 +2010,139 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <top style="thin"/>
     </border>
     <border>
@@ -1738,7 +2165,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1842,13 +2269,30 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1869,18 +2313,13 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true">
       <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2261,11 +2700,11 @@
       <c r="B2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C2" t="s" s="60">
-        <v>446</v>
-      </c>
-      <c r="D2" t="s" s="60">
-        <v>447</v>
+      <c r="C2" t="s" s="0">
+        <v>500</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>501</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>31</v>
@@ -2273,11 +2712,11 @@
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G2" t="s" s="60">
-        <v>437</v>
-      </c>
-      <c r="H2" t="s" s="60">
-        <v>448</v>
+      <c r="G2" t="s" s="0">
+        <v>489</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>502</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -2345,28 +2784,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="49" t="s">
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="50"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="61"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
@@ -2610,7 +3049,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{087D34EC-64B6-464A-B1FA-1B3B12C5A42D}">
-  <dimension ref="A1:L130"/>
+  <dimension ref="A1:L179"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="15.44140625"/>
@@ -2628,23 +3067,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="52" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="63" t="s">
         <v>116</v>
       </c>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="53" t="s">
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="64" t="s">
         <v>117</v>
       </c>
-      <c r="K1" s="53"/>
+      <c r="K1" s="64"/>
       <c r="L1" s="17"/>
     </row>
     <row r="2" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5217,13 +5656,13 @@
     </row>
     <row r="104" spans="6:12" x14ac:dyDescent="0.3">
       <c r="F104" s="39" t="s">
+        <v>364</v>
+      </c>
+      <c r="G104" s="39" t="s">
         <v>365</v>
       </c>
-      <c r="G104" s="39" t="s">
+      <c r="H104" s="39" t="s">
         <v>366</v>
-      </c>
-      <c r="H104" s="39" t="s">
-        <v>367</v>
       </c>
       <c r="I104" s="39" t="s">
         <v>72</v>
@@ -5231,13 +5670,13 @@
     </row>
     <row r="105" spans="6:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="F105" s="39" t="s">
+        <v>367</v>
+      </c>
+      <c r="G105" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="H105" s="39" t="s">
         <v>368</v>
-      </c>
-      <c r="G105" s="39" t="s">
-        <v>366</v>
-      </c>
-      <c r="H105" s="39" t="s">
-        <v>369</v>
       </c>
       <c r="I105" s="39" t="s">
         <v>66</v>
@@ -5248,30 +5687,30 @@
     </row>
     <row r="106" spans="6:12" x14ac:dyDescent="0.3">
       <c r="F106" s="39" t="s">
+        <v>369</v>
+      </c>
+      <c r="G106" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="H106" s="39" t="s">
         <v>370</v>
       </c>
-      <c r="G106" s="39" t="s">
-        <v>366</v>
-      </c>
-      <c r="H106" s="39" t="s">
+      <c r="I106" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="L106" s="40" t="s">
         <v>371</v>
-      </c>
-      <c r="I106" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="L106" s="40" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="107" spans="6:12" x14ac:dyDescent="0.3">
       <c r="F107" s="39" t="s">
+        <v>372</v>
+      </c>
+      <c r="G107" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="H107" s="39" t="s">
         <v>373</v>
-      </c>
-      <c r="G107" s="39" t="s">
-        <v>366</v>
-      </c>
-      <c r="H107" s="39" t="s">
-        <v>374</v>
       </c>
       <c r="I107" s="39" t="s">
         <v>72</v>
@@ -5279,13 +5718,13 @@
     </row>
     <row r="108" spans="6:12" x14ac:dyDescent="0.3">
       <c r="F108" s="39" t="s">
+        <v>374</v>
+      </c>
+      <c r="G108" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="H108" s="39" t="s">
         <v>375</v>
-      </c>
-      <c r="G108" s="39" t="s">
-        <v>366</v>
-      </c>
-      <c r="H108" s="39" t="s">
-        <v>376</v>
       </c>
       <c r="I108" s="39" t="s">
         <v>72</v>
@@ -5293,13 +5732,13 @@
     </row>
     <row r="109" spans="6:12" x14ac:dyDescent="0.3">
       <c r="F109" s="39" t="s">
+        <v>376</v>
+      </c>
+      <c r="G109" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="H109" s="39" t="s">
         <v>377</v>
-      </c>
-      <c r="G109" s="39" t="s">
-        <v>366</v>
-      </c>
-      <c r="H109" s="39" t="s">
-        <v>378</v>
       </c>
       <c r="I109" s="39" t="s">
         <v>66</v>
@@ -5310,87 +5749,87 @@
     </row>
     <row r="110" spans="6:12" x14ac:dyDescent="0.3">
       <c r="F110" s="39" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G110" s="39" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H110" s="39" t="s">
+        <v>378</v>
+      </c>
+      <c r="I110" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="L110" s="40" t="s">
         <v>379</v>
-      </c>
-      <c r="I110" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="L110" s="40" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="111" spans="6:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="F111" s="39" t="s">
+        <v>380</v>
+      </c>
+      <c r="G111" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="H111" s="39" t="s">
         <v>381</v>
       </c>
-      <c r="G111" s="39" t="s">
-        <v>366</v>
-      </c>
-      <c r="H111" s="39" t="s">
+      <c r="I111" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="L111" s="40" t="s">
         <v>382</v>
-      </c>
-      <c r="I111" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="L111" s="40" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="112" spans="6:12" x14ac:dyDescent="0.3">
       <c r="F112" s="39" t="s">
+        <v>383</v>
+      </c>
+      <c r="G112" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="H112" s="39" t="s">
         <v>384</v>
       </c>
-      <c r="G112" s="39" t="s">
-        <v>366</v>
-      </c>
-      <c r="H112" s="39" t="s">
-        <v>385</v>
-      </c>
       <c r="I112" s="39" t="s">
         <v>66</v>
       </c>
       <c r="L112" s="40" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="113" spans="6:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="F113" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="G113" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="H113" s="39" t="s">
         <v>386</v>
       </c>
-      <c r="G113" s="39" t="s">
-        <v>366</v>
-      </c>
-      <c r="H113" s="39" t="s">
-        <v>387</v>
-      </c>
       <c r="I113" s="39" t="s">
         <v>66</v>
       </c>
       <c r="L113" s="40" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="114" spans="6:12" x14ac:dyDescent="0.3">
       <c r="F114" s="39" t="s">
+        <v>388</v>
+      </c>
+      <c r="G114" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="H114" s="39" t="s">
         <v>389</v>
       </c>
-      <c r="G114" s="39" t="s">
-        <v>366</v>
-      </c>
-      <c r="H114" s="39" t="s">
-        <v>390</v>
-      </c>
       <c r="I114" s="39" t="s">
         <v>72</v>
       </c>
       <c r="J114" s="39" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K114" s="39" t="s">
         <v>356</v>
@@ -5398,251 +5837,1107 @@
     </row>
     <row r="115" spans="6:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="F115" s="39" t="s">
+        <v>390</v>
+      </c>
+      <c r="G115" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="H115" s="39" t="s">
         <v>391</v>
       </c>
-      <c r="G115" s="39" t="s">
-        <v>366</v>
-      </c>
-      <c r="H115" s="39" t="s">
+      <c r="I115" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="L115" s="40" t="s">
         <v>392</v>
-      </c>
-      <c r="I115" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="L115" s="40" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="116" spans="6:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="F116" s="39" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G116" s="39" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H116" s="39" t="s">
+        <v>394</v>
+      </c>
+      <c r="I116" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="J116" s="39" t="s">
+        <v>393</v>
+      </c>
+      <c r="K116" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="L116" s="40" t="s">
         <v>395</v>
       </c>
-      <c r="I116" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="J116" s="39" t="s">
-        <v>394</v>
-      </c>
-      <c r="K116" s="39" t="s">
-        <v>366</v>
-      </c>
-      <c r="L116" s="40" t="s">
+    </row>
+    <row r="117" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F117" s="44" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="117" spans="6:12" x14ac:dyDescent="0.3">
-      <c r="F117" s="46" t="s">
+      <c r="G117" s="44" t="s">
+        <v>397</v>
+      </c>
+      <c r="H117" s="44" t="s">
+        <v>398</v>
+      </c>
+      <c r="I117" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J117" s="45"/>
+      <c r="K117" s="45"/>
+    </row>
+    <row r="118" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F118" s="44" t="s">
+        <v>399</v>
+      </c>
+      <c r="G118" s="44" t="s">
+        <v>397</v>
+      </c>
+      <c r="H118" s="44" t="s">
+        <v>400</v>
+      </c>
+      <c r="I118" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J118" s="45"/>
+      <c r="K118" s="45"/>
+    </row>
+    <row r="119" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F119" s="44" t="s">
+        <v>401</v>
+      </c>
+      <c r="G119" s="44" t="s">
+        <v>397</v>
+      </c>
+      <c r="H119" s="44" t="s">
+        <v>402</v>
+      </c>
+      <c r="I119" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J119" s="45"/>
+      <c r="K119" s="45"/>
+    </row>
+    <row r="120" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F120" s="44" t="s">
+        <v>403</v>
+      </c>
+      <c r="G120" s="44" t="s">
+        <v>397</v>
+      </c>
+      <c r="H120" s="44" t="s">
+        <v>404</v>
+      </c>
+      <c r="I120" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J120" s="45"/>
+      <c r="K120" s="45"/>
+    </row>
+    <row r="121" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F121" s="44" t="s">
+        <v>405</v>
+      </c>
+      <c r="G121" s="44" t="s">
+        <v>397</v>
+      </c>
+      <c r="H121" s="44" t="s">
+        <v>406</v>
+      </c>
+      <c r="I121" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J121" s="45"/>
+      <c r="K121" s="45"/>
+    </row>
+    <row r="122" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F122" s="44" t="s">
+        <v>407</v>
+      </c>
+      <c r="G122" s="44" t="s">
+        <v>397</v>
+      </c>
+      <c r="H122" s="44" t="s">
+        <v>408</v>
+      </c>
+      <c r="I122" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J122" s="45"/>
+      <c r="K122" s="45"/>
+    </row>
+    <row r="123" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F123" s="44" t="s">
         <v>409</v>
       </c>
-      <c r="G117" s="46" t="s">
+      <c r="G123" s="44" t="s">
+        <v>397</v>
+      </c>
+      <c r="H123" s="44" t="s">
         <v>410</v>
       </c>
-      <c r="H117" s="46" t="s">
+      <c r="I123" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J123" s="45"/>
+      <c r="K123" s="45"/>
+    </row>
+    <row r="124" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F124" s="44" t="s">
         <v>411</v>
       </c>
-      <c r="I117" s="46" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="118" spans="6:12" x14ac:dyDescent="0.3">
-      <c r="F118" s="46" t="s">
+      <c r="G124" s="44" t="s">
+        <v>397</v>
+      </c>
+      <c r="H124" s="44" t="s">
         <v>412</v>
       </c>
-      <c r="G118" s="46" t="s">
-        <v>410</v>
-      </c>
-      <c r="H118" s="46" t="s">
+      <c r="I124" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J124" s="45"/>
+      <c r="K124" s="45"/>
+    </row>
+    <row r="125" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F125" s="44" t="s">
         <v>413</v>
       </c>
-      <c r="I118" s="46" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="119" spans="6:12" x14ac:dyDescent="0.3">
-      <c r="F119" s="46" t="s">
+      <c r="G125" s="44" t="s">
+        <v>397</v>
+      </c>
+      <c r="H125" s="44" t="s">
         <v>414</v>
       </c>
-      <c r="G119" s="46" t="s">
-        <v>410</v>
-      </c>
-      <c r="H119" s="46" t="s">
+      <c r="I125" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="J125" s="45"/>
+      <c r="K125" s="45"/>
+      <c r="L125" s="47" t="s">
         <v>415</v>
       </c>
-      <c r="I119" s="46" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="120" spans="6:12" x14ac:dyDescent="0.3">
-      <c r="F120" s="46" t="s">
+    </row>
+    <row r="126" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F126" s="44" t="s">
         <v>416</v>
       </c>
-      <c r="G120" s="46" t="s">
-        <v>410</v>
-      </c>
-      <c r="H120" s="46" t="s">
+      <c r="G126" s="44" t="s">
+        <v>397</v>
+      </c>
+      <c r="H126" s="44" t="s">
         <v>417</v>
       </c>
-      <c r="I120" s="46" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="121" spans="6:12" x14ac:dyDescent="0.3">
-      <c r="F121" s="46" t="s">
+      <c r="I126" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="J126" s="45"/>
+      <c r="K126" s="45"/>
+      <c r="L126" s="47" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="127" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F127" s="44" t="s">
         <v>418</v>
       </c>
-      <c r="G121" s="46" t="s">
-        <v>410</v>
-      </c>
-      <c r="H121" s="46" t="s">
+      <c r="G127" s="44" t="s">
+        <v>397</v>
+      </c>
+      <c r="H127" s="44" t="s">
         <v>419</v>
       </c>
-      <c r="I121" s="46" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="122" spans="6:12" x14ac:dyDescent="0.3">
-      <c r="F122" s="46" t="s">
-        <v>420</v>
-      </c>
-      <c r="G122" s="46" t="s">
-        <v>410</v>
-      </c>
-      <c r="H122" s="46" t="s">
-        <v>421</v>
-      </c>
-      <c r="I122" s="46" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="123" spans="6:12" x14ac:dyDescent="0.3">
-      <c r="F123" s="46" t="s">
+      <c r="I127" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="J127" s="45"/>
+      <c r="K127" s="45"/>
+      <c r="L127" s="47" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="128" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F128" s="45" t="s">
+        <v>423</v>
+      </c>
+      <c r="G128" s="45" t="s">
         <v>422</v>
       </c>
-      <c r="G123" s="46" t="s">
-        <v>410</v>
-      </c>
-      <c r="H123" s="46" t="s">
-        <v>423</v>
-      </c>
-      <c r="I123" s="46" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="124" spans="6:12" x14ac:dyDescent="0.3">
-      <c r="F124" s="46" t="s">
+      <c r="H128" s="45" t="s">
         <v>424</v>
       </c>
-      <c r="G124" s="46" t="s">
-        <v>410</v>
-      </c>
-      <c r="H124" s="46" t="s">
+      <c r="I128" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="J128" s="45"/>
+      <c r="K128" s="45"/>
+      <c r="L128" s="47" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="129" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F129" s="45" t="s">
         <v>425</v>
       </c>
-      <c r="I124" s="46" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="125" spans="6:12" x14ac:dyDescent="0.3">
-      <c r="F125" s="46" t="s">
+      <c r="G129" s="45" t="s">
+        <v>422</v>
+      </c>
+      <c r="H129" s="45" t="s">
         <v>426</v>
       </c>
-      <c r="G125" s="46" t="s">
-        <v>410</v>
-      </c>
-      <c r="H125" s="46" t="s">
+      <c r="I129" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J129" s="45"/>
+      <c r="K129" s="45"/>
+    </row>
+    <row r="130" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F130" s="45" t="s">
         <v>427</v>
       </c>
-      <c r="I125" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="L125" s="47" t="s">
+      <c r="G130" s="45" t="s">
+        <v>422</v>
+      </c>
+      <c r="H130" s="45" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="126" spans="6:12" x14ac:dyDescent="0.3">
-      <c r="F126" s="46" t="s">
+      <c r="I130" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J130" s="45"/>
+      <c r="K130" s="45"/>
+    </row>
+    <row r="131" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F131" s="45" t="s">
         <v>429</v>
       </c>
-      <c r="G126" s="46" t="s">
-        <v>410</v>
-      </c>
-      <c r="H126" s="46" t="s">
+      <c r="G131" s="45" t="s">
         <v>430</v>
       </c>
-      <c r="I126" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="L126" s="47" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="127" spans="6:12" x14ac:dyDescent="0.3">
-      <c r="F127" s="46" t="s">
+      <c r="H131" s="45" t="s">
         <v>431</v>
       </c>
-      <c r="G127" s="46" t="s">
-        <v>410</v>
-      </c>
-      <c r="H127" s="46" t="s">
+      <c r="I131" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="J131" s="45"/>
+      <c r="K131" s="45"/>
+      <c r="L131" s="47" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="132" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F132" s="45" t="s">
         <v>432</v>
       </c>
-      <c r="I127" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="L127" s="47" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="F128" t="s" s="57">
+      <c r="G132" s="45" t="s">
+        <v>430</v>
+      </c>
+      <c r="H132" s="45" t="s">
+        <v>433</v>
+      </c>
+      <c r="I132" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="J132" s="45"/>
+      <c r="K132" s="45"/>
+      <c r="L132" s="47" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="133" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F133" s="45" t="s">
+        <v>434</v>
+      </c>
+      <c r="G133" s="45" t="s">
+        <v>435</v>
+      </c>
+      <c r="H133" s="45" t="s">
+        <v>436</v>
+      </c>
+      <c r="I133" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J133" s="45"/>
+      <c r="K133" s="45"/>
+      <c r="L133" s="45"/>
+    </row>
+    <row r="134" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F134" s="45" t="s">
+        <v>437</v>
+      </c>
+      <c r="G134" s="45" t="s">
+        <v>435</v>
+      </c>
+      <c r="H134" s="45" t="s">
+        <v>438</v>
+      </c>
+      <c r="I134" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J134" s="45"/>
+      <c r="K134" s="45"/>
+      <c r="L134" s="45"/>
+    </row>
+    <row r="135" spans="6:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F135" s="45" t="s">
+        <v>439</v>
+      </c>
+      <c r="G135" s="45" t="s">
+        <v>435</v>
+      </c>
+      <c r="H135" s="45" t="s">
+        <v>440</v>
+      </c>
+      <c r="I135" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="J135" s="45"/>
+      <c r="K135" s="45"/>
+      <c r="L135" s="47" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="136" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F136" s="45" t="s">
         <v>442</v>
       </c>
-      <c r="G128" t="s" s="57">
-        <v>440</v>
-      </c>
-      <c r="H128" t="s" s="57">
+      <c r="G136" s="45" t="s">
+        <v>435</v>
+      </c>
+      <c r="H136" s="45" t="s">
         <v>443</v>
       </c>
-      <c r="I128" t="s" s="57">
-        <v>66</v>
-      </c>
-      <c r="L128" t="s" s="58">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="F129" t="s" s="59">
+      <c r="I136" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J136" s="45"/>
+      <c r="K136" s="45"/>
+      <c r="L136" s="45"/>
+    </row>
+    <row r="137" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F137" s="45" t="s">
         <v>444</v>
       </c>
-      <c r="G129" t="s" s="59">
-        <v>440</v>
-      </c>
-      <c r="H129" t="s" s="59">
+      <c r="G137" s="45" t="s">
+        <v>435</v>
+      </c>
+      <c r="H137" s="45" t="s">
         <v>445</v>
       </c>
-      <c r="I129" t="s" s="59">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="F130" t="s" s="63">
+      <c r="I137" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J137" s="45"/>
+      <c r="K137" s="45"/>
+      <c r="L137" s="45"/>
+    </row>
+    <row r="138" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F138" s="45" t="s">
+        <v>446</v>
+      </c>
+      <c r="G138" s="45" t="s">
+        <v>435</v>
+      </c>
+      <c r="H138" s="45" t="s">
+        <v>447</v>
+      </c>
+      <c r="I138" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J138" s="45"/>
+      <c r="K138" s="45"/>
+      <c r="L138" s="45"/>
+    </row>
+    <row r="139" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F139" s="45" t="s">
+        <v>448</v>
+      </c>
+      <c r="G139" s="45" t="s">
+        <v>435</v>
+      </c>
+      <c r="H139" s="45" t="s">
+        <v>449</v>
+      </c>
+      <c r="I139" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J139" s="45"/>
+      <c r="K139" s="45"/>
+      <c r="L139" s="45"/>
+    </row>
+    <row r="140" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F140" s="45" t="s">
+        <v>450</v>
+      </c>
+      <c r="G140" s="45" t="s">
+        <v>435</v>
+      </c>
+      <c r="H140" s="45" t="s">
         <v>451</v>
       </c>
-      <c r="G130" t="s" s="63">
-        <v>440</v>
-      </c>
-      <c r="H130" t="s" s="63">
+      <c r="I140" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J140" s="45"/>
+      <c r="K140" s="45"/>
+      <c r="L140" s="45"/>
+    </row>
+    <row r="141" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F141" s="45" t="s">
         <v>452</v>
       </c>
-      <c r="I130" t="s" s="63">
-        <v>72</v>
-      </c>
+      <c r="G141" s="45" t="s">
+        <v>435</v>
+      </c>
+      <c r="H141" s="45" t="s">
+        <v>453</v>
+      </c>
+      <c r="I141" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J141" s="45"/>
+      <c r="K141" s="45"/>
+      <c r="L141" s="45"/>
+    </row>
+    <row r="142" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F142" s="45" t="s">
+        <v>454</v>
+      </c>
+      <c r="G142" s="45" t="s">
+        <v>435</v>
+      </c>
+      <c r="H142" s="45" t="s">
+        <v>455</v>
+      </c>
+      <c r="I142" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J142" s="45"/>
+      <c r="K142" s="45"/>
+      <c r="L142" s="45"/>
+    </row>
+    <row r="143" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F143" s="45" t="s">
+        <v>456</v>
+      </c>
+      <c r="G143" s="45" t="s">
+        <v>435</v>
+      </c>
+      <c r="H143" s="45" t="s">
+        <v>457</v>
+      </c>
+      <c r="I143" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J143" s="45"/>
+      <c r="K143" s="45"/>
+      <c r="L143" s="45"/>
+    </row>
+    <row r="144" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F144" s="45" t="s">
+        <v>458</v>
+      </c>
+      <c r="G144" s="45" t="s">
+        <v>435</v>
+      </c>
+      <c r="H144" s="45" t="s">
+        <v>459</v>
+      </c>
+      <c r="I144" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J144" s="45"/>
+      <c r="K144" s="45"/>
+      <c r="L144" s="45"/>
+    </row>
+    <row r="145" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F145" s="45" t="s">
+        <v>460</v>
+      </c>
+      <c r="G145" s="45" t="s">
+        <v>461</v>
+      </c>
+      <c r="H145" s="45" t="s">
+        <v>462</v>
+      </c>
+      <c r="I145" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J145" s="45"/>
+      <c r="K145" s="45"/>
+      <c r="L145" s="45"/>
+    </row>
+    <row r="146" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F146" s="45" t="s">
+        <v>463</v>
+      </c>
+      <c r="G146" s="45" t="s">
+        <v>461</v>
+      </c>
+      <c r="H146" s="45" t="s">
+        <v>464</v>
+      </c>
+      <c r="I146" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J146" s="45"/>
+      <c r="K146" s="45"/>
+      <c r="L146" s="45"/>
+    </row>
+    <row r="147" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F147" s="45" t="s">
+        <v>465</v>
+      </c>
+      <c r="G147" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="H147" s="45" t="s">
+        <v>467</v>
+      </c>
+      <c r="I147" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="J147" s="45"/>
+      <c r="K147" s="45"/>
+      <c r="L147" s="47" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="148" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F148" s="45" t="s">
+        <v>468</v>
+      </c>
+      <c r="G148" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="H148" s="45" t="s">
+        <v>469</v>
+      </c>
+      <c r="I148" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="J148" s="45"/>
+      <c r="K148" s="45"/>
+      <c r="L148" s="47" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="149" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F149" s="45" t="s">
+        <v>470</v>
+      </c>
+      <c r="G149" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="H149" s="45" t="s">
+        <v>471</v>
+      </c>
+      <c r="I149" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="J149" s="45"/>
+      <c r="K149" s="45"/>
+      <c r="L149" s="47" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="150" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F150" s="45" t="s">
+        <v>472</v>
+      </c>
+      <c r="G150" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="H150" s="45" t="s">
+        <v>473</v>
+      </c>
+      <c r="I150" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="J150" s="45"/>
+      <c r="K150" s="45"/>
+      <c r="L150" s="47" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="151" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F151" s="45" t="s">
+        <v>474</v>
+      </c>
+      <c r="G151" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="H151" s="45" t="s">
+        <v>475</v>
+      </c>
+      <c r="I151" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="J151" s="45"/>
+      <c r="K151" s="45"/>
+      <c r="L151" s="47" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="152" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F152" s="45" t="s">
+        <v>476</v>
+      </c>
+      <c r="G152" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="H152" s="45" t="s">
+        <v>477</v>
+      </c>
+      <c r="I152" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J152" s="45"/>
+      <c r="K152" s="45"/>
+    </row>
+    <row r="153" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F153" s="45" t="s">
+        <v>478</v>
+      </c>
+      <c r="G153" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="H153" s="45" t="s">
+        <v>479</v>
+      </c>
+      <c r="I153" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="J153" s="45"/>
+      <c r="K153" s="45"/>
+      <c r="L153" s="47" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="154" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F154" s="45" t="s">
+        <v>481</v>
+      </c>
+      <c r="G154" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="H154" s="45" t="s">
+        <v>482</v>
+      </c>
+      <c r="I154" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J154" s="45"/>
+      <c r="K154" s="45"/>
+      <c r="L154" s="45"/>
+    </row>
+    <row r="155" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F155" s="45" t="s">
+        <v>483</v>
+      </c>
+      <c r="G155" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="H155" s="45" t="s">
+        <v>484</v>
+      </c>
+      <c r="I155" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J155" s="45"/>
+      <c r="K155" s="45"/>
+      <c r="L155" s="45"/>
+    </row>
+    <row r="156" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F156" s="45" t="s">
+        <v>485</v>
+      </c>
+      <c r="G156" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="H156" s="45" t="s">
+        <v>486</v>
+      </c>
+      <c r="I156" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J156" s="45"/>
+      <c r="K156" s="45"/>
+      <c r="L156" s="45"/>
+    </row>
+    <row r="157" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F157" s="45" t="s">
+        <v>487</v>
+      </c>
+      <c r="G157" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="H157" s="45" t="s">
+        <v>488</v>
+      </c>
+      <c r="I157" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J157" s="45"/>
+      <c r="K157" s="45"/>
+      <c r="L157" s="45"/>
+    </row>
+    <row r="158" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F158" s="45" t="s">
+        <v>490</v>
+      </c>
+      <c r="G158" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="H158" s="45" t="s">
+        <v>491</v>
+      </c>
+      <c r="I158" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J158" s="45"/>
+      <c r="K158" s="45"/>
+      <c r="L158" s="45"/>
+    </row>
+    <row r="159" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F159" s="45" t="s">
+        <v>492</v>
+      </c>
+      <c r="G159" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="H159" s="45" t="s">
+        <v>493</v>
+      </c>
+      <c r="I159" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J159" s="45"/>
+      <c r="K159" s="45"/>
+      <c r="L159" s="45"/>
+    </row>
+    <row r="160" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F160" s="45" t="s">
+        <v>494</v>
+      </c>
+      <c r="G160" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="H160" s="45" t="s">
+        <v>495</v>
+      </c>
+      <c r="I160" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J160" s="45"/>
+      <c r="K160" s="45"/>
+      <c r="L160" s="45"/>
+    </row>
+    <row r="161" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F161" s="45" t="s">
+        <v>496</v>
+      </c>
+      <c r="G161" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="H161" s="45" t="s">
+        <v>497</v>
+      </c>
+      <c r="I161" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J161" s="45"/>
+      <c r="K161" s="45"/>
+      <c r="L161" s="45"/>
+    </row>
+    <row r="162" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F162" s="45" t="s">
+        <v>498</v>
+      </c>
+      <c r="G162" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="H162" s="45" t="s">
+        <v>499</v>
+      </c>
+      <c r="I162" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J162" s="45"/>
+      <c r="K162" s="45"/>
+      <c r="L162" s="45"/>
+    </row>
+    <row r="163" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F163" s="45" t="s">
+        <v>503</v>
+      </c>
+      <c r="G163" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="H163" s="45" t="s">
+        <v>504</v>
+      </c>
+      <c r="I163" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J163" s="45"/>
+      <c r="K163" s="45"/>
+      <c r="L163" s="45"/>
+    </row>
+    <row r="164" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F164" s="45" t="s">
+        <v>505</v>
+      </c>
+      <c r="G164" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="H164" s="45" t="s">
+        <v>506</v>
+      </c>
+      <c r="I164" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="J164" s="45"/>
+      <c r="K164" s="45"/>
+      <c r="L164" s="47" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="165" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F165" s="45" t="s">
+        <v>508</v>
+      </c>
+      <c r="G165" s="45" t="s">
+        <v>509</v>
+      </c>
+      <c r="H165" s="45" t="s">
+        <v>510</v>
+      </c>
+      <c r="I165" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J165" s="45"/>
+      <c r="K165" s="45"/>
+      <c r="L165" s="45"/>
+    </row>
+    <row r="166" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F166" s="48" t="s">
+        <v>512</v>
+      </c>
+      <c r="G166" s="48" t="s">
+        <v>509</v>
+      </c>
+      <c r="H166" s="48" t="s">
+        <v>513</v>
+      </c>
+      <c r="I166" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="J166" s="48" t="s">
+        <v>511</v>
+      </c>
+      <c r="K166" s="48" t="s">
+        <v>466</v>
+      </c>
+      <c r="L166" s="45"/>
+    </row>
+    <row r="167" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F167" s="49" t="s">
+        <v>514</v>
+      </c>
+      <c r="G167" s="49" t="s">
+        <v>509</v>
+      </c>
+      <c r="H167" s="49" t="s">
+        <v>515</v>
+      </c>
+      <c r="I167" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="J167" s="50">
+        <v>2077089</v>
+      </c>
+      <c r="K167" s="48" t="s">
+        <v>516</v>
+      </c>
+      <c r="L167" s="45"/>
+    </row>
+    <row r="168" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F168" s="51" t="s">
+        <v>517</v>
+      </c>
+      <c r="G168" s="51" t="s">
+        <v>509</v>
+      </c>
+      <c r="H168" s="51" t="s">
+        <v>518</v>
+      </c>
+      <c r="I168" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="J168" s="45"/>
+      <c r="K168" s="45"/>
+      <c r="L168" s="45"/>
+    </row>
+    <row r="169" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F169" s="51" t="s">
+        <v>520</v>
+      </c>
+      <c r="G169" s="51" t="s">
+        <v>509</v>
+      </c>
+      <c r="H169" s="51" t="s">
+        <v>521</v>
+      </c>
+      <c r="I169" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="J169" s="51" t="s">
+        <v>519</v>
+      </c>
+      <c r="K169" s="51" t="s">
+        <v>509</v>
+      </c>
+      <c r="L169" s="45"/>
+    </row>
+    <row r="170" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F170" s="51" t="s">
+        <v>522</v>
+      </c>
+      <c r="G170" s="51" t="s">
+        <v>523</v>
+      </c>
+      <c r="H170" s="51" t="s">
+        <v>524</v>
+      </c>
+      <c r="I170" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="J170" s="51"/>
+      <c r="K170" s="45"/>
+      <c r="L170" s="45"/>
+    </row>
+    <row r="171" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F171" s="52" t="s">
+        <v>525</v>
+      </c>
+      <c r="G171" s="52" t="s">
+        <v>509</v>
+      </c>
+      <c r="H171" s="52" t="s">
+        <v>526</v>
+      </c>
+      <c r="I171" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="J171" s="45"/>
+      <c r="K171" s="45"/>
+      <c r="L171" s="45"/>
+    </row>
+    <row r="172" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F172" s="52" t="s">
+        <v>527</v>
+      </c>
+      <c r="G172" s="52" t="s">
+        <v>509</v>
+      </c>
+      <c r="H172" s="52" t="s">
+        <v>528</v>
+      </c>
+      <c r="I172" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="J172" s="45"/>
+      <c r="K172" s="45"/>
+      <c r="L172" s="45"/>
+    </row>
+    <row r="173" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F173" s="52" t="s">
+        <v>532</v>
+      </c>
+      <c r="G173" s="52" t="s">
+        <v>533</v>
+      </c>
+      <c r="H173" s="52" t="s">
+        <v>534</v>
+      </c>
+      <c r="I173" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="J173" s="45"/>
+      <c r="K173" s="45"/>
+      <c r="L173" s="45"/>
+    </row>
+    <row r="174" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F174" s="52" t="s">
+        <v>536</v>
+      </c>
+      <c r="G174" s="52" t="s">
+        <v>533</v>
+      </c>
+      <c r="H174" s="52" t="s">
+        <v>537</v>
+      </c>
+      <c r="I174" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="J174" s="52" t="s">
+        <v>535</v>
+      </c>
+      <c r="K174" s="52" t="s">
+        <v>533</v>
+      </c>
+      <c r="L174" s="45"/>
+    </row>
+    <row r="175" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F175" s="45"/>
+      <c r="G175" s="45"/>
+      <c r="H175" s="45"/>
+      <c r="I175" s="45"/>
+      <c r="J175" s="45"/>
+      <c r="K175" s="45"/>
+      <c r="L175" s="45"/>
+    </row>
+    <row r="176" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F176" s="45"/>
+      <c r="G176" s="45"/>
+      <c r="H176" s="45"/>
+      <c r="I176" s="45"/>
+      <c r="J176" s="45"/>
+      <c r="K176" s="45"/>
+      <c r="L176" s="45"/>
+    </row>
+    <row r="177" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F177" s="45"/>
+      <c r="G177" s="45"/>
+      <c r="H177" s="45"/>
+      <c r="I177" s="45"/>
+      <c r="J177" s="45"/>
+      <c r="K177" s="45"/>
+      <c r="L177" s="45"/>
+    </row>
+    <row r="178" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F178" s="45"/>
+      <c r="G178" s="45"/>
+      <c r="H178" s="45"/>
+      <c r="I178" s="45"/>
+      <c r="J178" s="45"/>
+      <c r="K178" s="45"/>
+      <c r="L178" s="45"/>
+    </row>
+    <row r="179" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F179" s="45"/>
+      <c r="G179" s="45"/>
+      <c r="H179" s="45"/>
+      <c r="I179" s="45"/>
+      <c r="J179" s="45"/>
+      <c r="K179" s="45"/>
+      <c r="L179" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5658,7 +6953,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70924E6C-D075-47E0-B0CB-3BEFA71EC108}">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="12.77734375"/>
@@ -5671,7 +6966,7 @@
     <col min="8" max="8" bestFit="true" customWidth="true" width="13.6640625"/>
     <col min="9" max="9" bestFit="true" customWidth="true" width="14.88671875"/>
     <col min="10" max="10" bestFit="true" customWidth="true" width="7.88671875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="9.77734375"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="10.33203125"/>
     <col min="12" max="12" customWidth="true" width="50.0"/>
   </cols>
   <sheetData>
@@ -5709,6 +7004,9 @@
       <c r="K1" s="42" t="s">
         <v>47</v>
       </c>
+      <c r="L1" s="19" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -5724,26 +7022,27 @@
         <v>39</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="F2" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" s="41" t="s">
-        <v>366</v>
-      </c>
-      <c r="H2" s="41" t="s">
-        <v>401</v>
-      </c>
-      <c r="I2" s="41" t="s">
-        <v>72</v>
-      </c>
-      <c r="J2" s="41" t="s">
-        <v>400</v>
-      </c>
-      <c r="K2" s="43" t="s">
-        <v>366</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="F2" s="52" t="s">
+        <v>520</v>
+      </c>
+      <c r="G2" s="52" t="s">
+        <v>509</v>
+      </c>
+      <c r="H2" s="52" t="s">
+        <v>521</v>
+      </c>
+      <c r="I2" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="J2" s="52" t="s">
+        <v>519</v>
+      </c>
+      <c r="K2" s="52" t="s">
+        <v>509</v>
+      </c>
+      <c r="L2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -5759,23 +7058,27 @@
         <v>39</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="F3" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="G3" s="41" t="s">
-        <v>366</v>
-      </c>
-      <c r="H3" s="41" t="s">
-        <v>397</v>
-      </c>
-      <c r="I3" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="44"/>
+        <v>421</v>
+      </c>
+      <c r="F3" s="52" t="s">
+        <v>530</v>
+      </c>
+      <c r="G3" s="52" t="s">
+        <v>509</v>
+      </c>
+      <c r="H3" s="52" t="s">
+        <v>531</v>
+      </c>
+      <c r="I3" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="J3" s="52" t="s">
+        <v>529</v>
+      </c>
+      <c r="K3" s="52" t="s">
+        <v>509</v>
+      </c>
+      <c r="L3" s="54"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
@@ -5791,25 +7094,31 @@
         <v>39</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="F4" s="41" t="s">
-        <v>74</v>
-      </c>
-      <c r="G4" s="41" t="s">
-        <v>366</v>
-      </c>
-      <c r="H4" s="41" t="s">
-        <v>398</v>
-      </c>
-      <c r="I4" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="44"/>
+        <v>420</v>
+      </c>
+      <c r="F4" s="52" t="s">
+        <v>536</v>
+      </c>
+      <c r="G4" s="52" t="s">
+        <v>533</v>
+      </c>
+      <c r="H4" s="52" t="s">
+        <v>537</v>
+      </c>
+      <c r="I4" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="J4" s="52" t="s">
+        <v>535</v>
+      </c>
+      <c r="K4" s="52" t="s">
+        <v>533</v>
+      </c>
+      <c r="L4" s="54"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="57"/>
+      <c r="B5" s="57"/>
       <c r="C5" s="2" t="s">
         <v>45</v>
       </c>
@@ -5817,25 +7126,31 @@
         <v>39</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="F5" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="G5" s="30" t="s">
-        <v>366</v>
-      </c>
-      <c r="H5" s="30" t="s">
-        <v>399</v>
-      </c>
-      <c r="I5" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
-      <c r="L5" s="44"/>
+        <v>421</v>
+      </c>
+      <c r="F5" s="53" t="s">
+        <v>539</v>
+      </c>
+      <c r="G5" s="53" t="s">
+        <v>533</v>
+      </c>
+      <c r="H5" s="53" t="s">
+        <v>540</v>
+      </c>
+      <c r="I5" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="J5" s="53" t="s">
+        <v>538</v>
+      </c>
+      <c r="K5" s="53" t="s">
+        <v>533</v>
+      </c>
+      <c r="L5" s="54"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="57"/>
+      <c r="B6" s="57"/>
       <c r="C6" s="2" t="s">
         <v>45</v>
       </c>
@@ -5843,28 +7158,31 @@
         <v>39</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="F6" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="G6" s="45" t="s">
-        <v>366</v>
-      </c>
-      <c r="H6" s="45" t="s">
-        <v>403</v>
-      </c>
-      <c r="I6" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="J6" s="45" t="s">
-        <v>402</v>
-      </c>
-      <c r="K6" s="45" t="s">
-        <v>366</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="F6" s="55" t="s">
+        <v>542</v>
+      </c>
+      <c r="G6" s="55" t="s">
+        <v>533</v>
+      </c>
+      <c r="H6" s="55" t="s">
+        <v>543</v>
+      </c>
+      <c r="I6" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="J6" s="55" t="s">
+        <v>541</v>
+      </c>
+      <c r="K6" s="55" t="s">
+        <v>533</v>
+      </c>
+      <c r="L6" s="53"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="57"/>
+      <c r="B7" s="57"/>
       <c r="C7" s="2" t="s">
         <v>45</v>
       </c>
@@ -5872,28 +7190,29 @@
         <v>39</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="F7" s="45" t="s">
-        <v>92</v>
-      </c>
-      <c r="G7" s="45" t="s">
-        <v>366</v>
-      </c>
-      <c r="H7" s="45" t="s">
-        <v>408</v>
-      </c>
-      <c r="I7" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="J7" s="45" t="s">
-        <v>407</v>
-      </c>
-      <c r="K7" s="45" t="s">
-        <v>366</v>
+        <v>421</v>
+      </c>
+      <c r="F7" s="57" t="s">
+        <v>544</v>
+      </c>
+      <c r="G7" s="57" t="s">
+        <v>533</v>
+      </c>
+      <c r="H7" s="57" t="s">
+        <v>545</v>
+      </c>
+      <c r="I7" s="57" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="43"/>
+      <c r="K7" s="43"/>
+      <c r="L7" s="58" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="57"/>
+      <c r="B8" s="57"/>
       <c r="C8" s="2" t="s">
         <v>45</v>
       </c>
@@ -5901,26 +7220,27 @@
         <v>39</v>
       </c>
       <c r="E8" s="1"/>
-      <c r="F8" s="56" t="s">
-        <v>95</v>
-      </c>
-      <c r="G8" s="56" t="s">
-        <v>440</v>
-      </c>
-      <c r="H8" s="56" t="s">
-        <v>441</v>
-      </c>
-      <c r="I8" s="56" t="s">
-        <v>72</v>
-      </c>
-      <c r="J8" s="55" t="s">
-        <v>439</v>
-      </c>
-      <c r="K8" s="55" t="s">
-        <v>440</v>
+      <c r="F8" s="57" t="s">
+        <v>546</v>
+      </c>
+      <c r="G8" s="57" t="s">
+        <v>533</v>
+      </c>
+      <c r="H8" s="57" t="s">
+        <v>547</v>
+      </c>
+      <c r="I8" s="57" t="s">
+        <v>66</v>
+      </c>
+      <c r="J8" s="45"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="58" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="57"/>
+      <c r="B9" s="57"/>
       <c r="C9" s="2" t="s">
         <v>45</v>
       </c>
@@ -5928,26 +7248,27 @@
         <v>39</v>
       </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="62" t="s">
-        <v>98</v>
-      </c>
-      <c r="G9" s="62" t="s">
-        <v>440</v>
-      </c>
-      <c r="H9" s="62" t="s">
-        <v>450</v>
-      </c>
-      <c r="I9" s="62" t="s">
-        <v>72</v>
-      </c>
-      <c r="J9" s="61" t="s">
-        <v>449</v>
-      </c>
-      <c r="K9" s="61" t="s">
-        <v>440</v>
+      <c r="F9" s="66" t="s">
+        <v>549</v>
+      </c>
+      <c r="G9" s="66" t="s">
+        <v>533</v>
+      </c>
+      <c r="H9" s="66" t="s">
+        <v>550</v>
+      </c>
+      <c r="I9" s="66" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" s="45"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="67" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="57"/>
+      <c r="B10" s="57"/>
       <c r="C10" s="2" t="s">
         <v>45</v>
       </c>
@@ -5961,8 +7282,11 @@
       <c r="I10" s="41"/>
       <c r="J10" s="41"/>
       <c r="K10" s="41"/>
+      <c r="L10" s="53"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="57"/>
+      <c r="B11" s="57"/>
       <c r="C11" s="2" t="s">
         <v>45</v>
       </c>
@@ -5976,8 +7300,11 @@
       <c r="I11" s="41"/>
       <c r="J11" s="41"/>
       <c r="K11" s="41"/>
+      <c r="L11" s="53"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="57"/>
+      <c r="B12" s="57"/>
       <c r="C12" s="2" t="s">
         <v>45</v>
       </c>
@@ -5991,8 +7318,11 @@
       <c r="I12" s="41"/>
       <c r="J12" s="41"/>
       <c r="K12" s="41"/>
+      <c r="L12" s="53"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="57"/>
+      <c r="B13" s="57"/>
       <c r="C13" s="2" t="s">
         <v>45</v>
       </c>
@@ -6006,8 +7336,11 @@
       <c r="I13" s="41"/>
       <c r="J13" s="41"/>
       <c r="K13" s="41"/>
+      <c r="L13" s="53"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="57"/>
+      <c r="B14" s="57"/>
       <c r="C14" s="2" t="s">
         <v>45</v>
       </c>
@@ -6021,8 +7354,11 @@
       <c r="I14" s="41"/>
       <c r="J14" s="41"/>
       <c r="K14" s="41"/>
+      <c r="L14" s="53"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="57"/>
+      <c r="B15" s="57"/>
       <c r="C15" s="2" t="s">
         <v>45</v>
       </c>
@@ -6036,23 +7372,247 @@
       <c r="I15" s="41"/>
       <c r="J15" s="41"/>
       <c r="K15" s="41"/>
+      <c r="L15" s="53"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C16" s="2" t="s">
+      <c r="A16" s="57"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="1"/>
+      <c r="E16" s="30"/>
       <c r="F16" s="41"/>
       <c r="G16" s="41"/>
       <c r="H16" s="41"/>
       <c r="I16" s="41"/>
       <c r="J16" s="41"/>
       <c r="K16" s="41"/>
+      <c r="L16" s="53"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="57"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="55"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
+      <c r="L17" s="56"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="57"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="57"/>
+      <c r="K18" s="57"/>
+      <c r="L18" s="57"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="57"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="57"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="57"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="57"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="57"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="57"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="57"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="57"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="57"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="57"/>
+      <c r="B23" s="57"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="57"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="57"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="57"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="57"/>
+      <c r="H24" s="57"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="57"/>
+      <c r="K24" s="57"/>
+      <c r="L24" s="57"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="57"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="57"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="57"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="57"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="57"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="57"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="57"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="57"/>
+      <c r="K28" s="57"/>
+      <c r="L28" s="57"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="57"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="57"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="57"/>
+      <c r="B30" s="57"/>
+      <c r="C30" s="57"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="57"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="57"/>
+      <c r="B31" s="57"/>
+      <c r="C31" s="57"/>
+      <c r="D31" s="57"/>
+      <c r="E31" s="57"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="57"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="57"/>
+      <c r="L31" s="57"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F32" s="57"/>
+      <c r="G32" s="57"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="57"/>
+      <c r="J32" s="57"/>
+      <c r="K32" s="57"/>
+      <c r="L32" s="57"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/test/resources/POC_data_sheet_v1.1.xlsx
+++ b/src/test/resources/POC_data_sheet_v1.1.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="597">
   <si>
     <t>Application</t>
   </si>
@@ -1695,6 +1695,144 @@
   </si>
   <si>
     <t>13:04:03</t>
+  </si>
+  <si>
+    <t>R173</t>
+  </si>
+  <si>
+    <t>08/14/2025</t>
+  </si>
+  <si>
+    <t>17:33:28</t>
+  </si>
+  <si>
+    <t>R174</t>
+  </si>
+  <si>
+    <t>17:34:50</t>
+  </si>
+  <si>
+    <t>R175</t>
+  </si>
+  <si>
+    <t>19:25:47</t>
+  </si>
+  <si>
+    <t>R176</t>
+  </si>
+  <si>
+    <t>19:26:30</t>
+  </si>
+  <si>
+    <t>R177</t>
+  </si>
+  <si>
+    <t>20:10:54</t>
+  </si>
+  <si>
+    <t>R178</t>
+  </si>
+  <si>
+    <t>20:11:15</t>
+  </si>
+  <si>
+    <t>R179</t>
+  </si>
+  <si>
+    <t>20:13:31</t>
+  </si>
+  <si>
+    <t>R180</t>
+  </si>
+  <si>
+    <t>20:13:53</t>
+  </si>
+  <si>
+    <t>R181</t>
+  </si>
+  <si>
+    <t>20:51:10</t>
+  </si>
+  <si>
+    <t>R182</t>
+  </si>
+  <si>
+    <t>20:51:30</t>
+  </si>
+  <si>
+    <t>R183</t>
+  </si>
+  <si>
+    <t>08/15/2025</t>
+  </si>
+  <si>
+    <t>10:06:14</t>
+  </si>
+  <si>
+    <t>Login was not successful for user: rahul.reddy917@outlook.com</t>
+  </si>
+  <si>
+    <t>R184</t>
+  </si>
+  <si>
+    <t>10:07:26</t>
+  </si>
+  <si>
+    <t>R185</t>
+  </si>
+  <si>
+    <t>10:59:53</t>
+  </si>
+  <si>
+    <t>R186</t>
+  </si>
+  <si>
+    <t>R187</t>
+  </si>
+  <si>
+    <t>11:25:29</t>
+  </si>
+  <si>
+    <t>R188</t>
+  </si>
+  <si>
+    <t>11:26:07</t>
+  </si>
+  <si>
+    <t>R189</t>
+  </si>
+  <si>
+    <t>11:27:50</t>
+  </si>
+  <si>
+    <t>R190</t>
+  </si>
+  <si>
+    <t>11:28:28</t>
+  </si>
+  <si>
+    <t>R191</t>
+  </si>
+  <si>
+    <t>11:50:10</t>
+  </si>
+  <si>
+    <t>R192</t>
+  </si>
+  <si>
+    <t>11:50:31</t>
+  </si>
+  <si>
+    <t>R193</t>
+  </si>
+  <si>
+    <t>12:00:15</t>
+  </si>
+  <si>
+    <t>R194</t>
+  </si>
+  <si>
+    <t>12:00:36</t>
   </si>
 </sst>
 </file>
@@ -2165,7 +2303,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2320,6 +2458,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true">
       <alignment wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3049,7 +3215,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{087D34EC-64B6-464A-B1FA-1B3B12C5A42D}">
-  <dimension ref="A1:L179"/>
+  <dimension ref="A1:L196"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="15.44140625"/>
@@ -6895,49 +7061,333 @@
       <c r="L174" s="45"/>
     </row>
     <row r="175" spans="6:12" x14ac:dyDescent="0.3">
-      <c r="F175" s="45"/>
-      <c r="G175" s="45"/>
-      <c r="H175" s="45"/>
-      <c r="I175" s="45"/>
+      <c r="F175" s="68" t="s">
+        <v>551</v>
+      </c>
+      <c r="G175" s="68" t="s">
+        <v>552</v>
+      </c>
+      <c r="H175" s="68" t="s">
+        <v>553</v>
+      </c>
+      <c r="I175" s="68" t="s">
+        <v>72</v>
+      </c>
       <c r="J175" s="45"/>
       <c r="K175" s="45"/>
       <c r="L175" s="45"/>
     </row>
     <row r="176" spans="6:12" x14ac:dyDescent="0.3">
-      <c r="F176" s="45"/>
-      <c r="G176" s="45"/>
-      <c r="H176" s="45"/>
-      <c r="I176" s="45"/>
+      <c r="F176" s="69" t="s">
+        <v>554</v>
+      </c>
+      <c r="G176" s="69" t="s">
+        <v>552</v>
+      </c>
+      <c r="H176" s="69" t="s">
+        <v>555</v>
+      </c>
+      <c r="I176" s="69" t="s">
+        <v>72</v>
+      </c>
       <c r="J176" s="45"/>
       <c r="K176" s="45"/>
       <c r="L176" s="45"/>
     </row>
     <row r="177" spans="6:12" x14ac:dyDescent="0.3">
-      <c r="F177" s="45"/>
-      <c r="G177" s="45"/>
-      <c r="H177" s="45"/>
-      <c r="I177" s="45"/>
+      <c r="F177" s="70" t="s">
+        <v>556</v>
+      </c>
+      <c r="G177" s="70" t="s">
+        <v>552</v>
+      </c>
+      <c r="H177" s="70" t="s">
+        <v>557</v>
+      </c>
+      <c r="I177" s="70" t="s">
+        <v>72</v>
+      </c>
       <c r="J177" s="45"/>
       <c r="K177" s="45"/>
       <c r="L177" s="45"/>
     </row>
     <row r="178" spans="6:12" x14ac:dyDescent="0.3">
-      <c r="F178" s="45"/>
-      <c r="G178" s="45"/>
-      <c r="H178" s="45"/>
-      <c r="I178" s="45"/>
+      <c r="F178" s="71" t="s">
+        <v>558</v>
+      </c>
+      <c r="G178" s="71" t="s">
+        <v>552</v>
+      </c>
+      <c r="H178" s="71" t="s">
+        <v>559</v>
+      </c>
+      <c r="I178" s="71" t="s">
+        <v>72</v>
+      </c>
       <c r="J178" s="45"/>
       <c r="K178" s="45"/>
       <c r="L178" s="45"/>
     </row>
     <row r="179" spans="6:12" x14ac:dyDescent="0.3">
-      <c r="F179" s="45"/>
-      <c r="G179" s="45"/>
-      <c r="H179" s="45"/>
-      <c r="I179" s="45"/>
+      <c r="F179" s="72" t="s">
+        <v>560</v>
+      </c>
+      <c r="G179" s="72" t="s">
+        <v>552</v>
+      </c>
+      <c r="H179" s="72" t="s">
+        <v>561</v>
+      </c>
+      <c r="I179" s="72" t="s">
+        <v>72</v>
+      </c>
       <c r="J179" s="45"/>
       <c r="K179" s="45"/>
       <c r="L179" s="45"/>
+    </row>
+    <row r="180">
+      <c r="F180" t="s" s="73">
+        <v>562</v>
+      </c>
+      <c r="G180" t="s" s="73">
+        <v>552</v>
+      </c>
+      <c r="H180" t="s" s="73">
+        <v>563</v>
+      </c>
+      <c r="I180" t="s" s="73">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="F181" t="s" s="74">
+        <v>564</v>
+      </c>
+      <c r="G181" t="s" s="74">
+        <v>552</v>
+      </c>
+      <c r="H181" t="s" s="74">
+        <v>565</v>
+      </c>
+      <c r="I181" t="s" s="74">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="F182" t="s" s="75">
+        <v>566</v>
+      </c>
+      <c r="G182" t="s" s="75">
+        <v>552</v>
+      </c>
+      <c r="H182" t="s" s="75">
+        <v>567</v>
+      </c>
+      <c r="I182" t="s" s="75">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="F183" t="s" s="76">
+        <v>568</v>
+      </c>
+      <c r="G183" t="s" s="76">
+        <v>552</v>
+      </c>
+      <c r="H183" t="s" s="76">
+        <v>569</v>
+      </c>
+      <c r="I183" t="s" s="76">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="F184" t="s" s="77">
+        <v>570</v>
+      </c>
+      <c r="G184" t="s" s="77">
+        <v>552</v>
+      </c>
+      <c r="H184" t="s" s="77">
+        <v>571</v>
+      </c>
+      <c r="I184" t="s" s="77">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="F185" t="s" s="78">
+        <v>572</v>
+      </c>
+      <c r="G185" t="s" s="78">
+        <v>573</v>
+      </c>
+      <c r="H185" t="s" s="78">
+        <v>574</v>
+      </c>
+      <c r="I185" t="s" s="78">
+        <v>66</v>
+      </c>
+      <c r="L185" t="s" s="79">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="F186" t="s" s="80">
+        <v>576</v>
+      </c>
+      <c r="G186" t="s" s="80">
+        <v>573</v>
+      </c>
+      <c r="H186" t="s" s="80">
+        <v>577</v>
+      </c>
+      <c r="I186" t="s" s="80">
+        <v>66</v>
+      </c>
+      <c r="L186" t="s" s="81">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="F187" t="s" s="82">
+        <v>578</v>
+      </c>
+      <c r="G187" t="s" s="82">
+        <v>573</v>
+      </c>
+      <c r="H187" t="s" s="82">
+        <v>579</v>
+      </c>
+      <c r="I187" t="s" s="82">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="F188" t="s" s="83">
+        <v>580</v>
+      </c>
+      <c r="G188" t="s" s="83">
+        <v>573</v>
+      </c>
+      <c r="H188" t="s" s="83">
+        <v>158</v>
+      </c>
+      <c r="I188" t="s" s="83">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="F189" t="s" s="84">
+        <v>581</v>
+      </c>
+      <c r="G189" t="s" s="84">
+        <v>573</v>
+      </c>
+      <c r="H189" t="s" s="84">
+        <v>582</v>
+      </c>
+      <c r="I189" t="s" s="84">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="F190" t="s" s="85">
+        <v>583</v>
+      </c>
+      <c r="G190" t="s" s="85">
+        <v>573</v>
+      </c>
+      <c r="H190" t="s" s="85">
+        <v>584</v>
+      </c>
+      <c r="I190" t="s" s="85">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="F191" t="s" s="86">
+        <v>585</v>
+      </c>
+      <c r="G191" t="s" s="86">
+        <v>573</v>
+      </c>
+      <c r="H191" t="s" s="86">
+        <v>586</v>
+      </c>
+      <c r="I191" t="s" s="86">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="F192" t="s" s="87">
+        <v>587</v>
+      </c>
+      <c r="G192" t="s" s="87">
+        <v>573</v>
+      </c>
+      <c r="H192" t="s" s="87">
+        <v>588</v>
+      </c>
+      <c r="I192" t="s" s="87">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="F193" t="s" s="88">
+        <v>589</v>
+      </c>
+      <c r="G193" t="s" s="88">
+        <v>573</v>
+      </c>
+      <c r="H193" t="s" s="88">
+        <v>590</v>
+      </c>
+      <c r="I193" t="s" s="88">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="F194" t="s" s="89">
+        <v>591</v>
+      </c>
+      <c r="G194" t="s" s="89">
+        <v>573</v>
+      </c>
+      <c r="H194" t="s" s="89">
+        <v>592</v>
+      </c>
+      <c r="I194" t="s" s="89">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="F195" t="s" s="90">
+        <v>593</v>
+      </c>
+      <c r="G195" t="s" s="90">
+        <v>573</v>
+      </c>
+      <c r="H195" t="s" s="90">
+        <v>594</v>
+      </c>
+      <c r="I195" t="s" s="90">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="F196" t="s" s="91">
+        <v>595</v>
+      </c>
+      <c r="G196" t="s" s="91">
+        <v>573</v>
+      </c>
+      <c r="H196" t="s" s="91">
+        <v>596</v>
+      </c>
+      <c r="I196" t="s" s="91">
+        <v>72</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/src/test/resources/POC_data_sheet_v1.1.xlsx
+++ b/src/test/resources/POC_data_sheet_v1.1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SPidugujothi\IdeaProjects\MyridiusUAF\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FEFE6FC-131A-4DB8-B7A3-756F36665478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2578436E-03F5-403D-BEE2-D5C465AEA0B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{08B05D20-EDEF-43CA-A5DF-998FB408C439}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{08B05D20-EDEF-43CA-A5DF-998FB408C439}"/>
   </bookViews>
   <sheets>
     <sheet name="Common_TestData" sheetId="2" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1609" uniqueCount="776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3427" uniqueCount="1087">
   <si>
     <t>Application</t>
   </si>
@@ -2370,12 +2370,946 @@
   </si>
   <si>
     <t>08:16:32</t>
+  </si>
+  <si>
+    <t>Demo Web Shop</t>
+  </si>
+  <si>
+    <t>Functional</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>Existing User</t>
+  </si>
+  <si>
+    <t>Valid Credentials</t>
+  </si>
+  <si>
+    <t>Ip4</t>
+  </si>
+  <si>
+    <t>Authentication</t>
+  </si>
+  <si>
+    <t>Test Product</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>12345</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Doe</t>
+  </si>
+  <si>
+    <t>john.doe@example.com</t>
+  </si>
+  <si>
+    <t>Los Angeles</t>
+  </si>
+  <si>
+    <t>123 Main St</t>
+  </si>
+  <si>
+    <t>1234567890</t>
+  </si>
+  <si>
+    <t>Regression</t>
+  </si>
+  <si>
+    <t>Logout</t>
+  </si>
+  <si>
+    <t>Successful Logout</t>
+  </si>
+  <si>
+    <t>Ip5</t>
+  </si>
+  <si>
+    <t>Session Management</t>
+  </si>
+  <si>
+    <t>Test Product 2</t>
+  </si>
+  <si>
+    <t>Ontario</t>
+  </si>
+  <si>
+    <t>M4B 1B5</t>
+  </si>
+  <si>
+    <t>Jane</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>jane.smith@example.com</t>
+  </si>
+  <si>
+    <t>Toronto</t>
+  </si>
+  <si>
+    <t>456 Elm St</t>
+  </si>
+  <si>
+    <t>9876543210</t>
+  </si>
+  <si>
+    <t>Smoke</t>
+  </si>
+  <si>
+    <t>Invalid Password</t>
+  </si>
+  <si>
+    <t>Ip6</t>
+  </si>
+  <si>
+    <t>Test Product 3</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>England</t>
+  </si>
+  <si>
+    <t>EC1A 1BB</t>
+  </si>
+  <si>
+    <t>Bob</t>
+  </si>
+  <si>
+    <t>Johnson</t>
+  </si>
+  <si>
+    <t>bob.johnson@example.com</t>
+  </si>
+  <si>
+    <t>London</t>
+  </si>
+  <si>
+    <t>789 Oak St</t>
+  </si>
+  <si>
+    <t>5551234567</t>
+  </si>
+  <si>
+    <t>Session Timeout</t>
+  </si>
+  <si>
+    <t>Ip7</t>
+  </si>
+  <si>
+    <t>Test Product 4</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>New South Wales</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>Alice</t>
+  </si>
+  <si>
+    <t>Williams</t>
+  </si>
+  <si>
+    <t>alice.williams@example.com</t>
+  </si>
+  <si>
+    <t>Sydney</t>
+  </si>
+  <si>
+    <t>901 Maple St</t>
+  </si>
+  <si>
+    <t>0987654321</t>
+  </si>
+  <si>
+    <t>Valid Credentials with Spaces</t>
+  </si>
+  <si>
+    <t>Ip8</t>
+  </si>
+  <si>
+    <t>Test Product 5</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Bavaria</t>
+  </si>
+  <si>
+    <t>80331</t>
+  </si>
+  <si>
+    <t>Mike</t>
+  </si>
+  <si>
+    <t>Brown</t>
+  </si>
+  <si>
+    <t>mike.brown@example.com</t>
+  </si>
+  <si>
+    <t>Munich</t>
+  </si>
+  <si>
+    <t>111 Pine St</t>
+  </si>
+  <si>
+    <t>Ip9</t>
+  </si>
+  <si>
+    <t>Apple iPhone 13</t>
+  </si>
+  <si>
+    <t>123-456-7890</t>
+  </si>
+  <si>
+    <t>Invalid Session</t>
+  </si>
+  <si>
+    <t>Ip10</t>
+  </si>
+  <si>
+    <t>Samsung TV</t>
+  </si>
+  <si>
+    <t>987-654-3210</t>
+  </si>
+  <si>
+    <t>Forgot Password</t>
+  </si>
+  <si>
+    <t>Ip11</t>
+  </si>
+  <si>
+    <t>Sony Laptop</t>
+  </si>
+  <si>
+    <t>EC2V 7EA</t>
+  </si>
+  <si>
+    <t>555-123-4567</t>
+  </si>
+  <si>
+    <t>Ip12</t>
+  </si>
+  <si>
+    <t>Nike Shoes</t>
+  </si>
+  <si>
+    <t>901-234-5678</t>
+  </si>
+  <si>
+    <t>Invalid Credentials</t>
+  </si>
+  <si>
+    <t>Ip13</t>
+  </si>
+  <si>
+    <t>Canon Camera</t>
+  </si>
+  <si>
+    <t>80799</t>
+  </si>
+  <si>
+    <t>111-222-3333</t>
+  </si>
+  <si>
+    <t>Ip14</t>
+  </si>
+  <si>
+    <t>HP Monitor</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Île-de-France</t>
+  </si>
+  <si>
+    <t>75001</t>
+  </si>
+  <si>
+    <t>Emma</t>
+  </si>
+  <si>
+    <t>Davis</t>
+  </si>
+  <si>
+    <t>emma.davis@example.com</t>
+  </si>
+  <si>
+    <t>Paris</t>
+  </si>
+  <si>
+    <t>222 Cedar St</t>
+  </si>
+  <si>
+    <t>444-555-6666</t>
+  </si>
+  <si>
+    <t>Ip15</t>
+  </si>
+  <si>
+    <t>94105</t>
+  </si>
+  <si>
+    <t>San Francisco</t>
+  </si>
+  <si>
+    <t>415-123-4567</t>
+  </si>
+  <si>
+    <t>Ip16</t>
+  </si>
+  <si>
+    <t>Samsung TV 4K</t>
+  </si>
+  <si>
+    <t>456 Queen St E</t>
+  </si>
+  <si>
+    <t>416-789-0123</t>
+  </si>
+  <si>
+    <t>Ip17</t>
+  </si>
+  <si>
+    <t>Sony PlayStation 5</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>michael.brown@example.com</t>
+  </si>
+  <si>
+    <t>789 Pitt St</t>
+  </si>
+  <si>
+    <t>02-123-4567</t>
+  </si>
+  <si>
+    <t>Ip18</t>
+  </si>
+  <si>
+    <t>Nintendo Switch</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
+    <t>Emily</t>
+  </si>
+  <si>
+    <t>emily.davis@example.com</t>
+  </si>
+  <si>
+    <t>123 Oxford St</t>
+  </si>
+  <si>
+    <t>020-123-4567</t>
+  </si>
+  <si>
+    <t>Ip19</t>
+  </si>
+  <si>
+    <t>Google Pixel 6</t>
+  </si>
+  <si>
+    <t>Sarah</t>
+  </si>
+  <si>
+    <t>Taylor</t>
+  </si>
+  <si>
+    <t>sarah.taylor@example.com</t>
+  </si>
+  <si>
+    <t>456 Lehelstr</t>
+  </si>
+  <si>
+    <t>089-123-4567</t>
+  </si>
+  <si>
+    <t>Ip20</t>
+  </si>
+  <si>
+    <t>Ip21</t>
+  </si>
+  <si>
+    <t>Ip22</t>
+  </si>
+  <si>
+    <t>Ip23</t>
+  </si>
+  <si>
+    <t>Ip24</t>
+  </si>
+  <si>
+    <t>234 Pine St</t>
+  </si>
+  <si>
+    <t>1112223333</t>
+  </si>
+  <si>
+    <t>User Session Management</t>
+  </si>
+  <si>
+    <t>Valid Logout</t>
+  </si>
+  <si>
+    <t>Ip25</t>
+  </si>
+  <si>
+    <t>Test Product A</t>
+  </si>
+  <si>
+    <t>90001</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Ip26</t>
+  </si>
+  <si>
+    <t>Test Product B</t>
+  </si>
+  <si>
+    <t>M5H 2N2</t>
+  </si>
+  <si>
+    <t>Ip27</t>
+  </si>
+  <si>
+    <t>Test Product C</t>
+  </si>
+  <si>
+    <t>SW1A 1AA</t>
+  </si>
+  <si>
+    <t>Ip28</t>
+  </si>
+  <si>
+    <t>Test Product D</t>
+  </si>
+  <si>
+    <t>321 Pine St</t>
+  </si>
+  <si>
+    <t>Ip29</t>
+  </si>
+  <si>
+    <t>Test Product E</t>
+  </si>
+  <si>
+    <t>Ip30</t>
+  </si>
+  <si>
+    <t>Ip31</t>
+  </si>
+  <si>
+    <t>Ip32</t>
+  </si>
+  <si>
+    <t>Ip33</t>
+  </si>
+  <si>
+    <t>Ip34</t>
+  </si>
+  <si>
+    <t>Ip35</t>
+  </si>
+  <si>
+    <t>Ip36</t>
+  </si>
+  <si>
+    <t>Ip37</t>
+  </si>
+  <si>
+    <t>Ip38</t>
+  </si>
+  <si>
+    <t>Ip39</t>
+  </si>
+  <si>
+    <t>Ip40</t>
+  </si>
+  <si>
+    <t>Ip41</t>
+  </si>
+  <si>
+    <t>Ip42</t>
+  </si>
+  <si>
+    <t>Ip43</t>
+  </si>
+  <si>
+    <t>Ip44</t>
+  </si>
+  <si>
+    <t>Ip45</t>
+  </si>
+  <si>
+    <t>Ip46</t>
+  </si>
+  <si>
+    <t>Ip47</t>
+  </si>
+  <si>
+    <t>Ip48</t>
+  </si>
+  <si>
+    <t>Ip49</t>
+  </si>
+  <si>
+    <t>Ip50</t>
+  </si>
+  <si>
+    <t>Ip51</t>
+  </si>
+  <si>
+    <t>Ip52</t>
+  </si>
+  <si>
+    <t>Ip53</t>
+  </si>
+  <si>
+    <t>Ip54</t>
+  </si>
+  <si>
+    <t>Ip55</t>
+  </si>
+  <si>
+    <t>Ip56</t>
+  </si>
+  <si>
+    <t>Ip57</t>
+  </si>
+  <si>
+    <t>Ip58</t>
+  </si>
+  <si>
+    <t>Ip59</t>
+  </si>
+  <si>
+    <t>User Login</t>
+  </si>
+  <si>
+    <t>Valid login with existing user</t>
+  </si>
+  <si>
+    <t>Login with correct credentials</t>
+  </si>
+  <si>
+    <t>Ip60</t>
+  </si>
+  <si>
+    <t>90210</t>
+  </si>
+  <si>
+    <t>emily.johnson@example.com</t>
+  </si>
+  <si>
+    <t>1234 Sunset Blvd</t>
+  </si>
+  <si>
+    <t>+1-310-555-0198</t>
+  </si>
+  <si>
+    <t>Login with incorrect password</t>
+  </si>
+  <si>
+    <t>Login fails with wrong password</t>
+  </si>
+  <si>
+    <t>Ip61</t>
+  </si>
+  <si>
+    <t>Oliver</t>
+  </si>
+  <si>
+    <t>oliver.smith@example.co.uk</t>
+  </si>
+  <si>
+    <t>221B Baker Street</t>
+  </si>
+  <si>
+    <t>+44-20-7946-0958</t>
+  </si>
+  <si>
+    <t>User Logout</t>
+  </si>
+  <si>
+    <t>Logout after successful login</t>
+  </si>
+  <si>
+    <t>User logs out from account page</t>
+  </si>
+  <si>
+    <t>Ip62</t>
+  </si>
+  <si>
+    <t>M5V 2T6</t>
+  </si>
+  <si>
+    <t>Sophie</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>sophie.martin@example.ca</t>
+  </si>
+  <si>
+    <t>56 King Street West</t>
+  </si>
+  <si>
+    <t>+1-416-555-0134</t>
+  </si>
+  <si>
+    <t>Session expires after inactivity</t>
+  </si>
+  <si>
+    <t>User is logged out after timeout</t>
+  </si>
+  <si>
+    <t>Ip63</t>
+  </si>
+  <si>
+    <t>Liam</t>
+  </si>
+  <si>
+    <t>liam.williams@example.com.au</t>
+  </si>
+  <si>
+    <t>789 George Street</t>
+  </si>
+  <si>
+    <t>+61-2-5550-1234</t>
+  </si>
+  <si>
+    <t>Login with locked account</t>
+  </si>
+  <si>
+    <t>Login fails for locked user</t>
+  </si>
+  <si>
+    <t>Ip64</t>
+  </si>
+  <si>
+    <t>Anna</t>
+  </si>
+  <si>
+    <t>Schmidt</t>
+  </si>
+  <si>
+    <t>anna.schmidt@example.de</t>
+  </si>
+  <si>
+    <t>12 Marienplatz</t>
+  </si>
+  <si>
+    <t>+49-89-555-1234</t>
+  </si>
+  <si>
+    <t>Ip65</t>
+  </si>
+  <si>
+    <t>Ip66</t>
+  </si>
+  <si>
+    <t>Ip67</t>
+  </si>
+  <si>
+    <t>Ip68</t>
+  </si>
+  <si>
+    <t>Ip69</t>
+  </si>
+  <si>
+    <t>User Authentication</t>
+  </si>
+  <si>
+    <t>Valid user login</t>
+  </si>
+  <si>
+    <t>Ip70</t>
+  </si>
+  <si>
+    <t>123 Market St</t>
+  </si>
+  <si>
+    <t>415-555-1234</t>
+  </si>
+  <si>
+    <t>Invalid password login</t>
+  </si>
+  <si>
+    <t>Ip71</t>
+  </si>
+  <si>
+    <t>10 Downing St</t>
+  </si>
+  <si>
+    <t>020 7946 0958</t>
+  </si>
+  <si>
+    <t>User logout</t>
+  </si>
+  <si>
+    <t>Ip72</t>
+  </si>
+  <si>
+    <t>250 Front St W</t>
+  </si>
+  <si>
+    <t>416-555-7890</t>
+  </si>
+  <si>
+    <t>Session timeout</t>
+  </si>
+  <si>
+    <t>Ip73</t>
+  </si>
+  <si>
+    <t>88 George St</t>
+  </si>
+  <si>
+    <t>02 9012 3456</t>
+  </si>
+  <si>
+    <t>Attempt login with locked user</t>
+  </si>
+  <si>
+    <t>Ip74</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Schneider</t>
+  </si>
+  <si>
+    <t>max.schneider@example.de</t>
+  </si>
+  <si>
+    <t>Marienplatz 1</t>
+  </si>
+  <si>
+    <t>089 123456</t>
+  </si>
+  <si>
+    <t>Ip75</t>
+  </si>
+  <si>
+    <t>123 Maple Ave</t>
+  </si>
+  <si>
+    <t>213-555-0198</t>
+  </si>
+  <si>
+    <t>Invalid password</t>
+  </si>
+  <si>
+    <t>Ip76</t>
+  </si>
+  <si>
+    <t>45 Queen St</t>
+  </si>
+  <si>
+    <t>User logs out after login</t>
+  </si>
+  <si>
+    <t>Logout from account page</t>
+  </si>
+  <si>
+    <t>Ip77</t>
+  </si>
+  <si>
+    <t>789 King St W</t>
+  </si>
+  <si>
+    <t>416-555-0123</t>
+  </si>
+  <si>
+    <t>Auto logout after timeout</t>
+  </si>
+  <si>
+    <t>Ip78</t>
+  </si>
+  <si>
+    <t>12 George St</t>
+  </si>
+  <si>
+    <t>Ip79</t>
+  </si>
+  <si>
+    <t>5 Ludwigstrasse</t>
+  </si>
+  <si>
+    <t>Ip80</t>
+  </si>
+  <si>
+    <t>Ip81</t>
+  </si>
+  <si>
+    <t>Ip82</t>
+  </si>
+  <si>
+    <t>Ip83</t>
+  </si>
+  <si>
+    <t>Ip84</t>
+  </si>
+  <si>
+    <t>Valid Login</t>
+  </si>
+  <si>
+    <t>Login with valid credentials</t>
+  </si>
+  <si>
+    <t>Ip85</t>
+  </si>
+  <si>
+    <t>Invalid Login</t>
+  </si>
+  <si>
+    <t>Ip86</t>
+  </si>
+  <si>
+    <t>Ip87</t>
+  </si>
+  <si>
+    <t>56 King Street W</t>
+  </si>
+  <si>
+    <t>416-555-0134</t>
+  </si>
+  <si>
+    <t>Ip88</t>
+  </si>
+  <si>
+    <t>89 George Street</t>
+  </si>
+  <si>
+    <t>Login attempt with locked user account</t>
+  </si>
+  <si>
+    <t>Ip89</t>
+  </si>
+  <si>
+    <t>089 1234567</t>
+  </si>
+  <si>
+    <t>Ip90</t>
+  </si>
+  <si>
+    <t>Ip91</t>
+  </si>
+  <si>
+    <t>Ip92</t>
+  </si>
+  <si>
+    <t>Ip93</t>
+  </si>
+  <si>
+    <t>Ip94</t>
+  </si>
+  <si>
+    <t>Ip95</t>
+  </si>
+  <si>
+    <t>415-555-0198</t>
+  </si>
+  <si>
+    <t>Ip96</t>
+  </si>
+  <si>
+    <t>Non-existent user</t>
+  </si>
+  <si>
+    <t>Login with unregistered email</t>
+  </si>
+  <si>
+    <t>Ip97</t>
+  </si>
+  <si>
+    <t>Lucas</t>
+  </si>
+  <si>
+    <t>lucas.martin@example.ca</t>
+  </si>
+  <si>
+    <t>250 King St W</t>
+  </si>
+  <si>
+    <t>Valid user logout</t>
+  </si>
+  <si>
+    <t>Ip98</t>
+  </si>
+  <si>
+    <t>sophie.williams@example.com.au</t>
+  </si>
+  <si>
+    <t>45 George St</t>
+  </si>
+  <si>
+    <t>Ip99</t>
+  </si>
+  <si>
+    <t>Ip100</t>
+  </si>
+  <si>
+    <t>Ip101</t>
+  </si>
+  <si>
+    <t>Ip102</t>
+  </si>
+  <si>
+    <t>Ip103</t>
+  </si>
+  <si>
+    <t>22 George St</t>
+  </si>
+  <si>
+    <t>Ip104</t>
+  </si>
+  <si>
+    <t>Müller</t>
+  </si>
+  <si>
+    <t>max.mueller@example.de</t>
+  </si>
+  <si>
+    <t>10 Marienplatz</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2451,7 +3385,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -2906,12 +3840,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <top style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3047,24 +4014,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -3088,6 +4037,45 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3426,58 +4414,58 @@
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" style="11" customWidth="1"/>
-    <col min="2" max="2" width="33.109375" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="6" max="6" width="20.109375" customWidth="1"/>
-    <col min="7" max="7" width="11.77734375" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" style="11" width="8.44140625"/>
+    <col min="2" max="2" customWidth="true" width="33.109375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="23.44140625"/>
+    <col min="4" max="4" customWidth="true" width="19.0"/>
+    <col min="6" max="6" customWidth="true" width="20.109375"/>
+    <col min="7" max="7" customWidth="true" width="11.77734375"/>
+    <col min="8" max="8" customWidth="true" width="13.33203125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="73" t="s">
+      <c r="B1" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="73" t="s">
+      <c r="C1" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="73" t="s">
+      <c r="D1" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="73" t="s">
+      <c r="E1" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="73" t="s">
+      <c r="F1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="74" t="s">
+      <c r="G1" s="68" t="s">
         <v>361</v>
       </c>
-      <c r="H1" s="74" t="s">
+      <c r="H1" s="68" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="77" t="s">
+      <c r="C2" s="71" t="s">
         <v>649</v>
       </c>
-      <c r="D2" s="77" t="s">
+      <c r="D2" s="71" t="s">
         <v>643</v>
       </c>
-      <c r="E2" s="71" t="s">
+      <c r="E2" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="71" t="s">
+      <c r="F2" s="65" t="s">
         <v>32</v>
       </c>
       <c r="G2" s="64" t="s">
@@ -3488,39 +4476,39 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="78" t="s">
+      <c r="C3" s="72" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="71" t="s">
+      <c r="D3" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="71" t="s">
+      <c r="E3" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="71"/>
+      <c r="F3" s="65"/>
       <c r="G3" s="64"/>
       <c r="H3" s="64"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="79" t="s">
+      <c r="A4" s="73" t="s">
         <v>729</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="71" t="s">
         <v>730</v>
       </c>
-      <c r="C4" s="77" t="s">
+      <c r="C4" s="71" t="s">
         <v>733</v>
       </c>
       <c r="D4" s="64" t="s">
         <v>732</v>
       </c>
-      <c r="E4" s="71" t="s">
+      <c r="E4" s="65" t="s">
         <v>31</v>
       </c>
       <c r="F4" s="64" t="s">
@@ -3545,60 +4533,60 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DBDDBCF-8BF7-4A20-A442-6B433E5992DA}">
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:R106"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.44140625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" style="6"/>
-    <col min="3" max="3" width="13.5546875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="26.21875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="40.21875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="7.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" style="6" customWidth="1"/>
-    <col min="8" max="8" width="12" style="6" customWidth="1"/>
-    <col min="9" max="9" width="29.21875" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.109375" style="6" customWidth="1"/>
-    <col min="12" max="12" width="7.6640625" style="6" customWidth="1"/>
-    <col min="13" max="13" width="15.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20" style="6" customWidth="1"/>
-    <col min="16" max="16" width="7.6640625" style="6" customWidth="1"/>
-    <col min="17" max="17" width="12.77734375" style="6" customWidth="1"/>
-    <col min="18" max="18" width="11" style="6" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.77734375" style="6" customWidth="1"/>
-    <col min="20" max="20" width="8.88671875" style="6"/>
-    <col min="21" max="21" width="21.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.21875" style="6" customWidth="1"/>
-    <col min="25" max="25" width="12.5546875" style="6" customWidth="1"/>
-    <col min="26" max="16384" width="8.88671875" style="6"/>
+    <col min="1" max="1" customWidth="true" style="6" width="16.44140625"/>
+    <col min="2" max="2" customWidth="true" style="6" width="14.0"/>
+    <col min="3" max="3" customWidth="true" style="6" width="17.77734375"/>
+    <col min="4" max="4" customWidth="true" style="6" width="26.21875"/>
+    <col min="5" max="5" customWidth="true" style="6" width="40.21875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="6" width="7.44140625"/>
+    <col min="7" max="7" customWidth="true" style="6" width="22.0"/>
+    <col min="8" max="8" customWidth="true" style="6" width="12.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="6" width="29.21875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="6" width="11.5546875"/>
+    <col min="11" max="11" customWidth="true" style="6" width="15.109375"/>
+    <col min="12" max="12" customWidth="true" style="6" width="15.21875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="6" width="15.77734375"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="6" width="15.109375"/>
+    <col min="15" max="15" customWidth="true" style="6" width="25.109375"/>
+    <col min="16" max="16" customWidth="true" style="6" width="14.77734375"/>
+    <col min="17" max="17" customWidth="true" style="6" width="14.6640625"/>
+    <col min="18" max="18" customWidth="true" style="6" width="16.33203125"/>
+    <col min="19" max="19" customWidth="true" style="6" width="12.77734375"/>
+    <col min="20" max="20" style="6" width="8.88671875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="6" width="21.77734375"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="6" width="13.6640625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="6" width="13.44140625"/>
+    <col min="24" max="24" customWidth="true" style="6" width="15.21875"/>
+    <col min="25" max="25" customWidth="true" style="6" width="12.5546875"/>
+    <col min="26" max="16384" style="6" width="8.88671875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="66" t="s">
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="66"/>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="67"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="76"/>
+      <c r="P1" s="76"/>
+      <c r="Q1" s="76"/>
+      <c r="R1" s="77"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
@@ -3822,6 +4810,5662 @@
       </c>
       <c r="R5" s="3">
         <v>2536588589</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" s="81" t="s">
+        <v>776</v>
+      </c>
+      <c r="B6" s="81" t="s">
+        <v>777</v>
+      </c>
+      <c r="C6" s="81" t="s">
+        <v>778</v>
+      </c>
+      <c r="D6" s="81" t="s">
+        <v>779</v>
+      </c>
+      <c r="E6" s="81" t="s">
+        <v>780</v>
+      </c>
+      <c r="F6" s="81" t="s">
+        <v>781</v>
+      </c>
+      <c r="G6" s="81" t="s">
+        <v>782</v>
+      </c>
+      <c r="H6" s="81" t="s">
+        <v>778</v>
+      </c>
+      <c r="I6" s="81" t="s">
+        <v>783</v>
+      </c>
+      <c r="J6" s="81" t="s">
+        <v>784</v>
+      </c>
+      <c r="K6" s="81" t="s">
+        <v>785</v>
+      </c>
+      <c r="L6" s="81" t="s">
+        <v>786</v>
+      </c>
+      <c r="M6" s="81" t="s">
+        <v>787</v>
+      </c>
+      <c r="N6" s="81" t="s">
+        <v>788</v>
+      </c>
+      <c r="O6" s="81" t="s">
+        <v>789</v>
+      </c>
+      <c r="P6" s="81" t="s">
+        <v>790</v>
+      </c>
+      <c r="Q6" s="81" t="s">
+        <v>791</v>
+      </c>
+      <c r="R6" s="81" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" s="81" t="s">
+        <v>776</v>
+      </c>
+      <c r="B7" s="81" t="s">
+        <v>793</v>
+      </c>
+      <c r="C7" s="81" t="s">
+        <v>794</v>
+      </c>
+      <c r="D7" s="81" t="s">
+        <v>779</v>
+      </c>
+      <c r="E7" s="81" t="s">
+        <v>795</v>
+      </c>
+      <c r="F7" s="81" t="s">
+        <v>796</v>
+      </c>
+      <c r="G7" s="81" t="s">
+        <v>797</v>
+      </c>
+      <c r="H7" s="81" t="s">
+        <v>794</v>
+      </c>
+      <c r="I7" s="81" t="s">
+        <v>798</v>
+      </c>
+      <c r="J7" s="81" t="s">
+        <v>78</v>
+      </c>
+      <c r="K7" s="81" t="s">
+        <v>799</v>
+      </c>
+      <c r="L7" s="81" t="s">
+        <v>800</v>
+      </c>
+      <c r="M7" s="81" t="s">
+        <v>801</v>
+      </c>
+      <c r="N7" s="81" t="s">
+        <v>802</v>
+      </c>
+      <c r="O7" s="81" t="s">
+        <v>803</v>
+      </c>
+      <c r="P7" s="81" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q7" s="81" t="s">
+        <v>805</v>
+      </c>
+      <c r="R7" s="81" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="81" t="s">
+        <v>776</v>
+      </c>
+      <c r="B8" s="81" t="s">
+        <v>807</v>
+      </c>
+      <c r="C8" s="81" t="s">
+        <v>778</v>
+      </c>
+      <c r="D8" s="81" t="s">
+        <v>779</v>
+      </c>
+      <c r="E8" s="81" t="s">
+        <v>808</v>
+      </c>
+      <c r="F8" s="81" t="s">
+        <v>809</v>
+      </c>
+      <c r="G8" s="81" t="s">
+        <v>782</v>
+      </c>
+      <c r="H8" s="81" t="s">
+        <v>778</v>
+      </c>
+      <c r="I8" s="81" t="s">
+        <v>810</v>
+      </c>
+      <c r="J8" s="81" t="s">
+        <v>811</v>
+      </c>
+      <c r="K8" s="81" t="s">
+        <v>812</v>
+      </c>
+      <c r="L8" s="81" t="s">
+        <v>813</v>
+      </c>
+      <c r="M8" s="81" t="s">
+        <v>814</v>
+      </c>
+      <c r="N8" s="81" t="s">
+        <v>815</v>
+      </c>
+      <c r="O8" s="81" t="s">
+        <v>816</v>
+      </c>
+      <c r="P8" s="81" t="s">
+        <v>817</v>
+      </c>
+      <c r="Q8" s="81" t="s">
+        <v>818</v>
+      </c>
+      <c r="R8" s="81" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="81" t="s">
+        <v>776</v>
+      </c>
+      <c r="B9" s="81" t="s">
+        <v>777</v>
+      </c>
+      <c r="C9" s="81" t="s">
+        <v>794</v>
+      </c>
+      <c r="D9" s="81" t="s">
+        <v>779</v>
+      </c>
+      <c r="E9" s="81" t="s">
+        <v>820</v>
+      </c>
+      <c r="F9" s="81" t="s">
+        <v>821</v>
+      </c>
+      <c r="G9" s="81" t="s">
+        <v>797</v>
+      </c>
+      <c r="H9" s="81" t="s">
+        <v>794</v>
+      </c>
+      <c r="I9" s="81" t="s">
+        <v>822</v>
+      </c>
+      <c r="J9" s="81" t="s">
+        <v>823</v>
+      </c>
+      <c r="K9" s="81" t="s">
+        <v>824</v>
+      </c>
+      <c r="L9" s="81" t="s">
+        <v>825</v>
+      </c>
+      <c r="M9" s="81" t="s">
+        <v>826</v>
+      </c>
+      <c r="N9" s="81" t="s">
+        <v>827</v>
+      </c>
+      <c r="O9" s="81" t="s">
+        <v>828</v>
+      </c>
+      <c r="P9" s="81" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q9" s="81" t="s">
+        <v>830</v>
+      </c>
+      <c r="R9" s="81" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="81" t="s">
+        <v>776</v>
+      </c>
+      <c r="B10" s="81" t="s">
+        <v>793</v>
+      </c>
+      <c r="C10" s="81" t="s">
+        <v>778</v>
+      </c>
+      <c r="D10" s="81" t="s">
+        <v>779</v>
+      </c>
+      <c r="E10" s="81" t="s">
+        <v>832</v>
+      </c>
+      <c r="F10" s="81" t="s">
+        <v>833</v>
+      </c>
+      <c r="G10" s="81" t="s">
+        <v>782</v>
+      </c>
+      <c r="H10" s="81" t="s">
+        <v>778</v>
+      </c>
+      <c r="I10" s="81" t="s">
+        <v>834</v>
+      </c>
+      <c r="J10" s="81" t="s">
+        <v>835</v>
+      </c>
+      <c r="K10" s="81" t="s">
+        <v>836</v>
+      </c>
+      <c r="L10" s="81" t="s">
+        <v>837</v>
+      </c>
+      <c r="M10" s="81" t="s">
+        <v>838</v>
+      </c>
+      <c r="N10" s="81" t="s">
+        <v>839</v>
+      </c>
+      <c r="O10" s="81" t="s">
+        <v>840</v>
+      </c>
+      <c r="P10" s="81" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q10" s="81" t="s">
+        <v>842</v>
+      </c>
+      <c r="R10" s="81" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="82" t="s">
+        <v>776</v>
+      </c>
+      <c r="B11" s="82" t="s">
+        <v>777</v>
+      </c>
+      <c r="C11" s="82" t="s">
+        <v>778</v>
+      </c>
+      <c r="D11" s="82" t="s">
+        <v>779</v>
+      </c>
+      <c r="E11" s="82" t="s">
+        <v>780</v>
+      </c>
+      <c r="F11" s="82" t="s">
+        <v>843</v>
+      </c>
+      <c r="G11" s="82" t="s">
+        <v>782</v>
+      </c>
+      <c r="H11" s="82" t="s">
+        <v>778</v>
+      </c>
+      <c r="I11" s="82" t="s">
+        <v>844</v>
+      </c>
+      <c r="J11" s="82" t="s">
+        <v>784</v>
+      </c>
+      <c r="K11" s="82" t="s">
+        <v>785</v>
+      </c>
+      <c r="L11" s="82" t="s">
+        <v>786</v>
+      </c>
+      <c r="M11" s="82" t="s">
+        <v>787</v>
+      </c>
+      <c r="N11" s="82" t="s">
+        <v>788</v>
+      </c>
+      <c r="O11" s="82" t="s">
+        <v>789</v>
+      </c>
+      <c r="P11" s="82" t="s">
+        <v>790</v>
+      </c>
+      <c r="Q11" s="82" t="s">
+        <v>791</v>
+      </c>
+      <c r="R11" s="82" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="82" t="s">
+        <v>776</v>
+      </c>
+      <c r="B12" s="82" t="s">
+        <v>793</v>
+      </c>
+      <c r="C12" s="82" t="s">
+        <v>794</v>
+      </c>
+      <c r="D12" s="82" t="s">
+        <v>779</v>
+      </c>
+      <c r="E12" s="82" t="s">
+        <v>846</v>
+      </c>
+      <c r="F12" s="82" t="s">
+        <v>847</v>
+      </c>
+      <c r="G12" s="82" t="s">
+        <v>797</v>
+      </c>
+      <c r="H12" s="82" t="s">
+        <v>794</v>
+      </c>
+      <c r="I12" s="82" t="s">
+        <v>848</v>
+      </c>
+      <c r="J12" s="82" t="s">
+        <v>78</v>
+      </c>
+      <c r="K12" s="82" t="s">
+        <v>799</v>
+      </c>
+      <c r="L12" s="82" t="s">
+        <v>800</v>
+      </c>
+      <c r="M12" s="82" t="s">
+        <v>801</v>
+      </c>
+      <c r="N12" s="82" t="s">
+        <v>802</v>
+      </c>
+      <c r="O12" s="82" t="s">
+        <v>803</v>
+      </c>
+      <c r="P12" s="82" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q12" s="82" t="s">
+        <v>805</v>
+      </c>
+      <c r="R12" s="82" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="82" t="s">
+        <v>776</v>
+      </c>
+      <c r="B13" s="82" t="s">
+        <v>777</v>
+      </c>
+      <c r="C13" s="82" t="s">
+        <v>778</v>
+      </c>
+      <c r="D13" s="82" t="s">
+        <v>779</v>
+      </c>
+      <c r="E13" s="82" t="s">
+        <v>850</v>
+      </c>
+      <c r="F13" s="82" t="s">
+        <v>851</v>
+      </c>
+      <c r="G13" s="82" t="s">
+        <v>782</v>
+      </c>
+      <c r="H13" s="82" t="s">
+        <v>778</v>
+      </c>
+      <c r="I13" s="82" t="s">
+        <v>852</v>
+      </c>
+      <c r="J13" s="82" t="s">
+        <v>811</v>
+      </c>
+      <c r="K13" s="82" t="s">
+        <v>812</v>
+      </c>
+      <c r="L13" s="82" t="s">
+        <v>853</v>
+      </c>
+      <c r="M13" s="82" t="s">
+        <v>814</v>
+      </c>
+      <c r="N13" s="82" t="s">
+        <v>815</v>
+      </c>
+      <c r="O13" s="82" t="s">
+        <v>816</v>
+      </c>
+      <c r="P13" s="82" t="s">
+        <v>817</v>
+      </c>
+      <c r="Q13" s="82" t="s">
+        <v>818</v>
+      </c>
+      <c r="R13" s="82" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="82" t="s">
+        <v>776</v>
+      </c>
+      <c r="B14" s="82" t="s">
+        <v>793</v>
+      </c>
+      <c r="C14" s="82" t="s">
+        <v>794</v>
+      </c>
+      <c r="D14" s="82" t="s">
+        <v>779</v>
+      </c>
+      <c r="E14" s="82" t="s">
+        <v>820</v>
+      </c>
+      <c r="F14" s="82" t="s">
+        <v>855</v>
+      </c>
+      <c r="G14" s="82" t="s">
+        <v>797</v>
+      </c>
+      <c r="H14" s="82" t="s">
+        <v>794</v>
+      </c>
+      <c r="I14" s="82" t="s">
+        <v>856</v>
+      </c>
+      <c r="J14" s="82" t="s">
+        <v>823</v>
+      </c>
+      <c r="K14" s="82" t="s">
+        <v>824</v>
+      </c>
+      <c r="L14" s="82" t="s">
+        <v>825</v>
+      </c>
+      <c r="M14" s="82" t="s">
+        <v>826</v>
+      </c>
+      <c r="N14" s="82" t="s">
+        <v>827</v>
+      </c>
+      <c r="O14" s="82" t="s">
+        <v>828</v>
+      </c>
+      <c r="P14" s="82" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q14" s="82" t="s">
+        <v>830</v>
+      </c>
+      <c r="R14" s="82" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="82" t="s">
+        <v>776</v>
+      </c>
+      <c r="B15" s="82" t="s">
+        <v>777</v>
+      </c>
+      <c r="C15" s="82" t="s">
+        <v>778</v>
+      </c>
+      <c r="D15" s="82" t="s">
+        <v>779</v>
+      </c>
+      <c r="E15" s="82" t="s">
+        <v>858</v>
+      </c>
+      <c r="F15" s="82" t="s">
+        <v>859</v>
+      </c>
+      <c r="G15" s="82" t="s">
+        <v>782</v>
+      </c>
+      <c r="H15" s="82" t="s">
+        <v>778</v>
+      </c>
+      <c r="I15" s="82" t="s">
+        <v>860</v>
+      </c>
+      <c r="J15" s="82" t="s">
+        <v>835</v>
+      </c>
+      <c r="K15" s="82" t="s">
+        <v>836</v>
+      </c>
+      <c r="L15" s="82" t="s">
+        <v>861</v>
+      </c>
+      <c r="M15" s="82" t="s">
+        <v>838</v>
+      </c>
+      <c r="N15" s="82" t="s">
+        <v>839</v>
+      </c>
+      <c r="O15" s="82" t="s">
+        <v>840</v>
+      </c>
+      <c r="P15" s="82" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q15" s="82" t="s">
+        <v>842</v>
+      </c>
+      <c r="R15" s="82" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="82" t="s">
+        <v>776</v>
+      </c>
+      <c r="B16" s="82" t="s">
+        <v>793</v>
+      </c>
+      <c r="C16" s="82" t="s">
+        <v>794</v>
+      </c>
+      <c r="D16" s="82" t="s">
+        <v>779</v>
+      </c>
+      <c r="E16" s="82" t="s">
+        <v>846</v>
+      </c>
+      <c r="F16" s="82" t="s">
+        <v>863</v>
+      </c>
+      <c r="G16" s="82" t="s">
+        <v>797</v>
+      </c>
+      <c r="H16" s="82" t="s">
+        <v>794</v>
+      </c>
+      <c r="I16" s="82" t="s">
+        <v>864</v>
+      </c>
+      <c r="J16" s="82" t="s">
+        <v>865</v>
+      </c>
+      <c r="K16" s="82" t="s">
+        <v>866</v>
+      </c>
+      <c r="L16" s="82" t="s">
+        <v>867</v>
+      </c>
+      <c r="M16" s="82" t="s">
+        <v>868</v>
+      </c>
+      <c r="N16" s="82" t="s">
+        <v>869</v>
+      </c>
+      <c r="O16" s="82" t="s">
+        <v>870</v>
+      </c>
+      <c r="P16" s="82" t="s">
+        <v>871</v>
+      </c>
+      <c r="Q16" s="82" t="s">
+        <v>872</v>
+      </c>
+      <c r="R16" s="82" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="83" t="s">
+        <v>776</v>
+      </c>
+      <c r="B17" s="83" t="s">
+        <v>777</v>
+      </c>
+      <c r="C17" s="83" t="s">
+        <v>778</v>
+      </c>
+      <c r="D17" s="83" t="s">
+        <v>779</v>
+      </c>
+      <c r="E17" s="83" t="s">
+        <v>780</v>
+      </c>
+      <c r="F17" s="83" t="s">
+        <v>874</v>
+      </c>
+      <c r="G17" s="83" t="s">
+        <v>782</v>
+      </c>
+      <c r="H17" s="83" t="s">
+        <v>778</v>
+      </c>
+      <c r="I17" s="83" t="s">
+        <v>844</v>
+      </c>
+      <c r="J17" s="83" t="s">
+        <v>784</v>
+      </c>
+      <c r="K17" s="83" t="s">
+        <v>785</v>
+      </c>
+      <c r="L17" s="83" t="s">
+        <v>875</v>
+      </c>
+      <c r="M17" s="83" t="s">
+        <v>787</v>
+      </c>
+      <c r="N17" s="83" t="s">
+        <v>788</v>
+      </c>
+      <c r="O17" s="83" t="s">
+        <v>789</v>
+      </c>
+      <c r="P17" s="83" t="s">
+        <v>876</v>
+      </c>
+      <c r="Q17" s="83" t="s">
+        <v>791</v>
+      </c>
+      <c r="R17" s="83" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="83" t="s">
+        <v>776</v>
+      </c>
+      <c r="B18" s="83" t="s">
+        <v>793</v>
+      </c>
+      <c r="C18" s="83" t="s">
+        <v>794</v>
+      </c>
+      <c r="D18" s="83" t="s">
+        <v>779</v>
+      </c>
+      <c r="E18" s="83" t="s">
+        <v>795</v>
+      </c>
+      <c r="F18" s="83" t="s">
+        <v>878</v>
+      </c>
+      <c r="G18" s="83" t="s">
+        <v>797</v>
+      </c>
+      <c r="H18" s="83" t="s">
+        <v>794</v>
+      </c>
+      <c r="I18" s="83" t="s">
+        <v>879</v>
+      </c>
+      <c r="J18" s="83" t="s">
+        <v>78</v>
+      </c>
+      <c r="K18" s="83" t="s">
+        <v>799</v>
+      </c>
+      <c r="L18" s="83" t="s">
+        <v>800</v>
+      </c>
+      <c r="M18" s="83" t="s">
+        <v>801</v>
+      </c>
+      <c r="N18" s="83" t="s">
+        <v>802</v>
+      </c>
+      <c r="O18" s="83" t="s">
+        <v>803</v>
+      </c>
+      <c r="P18" s="83" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q18" s="83" t="s">
+        <v>880</v>
+      </c>
+      <c r="R18" s="83" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="83" t="s">
+        <v>776</v>
+      </c>
+      <c r="B19" s="83" t="s">
+        <v>807</v>
+      </c>
+      <c r="C19" s="83" t="s">
+        <v>778</v>
+      </c>
+      <c r="D19" s="83" t="s">
+        <v>779</v>
+      </c>
+      <c r="E19" s="83" t="s">
+        <v>808</v>
+      </c>
+      <c r="F19" s="83" t="s">
+        <v>882</v>
+      </c>
+      <c r="G19" s="83" t="s">
+        <v>782</v>
+      </c>
+      <c r="H19" s="83" t="s">
+        <v>778</v>
+      </c>
+      <c r="I19" s="83" t="s">
+        <v>883</v>
+      </c>
+      <c r="J19" s="83" t="s">
+        <v>823</v>
+      </c>
+      <c r="K19" s="83" t="s">
+        <v>824</v>
+      </c>
+      <c r="L19" s="83" t="s">
+        <v>825</v>
+      </c>
+      <c r="M19" s="83" t="s">
+        <v>884</v>
+      </c>
+      <c r="N19" s="83" t="s">
+        <v>839</v>
+      </c>
+      <c r="O19" s="83" t="s">
+        <v>885</v>
+      </c>
+      <c r="P19" s="83" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q19" s="83" t="s">
+        <v>886</v>
+      </c>
+      <c r="R19" s="83" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="83" t="s">
+        <v>776</v>
+      </c>
+      <c r="B20" s="83" t="s">
+        <v>793</v>
+      </c>
+      <c r="C20" s="83" t="s">
+        <v>794</v>
+      </c>
+      <c r="D20" s="83" t="s">
+        <v>779</v>
+      </c>
+      <c r="E20" s="83" t="s">
+        <v>820</v>
+      </c>
+      <c r="F20" s="83" t="s">
+        <v>888</v>
+      </c>
+      <c r="G20" s="83" t="s">
+        <v>797</v>
+      </c>
+      <c r="H20" s="83" t="s">
+        <v>794</v>
+      </c>
+      <c r="I20" s="83" t="s">
+        <v>889</v>
+      </c>
+      <c r="J20" s="83" t="s">
+        <v>890</v>
+      </c>
+      <c r="K20" s="83" t="s">
+        <v>812</v>
+      </c>
+      <c r="L20" s="83" t="s">
+        <v>853</v>
+      </c>
+      <c r="M20" s="83" t="s">
+        <v>891</v>
+      </c>
+      <c r="N20" s="83" t="s">
+        <v>869</v>
+      </c>
+      <c r="O20" s="83" t="s">
+        <v>892</v>
+      </c>
+      <c r="P20" s="83" t="s">
+        <v>817</v>
+      </c>
+      <c r="Q20" s="83" t="s">
+        <v>893</v>
+      </c>
+      <c r="R20" s="83" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="83" t="s">
+        <v>776</v>
+      </c>
+      <c r="B21" s="83" t="s">
+        <v>777</v>
+      </c>
+      <c r="C21" s="83" t="s">
+        <v>778</v>
+      </c>
+      <c r="D21" s="83" t="s">
+        <v>779</v>
+      </c>
+      <c r="E21" s="83" t="s">
+        <v>850</v>
+      </c>
+      <c r="F21" s="83" t="s">
+        <v>895</v>
+      </c>
+      <c r="G21" s="83" t="s">
+        <v>782</v>
+      </c>
+      <c r="H21" s="83" t="s">
+        <v>778</v>
+      </c>
+      <c r="I21" s="83" t="s">
+        <v>896</v>
+      </c>
+      <c r="J21" s="83" t="s">
+        <v>835</v>
+      </c>
+      <c r="K21" s="83" t="s">
+        <v>836</v>
+      </c>
+      <c r="L21" s="83" t="s">
+        <v>837</v>
+      </c>
+      <c r="M21" s="83" t="s">
+        <v>897</v>
+      </c>
+      <c r="N21" s="83" t="s">
+        <v>898</v>
+      </c>
+      <c r="O21" s="83" t="s">
+        <v>899</v>
+      </c>
+      <c r="P21" s="83" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q21" s="83" t="s">
+        <v>900</v>
+      </c>
+      <c r="R21" s="83" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="84" t="s">
+        <v>776</v>
+      </c>
+      <c r="B22" s="84" t="s">
+        <v>777</v>
+      </c>
+      <c r="C22" s="84" t="s">
+        <v>778</v>
+      </c>
+      <c r="D22" s="84" t="s">
+        <v>779</v>
+      </c>
+      <c r="E22" s="84" t="s">
+        <v>780</v>
+      </c>
+      <c r="F22" s="84" t="s">
+        <v>902</v>
+      </c>
+      <c r="G22" s="84" t="s">
+        <v>782</v>
+      </c>
+      <c r="H22" s="84" t="s">
+        <v>778</v>
+      </c>
+      <c r="I22" s="84" t="s">
+        <v>783</v>
+      </c>
+      <c r="J22" s="84" t="s">
+        <v>784</v>
+      </c>
+      <c r="K22" s="84" t="s">
+        <v>785</v>
+      </c>
+      <c r="L22" s="84" t="s">
+        <v>786</v>
+      </c>
+      <c r="M22" s="84" t="s">
+        <v>787</v>
+      </c>
+      <c r="N22" s="84" t="s">
+        <v>788</v>
+      </c>
+      <c r="O22" s="84" t="s">
+        <v>789</v>
+      </c>
+      <c r="P22" s="84" t="s">
+        <v>790</v>
+      </c>
+      <c r="Q22" s="84" t="s">
+        <v>791</v>
+      </c>
+      <c r="R22" s="84" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="84" t="s">
+        <v>776</v>
+      </c>
+      <c r="B23" s="84" t="s">
+        <v>777</v>
+      </c>
+      <c r="C23" s="84" t="s">
+        <v>794</v>
+      </c>
+      <c r="D23" s="84" t="s">
+        <v>779</v>
+      </c>
+      <c r="E23" s="84" t="s">
+        <v>795</v>
+      </c>
+      <c r="F23" s="84" t="s">
+        <v>903</v>
+      </c>
+      <c r="G23" s="84" t="s">
+        <v>797</v>
+      </c>
+      <c r="H23" s="84" t="s">
+        <v>794</v>
+      </c>
+      <c r="I23" s="84" t="s">
+        <v>798</v>
+      </c>
+      <c r="J23" s="84" t="s">
+        <v>78</v>
+      </c>
+      <c r="K23" s="84" t="s">
+        <v>799</v>
+      </c>
+      <c r="L23" s="84" t="s">
+        <v>800</v>
+      </c>
+      <c r="M23" s="84" t="s">
+        <v>801</v>
+      </c>
+      <c r="N23" s="84" t="s">
+        <v>802</v>
+      </c>
+      <c r="O23" s="84" t="s">
+        <v>803</v>
+      </c>
+      <c r="P23" s="84" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q23" s="84" t="s">
+        <v>805</v>
+      </c>
+      <c r="R23" s="84" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="84" t="s">
+        <v>776</v>
+      </c>
+      <c r="B24" s="84" t="s">
+        <v>777</v>
+      </c>
+      <c r="C24" s="84" t="s">
+        <v>778</v>
+      </c>
+      <c r="D24" s="84" t="s">
+        <v>779</v>
+      </c>
+      <c r="E24" s="84" t="s">
+        <v>808</v>
+      </c>
+      <c r="F24" s="84" t="s">
+        <v>904</v>
+      </c>
+      <c r="G24" s="84" t="s">
+        <v>782</v>
+      </c>
+      <c r="H24" s="84" t="s">
+        <v>778</v>
+      </c>
+      <c r="I24" s="84" t="s">
+        <v>810</v>
+      </c>
+      <c r="J24" s="84" t="s">
+        <v>811</v>
+      </c>
+      <c r="K24" s="84" t="s">
+        <v>812</v>
+      </c>
+      <c r="L24" s="84" t="s">
+        <v>813</v>
+      </c>
+      <c r="M24" s="84" t="s">
+        <v>814</v>
+      </c>
+      <c r="N24" s="84" t="s">
+        <v>815</v>
+      </c>
+      <c r="O24" s="84" t="s">
+        <v>816</v>
+      </c>
+      <c r="P24" s="84" t="s">
+        <v>817</v>
+      </c>
+      <c r="Q24" s="84" t="s">
+        <v>818</v>
+      </c>
+      <c r="R24" s="84" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="84" t="s">
+        <v>776</v>
+      </c>
+      <c r="B25" s="84" t="s">
+        <v>777</v>
+      </c>
+      <c r="C25" s="84" t="s">
+        <v>794</v>
+      </c>
+      <c r="D25" s="84" t="s">
+        <v>779</v>
+      </c>
+      <c r="E25" s="84" t="s">
+        <v>820</v>
+      </c>
+      <c r="F25" s="84" t="s">
+        <v>905</v>
+      </c>
+      <c r="G25" s="84" t="s">
+        <v>797</v>
+      </c>
+      <c r="H25" s="84" t="s">
+        <v>794</v>
+      </c>
+      <c r="I25" s="84" t="s">
+        <v>822</v>
+      </c>
+      <c r="J25" s="84" t="s">
+        <v>823</v>
+      </c>
+      <c r="K25" s="84" t="s">
+        <v>824</v>
+      </c>
+      <c r="L25" s="84" t="s">
+        <v>825</v>
+      </c>
+      <c r="M25" s="84" t="s">
+        <v>826</v>
+      </c>
+      <c r="N25" s="84" t="s">
+        <v>827</v>
+      </c>
+      <c r="O25" s="84" t="s">
+        <v>828</v>
+      </c>
+      <c r="P25" s="84" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q25" s="84" t="s">
+        <v>830</v>
+      </c>
+      <c r="R25" s="84" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="84" t="s">
+        <v>776</v>
+      </c>
+      <c r="B26" s="84" t="s">
+        <v>777</v>
+      </c>
+      <c r="C26" s="84" t="s">
+        <v>778</v>
+      </c>
+      <c r="D26" s="84" t="s">
+        <v>779</v>
+      </c>
+      <c r="E26" s="84" t="s">
+        <v>832</v>
+      </c>
+      <c r="F26" s="84" t="s">
+        <v>906</v>
+      </c>
+      <c r="G26" s="84" t="s">
+        <v>782</v>
+      </c>
+      <c r="H26" s="84" t="s">
+        <v>778</v>
+      </c>
+      <c r="I26" s="84" t="s">
+        <v>834</v>
+      </c>
+      <c r="J26" s="84" t="s">
+        <v>835</v>
+      </c>
+      <c r="K26" s="84" t="s">
+        <v>836</v>
+      </c>
+      <c r="L26" s="84" t="s">
+        <v>861</v>
+      </c>
+      <c r="M26" s="84" t="s">
+        <v>838</v>
+      </c>
+      <c r="N26" s="84" t="s">
+        <v>839</v>
+      </c>
+      <c r="O26" s="84" t="s">
+        <v>840</v>
+      </c>
+      <c r="P26" s="84" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q26" s="84" t="s">
+        <v>907</v>
+      </c>
+      <c r="R26" s="84" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="85" t="s">
+        <v>776</v>
+      </c>
+      <c r="B27" s="85" t="s">
+        <v>793</v>
+      </c>
+      <c r="C27" s="85" t="s">
+        <v>909</v>
+      </c>
+      <c r="D27" s="85" t="s">
+        <v>779</v>
+      </c>
+      <c r="E27" s="85" t="s">
+        <v>910</v>
+      </c>
+      <c r="F27" s="85" t="s">
+        <v>911</v>
+      </c>
+      <c r="G27" s="85" t="s">
+        <v>797</v>
+      </c>
+      <c r="H27" s="85" t="s">
+        <v>794</v>
+      </c>
+      <c r="I27" s="85" t="s">
+        <v>912</v>
+      </c>
+      <c r="J27" s="85" t="s">
+        <v>784</v>
+      </c>
+      <c r="K27" s="85" t="s">
+        <v>785</v>
+      </c>
+      <c r="L27" s="85" t="s">
+        <v>913</v>
+      </c>
+      <c r="M27" s="85" t="s">
+        <v>914</v>
+      </c>
+      <c r="N27" s="85" t="s">
+        <v>914</v>
+      </c>
+      <c r="O27" s="85" t="s">
+        <v>914</v>
+      </c>
+      <c r="P27" s="85" t="s">
+        <v>790</v>
+      </c>
+      <c r="Q27" s="85" t="s">
+        <v>791</v>
+      </c>
+      <c r="R27" s="85" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="85" t="s">
+        <v>776</v>
+      </c>
+      <c r="B28" s="85" t="s">
+        <v>793</v>
+      </c>
+      <c r="C28" s="85" t="s">
+        <v>909</v>
+      </c>
+      <c r="D28" s="85" t="s">
+        <v>779</v>
+      </c>
+      <c r="E28" s="85" t="s">
+        <v>910</v>
+      </c>
+      <c r="F28" s="85" t="s">
+        <v>915</v>
+      </c>
+      <c r="G28" s="85" t="s">
+        <v>797</v>
+      </c>
+      <c r="H28" s="85" t="s">
+        <v>794</v>
+      </c>
+      <c r="I28" s="85" t="s">
+        <v>916</v>
+      </c>
+      <c r="J28" s="85" t="s">
+        <v>78</v>
+      </c>
+      <c r="K28" s="85" t="s">
+        <v>799</v>
+      </c>
+      <c r="L28" s="85" t="s">
+        <v>917</v>
+      </c>
+      <c r="M28" s="85" t="s">
+        <v>914</v>
+      </c>
+      <c r="N28" s="85" t="s">
+        <v>914</v>
+      </c>
+      <c r="O28" s="85" t="s">
+        <v>914</v>
+      </c>
+      <c r="P28" s="85" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q28" s="85" t="s">
+        <v>805</v>
+      </c>
+      <c r="R28" s="85" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="85" t="s">
+        <v>776</v>
+      </c>
+      <c r="B29" s="85" t="s">
+        <v>793</v>
+      </c>
+      <c r="C29" s="85" t="s">
+        <v>909</v>
+      </c>
+      <c r="D29" s="85" t="s">
+        <v>779</v>
+      </c>
+      <c r="E29" s="85" t="s">
+        <v>910</v>
+      </c>
+      <c r="F29" s="85" t="s">
+        <v>918</v>
+      </c>
+      <c r="G29" s="85" t="s">
+        <v>797</v>
+      </c>
+      <c r="H29" s="85" t="s">
+        <v>794</v>
+      </c>
+      <c r="I29" s="85" t="s">
+        <v>919</v>
+      </c>
+      <c r="J29" s="85" t="s">
+        <v>811</v>
+      </c>
+      <c r="K29" s="85" t="s">
+        <v>812</v>
+      </c>
+      <c r="L29" s="85" t="s">
+        <v>920</v>
+      </c>
+      <c r="M29" s="85" t="s">
+        <v>914</v>
+      </c>
+      <c r="N29" s="85" t="s">
+        <v>914</v>
+      </c>
+      <c r="O29" s="85" t="s">
+        <v>914</v>
+      </c>
+      <c r="P29" s="85" t="s">
+        <v>817</v>
+      </c>
+      <c r="Q29" s="85" t="s">
+        <v>818</v>
+      </c>
+      <c r="R29" s="85" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="85" t="s">
+        <v>776</v>
+      </c>
+      <c r="B30" s="85" t="s">
+        <v>793</v>
+      </c>
+      <c r="C30" s="85" t="s">
+        <v>909</v>
+      </c>
+      <c r="D30" s="85" t="s">
+        <v>779</v>
+      </c>
+      <c r="E30" s="85" t="s">
+        <v>910</v>
+      </c>
+      <c r="F30" s="85" t="s">
+        <v>921</v>
+      </c>
+      <c r="G30" s="85" t="s">
+        <v>797</v>
+      </c>
+      <c r="H30" s="85" t="s">
+        <v>794</v>
+      </c>
+      <c r="I30" s="85" t="s">
+        <v>922</v>
+      </c>
+      <c r="J30" s="85" t="s">
+        <v>835</v>
+      </c>
+      <c r="K30" s="85" t="s">
+        <v>836</v>
+      </c>
+      <c r="L30" s="85" t="s">
+        <v>837</v>
+      </c>
+      <c r="M30" s="85" t="s">
+        <v>914</v>
+      </c>
+      <c r="N30" s="85" t="s">
+        <v>914</v>
+      </c>
+      <c r="O30" s="85" t="s">
+        <v>914</v>
+      </c>
+      <c r="P30" s="85" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q30" s="85" t="s">
+        <v>923</v>
+      </c>
+      <c r="R30" s="85" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="85" t="s">
+        <v>776</v>
+      </c>
+      <c r="B31" s="85" t="s">
+        <v>793</v>
+      </c>
+      <c r="C31" s="85" t="s">
+        <v>909</v>
+      </c>
+      <c r="D31" s="85" t="s">
+        <v>779</v>
+      </c>
+      <c r="E31" s="85" t="s">
+        <v>910</v>
+      </c>
+      <c r="F31" s="85" t="s">
+        <v>924</v>
+      </c>
+      <c r="G31" s="85" t="s">
+        <v>797</v>
+      </c>
+      <c r="H31" s="85" t="s">
+        <v>794</v>
+      </c>
+      <c r="I31" s="85" t="s">
+        <v>925</v>
+      </c>
+      <c r="J31" s="85" t="s">
+        <v>823</v>
+      </c>
+      <c r="K31" s="85" t="s">
+        <v>824</v>
+      </c>
+      <c r="L31" s="85" t="s">
+        <v>825</v>
+      </c>
+      <c r="M31" s="85" t="s">
+        <v>914</v>
+      </c>
+      <c r="N31" s="85" t="s">
+        <v>914</v>
+      </c>
+      <c r="O31" s="85" t="s">
+        <v>914</v>
+      </c>
+      <c r="P31" s="85" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q31" s="85" t="s">
+        <v>830</v>
+      </c>
+      <c r="R31" s="85" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="86" t="s">
+        <v>776</v>
+      </c>
+      <c r="B32" s="86" t="s">
+        <v>793</v>
+      </c>
+      <c r="C32" s="86" t="s">
+        <v>909</v>
+      </c>
+      <c r="D32" s="86" t="s">
+        <v>779</v>
+      </c>
+      <c r="E32" s="86" t="s">
+        <v>910</v>
+      </c>
+      <c r="F32" s="86" t="s">
+        <v>926</v>
+      </c>
+      <c r="G32" s="86" t="s">
+        <v>797</v>
+      </c>
+      <c r="H32" s="86" t="s">
+        <v>794</v>
+      </c>
+      <c r="I32" s="86" t="s">
+        <v>912</v>
+      </c>
+      <c r="J32" s="86" t="s">
+        <v>784</v>
+      </c>
+      <c r="K32" s="86" t="s">
+        <v>785</v>
+      </c>
+      <c r="L32" s="86" t="s">
+        <v>913</v>
+      </c>
+      <c r="M32" s="86" t="s">
+        <v>914</v>
+      </c>
+      <c r="N32" s="86" t="s">
+        <v>914</v>
+      </c>
+      <c r="O32" s="86" t="s">
+        <v>914</v>
+      </c>
+      <c r="P32" s="86" t="s">
+        <v>790</v>
+      </c>
+      <c r="Q32" s="86" t="s">
+        <v>791</v>
+      </c>
+      <c r="R32" s="86" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="86" t="s">
+        <v>776</v>
+      </c>
+      <c r="B33" s="86" t="s">
+        <v>793</v>
+      </c>
+      <c r="C33" s="86" t="s">
+        <v>909</v>
+      </c>
+      <c r="D33" s="86" t="s">
+        <v>779</v>
+      </c>
+      <c r="E33" s="86" t="s">
+        <v>910</v>
+      </c>
+      <c r="F33" s="86" t="s">
+        <v>927</v>
+      </c>
+      <c r="G33" s="86" t="s">
+        <v>797</v>
+      </c>
+      <c r="H33" s="86" t="s">
+        <v>794</v>
+      </c>
+      <c r="I33" s="86" t="s">
+        <v>916</v>
+      </c>
+      <c r="J33" s="86" t="s">
+        <v>78</v>
+      </c>
+      <c r="K33" s="86" t="s">
+        <v>799</v>
+      </c>
+      <c r="L33" s="86" t="s">
+        <v>917</v>
+      </c>
+      <c r="M33" s="86" t="s">
+        <v>914</v>
+      </c>
+      <c r="N33" s="86" t="s">
+        <v>914</v>
+      </c>
+      <c r="O33" s="86" t="s">
+        <v>914</v>
+      </c>
+      <c r="P33" s="86" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q33" s="86" t="s">
+        <v>805</v>
+      </c>
+      <c r="R33" s="86" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="86" t="s">
+        <v>776</v>
+      </c>
+      <c r="B34" s="86" t="s">
+        <v>793</v>
+      </c>
+      <c r="C34" s="86" t="s">
+        <v>909</v>
+      </c>
+      <c r="D34" s="86" t="s">
+        <v>779</v>
+      </c>
+      <c r="E34" s="86" t="s">
+        <v>910</v>
+      </c>
+      <c r="F34" s="86" t="s">
+        <v>928</v>
+      </c>
+      <c r="G34" s="86" t="s">
+        <v>797</v>
+      </c>
+      <c r="H34" s="86" t="s">
+        <v>794</v>
+      </c>
+      <c r="I34" s="86" t="s">
+        <v>919</v>
+      </c>
+      <c r="J34" s="86" t="s">
+        <v>811</v>
+      </c>
+      <c r="K34" s="86" t="s">
+        <v>812</v>
+      </c>
+      <c r="L34" s="86" t="s">
+        <v>920</v>
+      </c>
+      <c r="M34" s="86" t="s">
+        <v>914</v>
+      </c>
+      <c r="N34" s="86" t="s">
+        <v>914</v>
+      </c>
+      <c r="O34" s="86" t="s">
+        <v>914</v>
+      </c>
+      <c r="P34" s="86" t="s">
+        <v>817</v>
+      </c>
+      <c r="Q34" s="86" t="s">
+        <v>818</v>
+      </c>
+      <c r="R34" s="86" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="86" t="s">
+        <v>776</v>
+      </c>
+      <c r="B35" s="86" t="s">
+        <v>793</v>
+      </c>
+      <c r="C35" s="86" t="s">
+        <v>909</v>
+      </c>
+      <c r="D35" s="86" t="s">
+        <v>779</v>
+      </c>
+      <c r="E35" s="86" t="s">
+        <v>910</v>
+      </c>
+      <c r="F35" s="86" t="s">
+        <v>929</v>
+      </c>
+      <c r="G35" s="86" t="s">
+        <v>797</v>
+      </c>
+      <c r="H35" s="86" t="s">
+        <v>794</v>
+      </c>
+      <c r="I35" s="86" t="s">
+        <v>922</v>
+      </c>
+      <c r="J35" s="86" t="s">
+        <v>835</v>
+      </c>
+      <c r="K35" s="86" t="s">
+        <v>836</v>
+      </c>
+      <c r="L35" s="86" t="s">
+        <v>837</v>
+      </c>
+      <c r="M35" s="86" t="s">
+        <v>914</v>
+      </c>
+      <c r="N35" s="86" t="s">
+        <v>914</v>
+      </c>
+      <c r="O35" s="86" t="s">
+        <v>914</v>
+      </c>
+      <c r="P35" s="86" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q35" s="86" t="s">
+        <v>923</v>
+      </c>
+      <c r="R35" s="86" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="86" t="s">
+        <v>776</v>
+      </c>
+      <c r="B36" s="86" t="s">
+        <v>793</v>
+      </c>
+      <c r="C36" s="86" t="s">
+        <v>909</v>
+      </c>
+      <c r="D36" s="86" t="s">
+        <v>779</v>
+      </c>
+      <c r="E36" s="86" t="s">
+        <v>910</v>
+      </c>
+      <c r="F36" s="86" t="s">
+        <v>930</v>
+      </c>
+      <c r="G36" s="86" t="s">
+        <v>797</v>
+      </c>
+      <c r="H36" s="86" t="s">
+        <v>794</v>
+      </c>
+      <c r="I36" s="86" t="s">
+        <v>925</v>
+      </c>
+      <c r="J36" s="86" t="s">
+        <v>823</v>
+      </c>
+      <c r="K36" s="86" t="s">
+        <v>824</v>
+      </c>
+      <c r="L36" s="86" t="s">
+        <v>825</v>
+      </c>
+      <c r="M36" s="86" t="s">
+        <v>914</v>
+      </c>
+      <c r="N36" s="86" t="s">
+        <v>914</v>
+      </c>
+      <c r="O36" s="86" t="s">
+        <v>914</v>
+      </c>
+      <c r="P36" s="86" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q36" s="86" t="s">
+        <v>830</v>
+      </c>
+      <c r="R36" s="86" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="87" t="s">
+        <v>776</v>
+      </c>
+      <c r="B37" s="87" t="s">
+        <v>793</v>
+      </c>
+      <c r="C37" s="87" t="s">
+        <v>909</v>
+      </c>
+      <c r="D37" s="87" t="s">
+        <v>779</v>
+      </c>
+      <c r="E37" s="87" t="s">
+        <v>910</v>
+      </c>
+      <c r="F37" s="87" t="s">
+        <v>931</v>
+      </c>
+      <c r="G37" s="87" t="s">
+        <v>797</v>
+      </c>
+      <c r="H37" s="87" t="s">
+        <v>794</v>
+      </c>
+      <c r="I37" s="87" t="s">
+        <v>912</v>
+      </c>
+      <c r="J37" s="87" t="s">
+        <v>784</v>
+      </c>
+      <c r="K37" s="87" t="s">
+        <v>785</v>
+      </c>
+      <c r="L37" s="87" t="s">
+        <v>913</v>
+      </c>
+      <c r="M37" s="87" t="s">
+        <v>914</v>
+      </c>
+      <c r="N37" s="87" t="s">
+        <v>914</v>
+      </c>
+      <c r="O37" s="87" t="s">
+        <v>914</v>
+      </c>
+      <c r="P37" s="87" t="s">
+        <v>790</v>
+      </c>
+      <c r="Q37" s="87" t="s">
+        <v>791</v>
+      </c>
+      <c r="R37" s="87" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="87" t="s">
+        <v>776</v>
+      </c>
+      <c r="B38" s="87" t="s">
+        <v>793</v>
+      </c>
+      <c r="C38" s="87" t="s">
+        <v>909</v>
+      </c>
+      <c r="D38" s="87" t="s">
+        <v>779</v>
+      </c>
+      <c r="E38" s="87" t="s">
+        <v>910</v>
+      </c>
+      <c r="F38" s="87" t="s">
+        <v>932</v>
+      </c>
+      <c r="G38" s="87" t="s">
+        <v>797</v>
+      </c>
+      <c r="H38" s="87" t="s">
+        <v>794</v>
+      </c>
+      <c r="I38" s="87" t="s">
+        <v>916</v>
+      </c>
+      <c r="J38" s="87" t="s">
+        <v>78</v>
+      </c>
+      <c r="K38" s="87" t="s">
+        <v>799</v>
+      </c>
+      <c r="L38" s="87" t="s">
+        <v>917</v>
+      </c>
+      <c r="M38" s="87" t="s">
+        <v>914</v>
+      </c>
+      <c r="N38" s="87" t="s">
+        <v>914</v>
+      </c>
+      <c r="O38" s="87" t="s">
+        <v>914</v>
+      </c>
+      <c r="P38" s="87" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q38" s="87" t="s">
+        <v>805</v>
+      </c>
+      <c r="R38" s="87" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="87" t="s">
+        <v>776</v>
+      </c>
+      <c r="B39" s="87" t="s">
+        <v>793</v>
+      </c>
+      <c r="C39" s="87" t="s">
+        <v>909</v>
+      </c>
+      <c r="D39" s="87" t="s">
+        <v>779</v>
+      </c>
+      <c r="E39" s="87" t="s">
+        <v>910</v>
+      </c>
+      <c r="F39" s="87" t="s">
+        <v>933</v>
+      </c>
+      <c r="G39" s="87" t="s">
+        <v>797</v>
+      </c>
+      <c r="H39" s="87" t="s">
+        <v>794</v>
+      </c>
+      <c r="I39" s="87" t="s">
+        <v>919</v>
+      </c>
+      <c r="J39" s="87" t="s">
+        <v>811</v>
+      </c>
+      <c r="K39" s="87" t="s">
+        <v>812</v>
+      </c>
+      <c r="L39" s="87" t="s">
+        <v>920</v>
+      </c>
+      <c r="M39" s="87" t="s">
+        <v>914</v>
+      </c>
+      <c r="N39" s="87" t="s">
+        <v>914</v>
+      </c>
+      <c r="O39" s="87" t="s">
+        <v>914</v>
+      </c>
+      <c r="P39" s="87" t="s">
+        <v>817</v>
+      </c>
+      <c r="Q39" s="87" t="s">
+        <v>818</v>
+      </c>
+      <c r="R39" s="87" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="87" t="s">
+        <v>776</v>
+      </c>
+      <c r="B40" s="87" t="s">
+        <v>793</v>
+      </c>
+      <c r="C40" s="87" t="s">
+        <v>909</v>
+      </c>
+      <c r="D40" s="87" t="s">
+        <v>779</v>
+      </c>
+      <c r="E40" s="87" t="s">
+        <v>910</v>
+      </c>
+      <c r="F40" s="87" t="s">
+        <v>934</v>
+      </c>
+      <c r="G40" s="87" t="s">
+        <v>797</v>
+      </c>
+      <c r="H40" s="87" t="s">
+        <v>794</v>
+      </c>
+      <c r="I40" s="87" t="s">
+        <v>922</v>
+      </c>
+      <c r="J40" s="87" t="s">
+        <v>835</v>
+      </c>
+      <c r="K40" s="87" t="s">
+        <v>836</v>
+      </c>
+      <c r="L40" s="87" t="s">
+        <v>837</v>
+      </c>
+      <c r="M40" s="87" t="s">
+        <v>914</v>
+      </c>
+      <c r="N40" s="87" t="s">
+        <v>914</v>
+      </c>
+      <c r="O40" s="87" t="s">
+        <v>914</v>
+      </c>
+      <c r="P40" s="87" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q40" s="87" t="s">
+        <v>923</v>
+      </c>
+      <c r="R40" s="87" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="87" t="s">
+        <v>776</v>
+      </c>
+      <c r="B41" s="87" t="s">
+        <v>793</v>
+      </c>
+      <c r="C41" s="87" t="s">
+        <v>909</v>
+      </c>
+      <c r="D41" s="87" t="s">
+        <v>779</v>
+      </c>
+      <c r="E41" s="87" t="s">
+        <v>910</v>
+      </c>
+      <c r="F41" s="87" t="s">
+        <v>935</v>
+      </c>
+      <c r="G41" s="87" t="s">
+        <v>797</v>
+      </c>
+      <c r="H41" s="87" t="s">
+        <v>794</v>
+      </c>
+      <c r="I41" s="87" t="s">
+        <v>925</v>
+      </c>
+      <c r="J41" s="87" t="s">
+        <v>823</v>
+      </c>
+      <c r="K41" s="87" t="s">
+        <v>824</v>
+      </c>
+      <c r="L41" s="87" t="s">
+        <v>825</v>
+      </c>
+      <c r="M41" s="87" t="s">
+        <v>914</v>
+      </c>
+      <c r="N41" s="87" t="s">
+        <v>914</v>
+      </c>
+      <c r="O41" s="87" t="s">
+        <v>914</v>
+      </c>
+      <c r="P41" s="87" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q41" s="87" t="s">
+        <v>830</v>
+      </c>
+      <c r="R41" s="87" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="88" t="s">
+        <v>776</v>
+      </c>
+      <c r="B42" s="88" t="s">
+        <v>793</v>
+      </c>
+      <c r="C42" s="88" t="s">
+        <v>909</v>
+      </c>
+      <c r="D42" s="88" t="s">
+        <v>779</v>
+      </c>
+      <c r="E42" s="88" t="s">
+        <v>910</v>
+      </c>
+      <c r="F42" s="88" t="s">
+        <v>936</v>
+      </c>
+      <c r="G42" s="88" t="s">
+        <v>797</v>
+      </c>
+      <c r="H42" s="88" t="s">
+        <v>794</v>
+      </c>
+      <c r="I42" s="88" t="s">
+        <v>912</v>
+      </c>
+      <c r="J42" s="88" t="s">
+        <v>784</v>
+      </c>
+      <c r="K42" s="88" t="s">
+        <v>785</v>
+      </c>
+      <c r="L42" s="88" t="s">
+        <v>913</v>
+      </c>
+      <c r="M42" s="88" t="s">
+        <v>914</v>
+      </c>
+      <c r="N42" s="88" t="s">
+        <v>914</v>
+      </c>
+      <c r="O42" s="88" t="s">
+        <v>914</v>
+      </c>
+      <c r="P42" s="88" t="s">
+        <v>790</v>
+      </c>
+      <c r="Q42" s="88" t="s">
+        <v>791</v>
+      </c>
+      <c r="R42" s="88" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="88" t="s">
+        <v>776</v>
+      </c>
+      <c r="B43" s="88" t="s">
+        <v>793</v>
+      </c>
+      <c r="C43" s="88" t="s">
+        <v>909</v>
+      </c>
+      <c r="D43" s="88" t="s">
+        <v>779</v>
+      </c>
+      <c r="E43" s="88" t="s">
+        <v>910</v>
+      </c>
+      <c r="F43" s="88" t="s">
+        <v>937</v>
+      </c>
+      <c r="G43" s="88" t="s">
+        <v>797</v>
+      </c>
+      <c r="H43" s="88" t="s">
+        <v>794</v>
+      </c>
+      <c r="I43" s="88" t="s">
+        <v>916</v>
+      </c>
+      <c r="J43" s="88" t="s">
+        <v>78</v>
+      </c>
+      <c r="K43" s="88" t="s">
+        <v>799</v>
+      </c>
+      <c r="L43" s="88" t="s">
+        <v>917</v>
+      </c>
+      <c r="M43" s="88" t="s">
+        <v>914</v>
+      </c>
+      <c r="N43" s="88" t="s">
+        <v>914</v>
+      </c>
+      <c r="O43" s="88" t="s">
+        <v>914</v>
+      </c>
+      <c r="P43" s="88" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q43" s="88" t="s">
+        <v>805</v>
+      </c>
+      <c r="R43" s="88" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="88" t="s">
+        <v>776</v>
+      </c>
+      <c r="B44" s="88" t="s">
+        <v>793</v>
+      </c>
+      <c r="C44" s="88" t="s">
+        <v>909</v>
+      </c>
+      <c r="D44" s="88" t="s">
+        <v>779</v>
+      </c>
+      <c r="E44" s="88" t="s">
+        <v>910</v>
+      </c>
+      <c r="F44" s="88" t="s">
+        <v>938</v>
+      </c>
+      <c r="G44" s="88" t="s">
+        <v>797</v>
+      </c>
+      <c r="H44" s="88" t="s">
+        <v>794</v>
+      </c>
+      <c r="I44" s="88" t="s">
+        <v>919</v>
+      </c>
+      <c r="J44" s="88" t="s">
+        <v>811</v>
+      </c>
+      <c r="K44" s="88" t="s">
+        <v>812</v>
+      </c>
+      <c r="L44" s="88" t="s">
+        <v>920</v>
+      </c>
+      <c r="M44" s="88" t="s">
+        <v>914</v>
+      </c>
+      <c r="N44" s="88" t="s">
+        <v>914</v>
+      </c>
+      <c r="O44" s="88" t="s">
+        <v>914</v>
+      </c>
+      <c r="P44" s="88" t="s">
+        <v>817</v>
+      </c>
+      <c r="Q44" s="88" t="s">
+        <v>818</v>
+      </c>
+      <c r="R44" s="88" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="88" t="s">
+        <v>776</v>
+      </c>
+      <c r="B45" s="88" t="s">
+        <v>793</v>
+      </c>
+      <c r="C45" s="88" t="s">
+        <v>909</v>
+      </c>
+      <c r="D45" s="88" t="s">
+        <v>779</v>
+      </c>
+      <c r="E45" s="88" t="s">
+        <v>910</v>
+      </c>
+      <c r="F45" s="88" t="s">
+        <v>939</v>
+      </c>
+      <c r="G45" s="88" t="s">
+        <v>797</v>
+      </c>
+      <c r="H45" s="88" t="s">
+        <v>794</v>
+      </c>
+      <c r="I45" s="88" t="s">
+        <v>922</v>
+      </c>
+      <c r="J45" s="88" t="s">
+        <v>835</v>
+      </c>
+      <c r="K45" s="88" t="s">
+        <v>836</v>
+      </c>
+      <c r="L45" s="88" t="s">
+        <v>837</v>
+      </c>
+      <c r="M45" s="88" t="s">
+        <v>914</v>
+      </c>
+      <c r="N45" s="88" t="s">
+        <v>914</v>
+      </c>
+      <c r="O45" s="88" t="s">
+        <v>914</v>
+      </c>
+      <c r="P45" s="88" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q45" s="88" t="s">
+        <v>923</v>
+      </c>
+      <c r="R45" s="88" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="88" t="s">
+        <v>776</v>
+      </c>
+      <c r="B46" s="88" t="s">
+        <v>793</v>
+      </c>
+      <c r="C46" s="88" t="s">
+        <v>909</v>
+      </c>
+      <c r="D46" s="88" t="s">
+        <v>779</v>
+      </c>
+      <c r="E46" s="88" t="s">
+        <v>910</v>
+      </c>
+      <c r="F46" s="88" t="s">
+        <v>940</v>
+      </c>
+      <c r="G46" s="88" t="s">
+        <v>797</v>
+      </c>
+      <c r="H46" s="88" t="s">
+        <v>794</v>
+      </c>
+      <c r="I46" s="88" t="s">
+        <v>925</v>
+      </c>
+      <c r="J46" s="88" t="s">
+        <v>823</v>
+      </c>
+      <c r="K46" s="88" t="s">
+        <v>824</v>
+      </c>
+      <c r="L46" s="88" t="s">
+        <v>825</v>
+      </c>
+      <c r="M46" s="88" t="s">
+        <v>914</v>
+      </c>
+      <c r="N46" s="88" t="s">
+        <v>914</v>
+      </c>
+      <c r="O46" s="88" t="s">
+        <v>914</v>
+      </c>
+      <c r="P46" s="88" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q46" s="88" t="s">
+        <v>830</v>
+      </c>
+      <c r="R46" s="88" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="89" t="s">
+        <v>776</v>
+      </c>
+      <c r="B47" s="89" t="s">
+        <v>793</v>
+      </c>
+      <c r="C47" s="89" t="s">
+        <v>909</v>
+      </c>
+      <c r="D47" s="89" t="s">
+        <v>779</v>
+      </c>
+      <c r="E47" s="89" t="s">
+        <v>910</v>
+      </c>
+      <c r="F47" s="89" t="s">
+        <v>941</v>
+      </c>
+      <c r="G47" s="89" t="s">
+        <v>797</v>
+      </c>
+      <c r="H47" s="89" t="s">
+        <v>794</v>
+      </c>
+      <c r="I47" s="89" t="s">
+        <v>912</v>
+      </c>
+      <c r="J47" s="89" t="s">
+        <v>784</v>
+      </c>
+      <c r="K47" s="89" t="s">
+        <v>785</v>
+      </c>
+      <c r="L47" s="89" t="s">
+        <v>913</v>
+      </c>
+      <c r="M47" s="89" t="s">
+        <v>914</v>
+      </c>
+      <c r="N47" s="89" t="s">
+        <v>914</v>
+      </c>
+      <c r="O47" s="89" t="s">
+        <v>914</v>
+      </c>
+      <c r="P47" s="89" t="s">
+        <v>790</v>
+      </c>
+      <c r="Q47" s="89" t="s">
+        <v>791</v>
+      </c>
+      <c r="R47" s="89" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="89" t="s">
+        <v>776</v>
+      </c>
+      <c r="B48" s="89" t="s">
+        <v>793</v>
+      </c>
+      <c r="C48" s="89" t="s">
+        <v>909</v>
+      </c>
+      <c r="D48" s="89" t="s">
+        <v>779</v>
+      </c>
+      <c r="E48" s="89" t="s">
+        <v>910</v>
+      </c>
+      <c r="F48" s="89" t="s">
+        <v>942</v>
+      </c>
+      <c r="G48" s="89" t="s">
+        <v>797</v>
+      </c>
+      <c r="H48" s="89" t="s">
+        <v>794</v>
+      </c>
+      <c r="I48" s="89" t="s">
+        <v>916</v>
+      </c>
+      <c r="J48" s="89" t="s">
+        <v>78</v>
+      </c>
+      <c r="K48" s="89" t="s">
+        <v>799</v>
+      </c>
+      <c r="L48" s="89" t="s">
+        <v>917</v>
+      </c>
+      <c r="M48" s="89" t="s">
+        <v>914</v>
+      </c>
+      <c r="N48" s="89" t="s">
+        <v>914</v>
+      </c>
+      <c r="O48" s="89" t="s">
+        <v>914</v>
+      </c>
+      <c r="P48" s="89" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q48" s="89" t="s">
+        <v>805</v>
+      </c>
+      <c r="R48" s="89" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="89" t="s">
+        <v>776</v>
+      </c>
+      <c r="B49" s="89" t="s">
+        <v>793</v>
+      </c>
+      <c r="C49" s="89" t="s">
+        <v>909</v>
+      </c>
+      <c r="D49" s="89" t="s">
+        <v>779</v>
+      </c>
+      <c r="E49" s="89" t="s">
+        <v>910</v>
+      </c>
+      <c r="F49" s="89" t="s">
+        <v>943</v>
+      </c>
+      <c r="G49" s="89" t="s">
+        <v>797</v>
+      </c>
+      <c r="H49" s="89" t="s">
+        <v>794</v>
+      </c>
+      <c r="I49" s="89" t="s">
+        <v>919</v>
+      </c>
+      <c r="J49" s="89" t="s">
+        <v>811</v>
+      </c>
+      <c r="K49" s="89" t="s">
+        <v>812</v>
+      </c>
+      <c r="L49" s="89" t="s">
+        <v>920</v>
+      </c>
+      <c r="M49" s="89" t="s">
+        <v>914</v>
+      </c>
+      <c r="N49" s="89" t="s">
+        <v>914</v>
+      </c>
+      <c r="O49" s="89" t="s">
+        <v>914</v>
+      </c>
+      <c r="P49" s="89" t="s">
+        <v>817</v>
+      </c>
+      <c r="Q49" s="89" t="s">
+        <v>818</v>
+      </c>
+      <c r="R49" s="89" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="89" t="s">
+        <v>776</v>
+      </c>
+      <c r="B50" s="89" t="s">
+        <v>793</v>
+      </c>
+      <c r="C50" s="89" t="s">
+        <v>909</v>
+      </c>
+      <c r="D50" s="89" t="s">
+        <v>779</v>
+      </c>
+      <c r="E50" s="89" t="s">
+        <v>910</v>
+      </c>
+      <c r="F50" s="89" t="s">
+        <v>944</v>
+      </c>
+      <c r="G50" s="89" t="s">
+        <v>797</v>
+      </c>
+      <c r="H50" s="89" t="s">
+        <v>794</v>
+      </c>
+      <c r="I50" s="89" t="s">
+        <v>922</v>
+      </c>
+      <c r="J50" s="89" t="s">
+        <v>835</v>
+      </c>
+      <c r="K50" s="89" t="s">
+        <v>836</v>
+      </c>
+      <c r="L50" s="89" t="s">
+        <v>837</v>
+      </c>
+      <c r="M50" s="89" t="s">
+        <v>914</v>
+      </c>
+      <c r="N50" s="89" t="s">
+        <v>914</v>
+      </c>
+      <c r="O50" s="89" t="s">
+        <v>914</v>
+      </c>
+      <c r="P50" s="89" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q50" s="89" t="s">
+        <v>923</v>
+      </c>
+      <c r="R50" s="89" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="89" t="s">
+        <v>776</v>
+      </c>
+      <c r="B51" s="89" t="s">
+        <v>793</v>
+      </c>
+      <c r="C51" s="89" t="s">
+        <v>909</v>
+      </c>
+      <c r="D51" s="89" t="s">
+        <v>779</v>
+      </c>
+      <c r="E51" s="89" t="s">
+        <v>910</v>
+      </c>
+      <c r="F51" s="89" t="s">
+        <v>945</v>
+      </c>
+      <c r="G51" s="89" t="s">
+        <v>797</v>
+      </c>
+      <c r="H51" s="89" t="s">
+        <v>794</v>
+      </c>
+      <c r="I51" s="89" t="s">
+        <v>925</v>
+      </c>
+      <c r="J51" s="89" t="s">
+        <v>823</v>
+      </c>
+      <c r="K51" s="89" t="s">
+        <v>824</v>
+      </c>
+      <c r="L51" s="89" t="s">
+        <v>825</v>
+      </c>
+      <c r="M51" s="89" t="s">
+        <v>914</v>
+      </c>
+      <c r="N51" s="89" t="s">
+        <v>914</v>
+      </c>
+      <c r="O51" s="89" t="s">
+        <v>914</v>
+      </c>
+      <c r="P51" s="89" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q51" s="89" t="s">
+        <v>830</v>
+      </c>
+      <c r="R51" s="89" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="90" t="s">
+        <v>776</v>
+      </c>
+      <c r="B52" s="90" t="s">
+        <v>793</v>
+      </c>
+      <c r="C52" s="90" t="s">
+        <v>909</v>
+      </c>
+      <c r="D52" s="90" t="s">
+        <v>779</v>
+      </c>
+      <c r="E52" s="90" t="s">
+        <v>910</v>
+      </c>
+      <c r="F52" s="90" t="s">
+        <v>946</v>
+      </c>
+      <c r="G52" s="90" t="s">
+        <v>797</v>
+      </c>
+      <c r="H52" s="90" t="s">
+        <v>794</v>
+      </c>
+      <c r="I52" s="90" t="s">
+        <v>912</v>
+      </c>
+      <c r="J52" s="90" t="s">
+        <v>784</v>
+      </c>
+      <c r="K52" s="90" t="s">
+        <v>785</v>
+      </c>
+      <c r="L52" s="90" t="s">
+        <v>913</v>
+      </c>
+      <c r="M52" s="90" t="s">
+        <v>914</v>
+      </c>
+      <c r="N52" s="90" t="s">
+        <v>914</v>
+      </c>
+      <c r="O52" s="90" t="s">
+        <v>914</v>
+      </c>
+      <c r="P52" s="90" t="s">
+        <v>790</v>
+      </c>
+      <c r="Q52" s="90" t="s">
+        <v>791</v>
+      </c>
+      <c r="R52" s="90" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="90" t="s">
+        <v>776</v>
+      </c>
+      <c r="B53" s="90" t="s">
+        <v>793</v>
+      </c>
+      <c r="C53" s="90" t="s">
+        <v>909</v>
+      </c>
+      <c r="D53" s="90" t="s">
+        <v>779</v>
+      </c>
+      <c r="E53" s="90" t="s">
+        <v>910</v>
+      </c>
+      <c r="F53" s="90" t="s">
+        <v>947</v>
+      </c>
+      <c r="G53" s="90" t="s">
+        <v>797</v>
+      </c>
+      <c r="H53" s="90" t="s">
+        <v>794</v>
+      </c>
+      <c r="I53" s="90" t="s">
+        <v>916</v>
+      </c>
+      <c r="J53" s="90" t="s">
+        <v>78</v>
+      </c>
+      <c r="K53" s="90" t="s">
+        <v>799</v>
+      </c>
+      <c r="L53" s="90" t="s">
+        <v>917</v>
+      </c>
+      <c r="M53" s="90" t="s">
+        <v>914</v>
+      </c>
+      <c r="N53" s="90" t="s">
+        <v>914</v>
+      </c>
+      <c r="O53" s="90" t="s">
+        <v>914</v>
+      </c>
+      <c r="P53" s="90" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q53" s="90" t="s">
+        <v>805</v>
+      </c>
+      <c r="R53" s="90" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="90" t="s">
+        <v>776</v>
+      </c>
+      <c r="B54" s="90" t="s">
+        <v>793</v>
+      </c>
+      <c r="C54" s="90" t="s">
+        <v>909</v>
+      </c>
+      <c r="D54" s="90" t="s">
+        <v>779</v>
+      </c>
+      <c r="E54" s="90" t="s">
+        <v>910</v>
+      </c>
+      <c r="F54" s="90" t="s">
+        <v>948</v>
+      </c>
+      <c r="G54" s="90" t="s">
+        <v>797</v>
+      </c>
+      <c r="H54" s="90" t="s">
+        <v>794</v>
+      </c>
+      <c r="I54" s="90" t="s">
+        <v>919</v>
+      </c>
+      <c r="J54" s="90" t="s">
+        <v>811</v>
+      </c>
+      <c r="K54" s="90" t="s">
+        <v>812</v>
+      </c>
+      <c r="L54" s="90" t="s">
+        <v>920</v>
+      </c>
+      <c r="M54" s="90" t="s">
+        <v>914</v>
+      </c>
+      <c r="N54" s="90" t="s">
+        <v>914</v>
+      </c>
+      <c r="O54" s="90" t="s">
+        <v>914</v>
+      </c>
+      <c r="P54" s="90" t="s">
+        <v>817</v>
+      </c>
+      <c r="Q54" s="90" t="s">
+        <v>818</v>
+      </c>
+      <c r="R54" s="90" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="90" t="s">
+        <v>776</v>
+      </c>
+      <c r="B55" s="90" t="s">
+        <v>793</v>
+      </c>
+      <c r="C55" s="90" t="s">
+        <v>909</v>
+      </c>
+      <c r="D55" s="90" t="s">
+        <v>779</v>
+      </c>
+      <c r="E55" s="90" t="s">
+        <v>910</v>
+      </c>
+      <c r="F55" s="90" t="s">
+        <v>949</v>
+      </c>
+      <c r="G55" s="90" t="s">
+        <v>797</v>
+      </c>
+      <c r="H55" s="90" t="s">
+        <v>794</v>
+      </c>
+      <c r="I55" s="90" t="s">
+        <v>922</v>
+      </c>
+      <c r="J55" s="90" t="s">
+        <v>835</v>
+      </c>
+      <c r="K55" s="90" t="s">
+        <v>836</v>
+      </c>
+      <c r="L55" s="90" t="s">
+        <v>837</v>
+      </c>
+      <c r="M55" s="90" t="s">
+        <v>914</v>
+      </c>
+      <c r="N55" s="90" t="s">
+        <v>914</v>
+      </c>
+      <c r="O55" s="90" t="s">
+        <v>914</v>
+      </c>
+      <c r="P55" s="90" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q55" s="90" t="s">
+        <v>923</v>
+      </c>
+      <c r="R55" s="90" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="90" t="s">
+        <v>776</v>
+      </c>
+      <c r="B56" s="90" t="s">
+        <v>793</v>
+      </c>
+      <c r="C56" s="90" t="s">
+        <v>909</v>
+      </c>
+      <c r="D56" s="90" t="s">
+        <v>779</v>
+      </c>
+      <c r="E56" s="90" t="s">
+        <v>910</v>
+      </c>
+      <c r="F56" s="90" t="s">
+        <v>950</v>
+      </c>
+      <c r="G56" s="90" t="s">
+        <v>797</v>
+      </c>
+      <c r="H56" s="90" t="s">
+        <v>794</v>
+      </c>
+      <c r="I56" s="90" t="s">
+        <v>925</v>
+      </c>
+      <c r="J56" s="90" t="s">
+        <v>823</v>
+      </c>
+      <c r="K56" s="90" t="s">
+        <v>824</v>
+      </c>
+      <c r="L56" s="90" t="s">
+        <v>825</v>
+      </c>
+      <c r="M56" s="90" t="s">
+        <v>914</v>
+      </c>
+      <c r="N56" s="90" t="s">
+        <v>914</v>
+      </c>
+      <c r="O56" s="90" t="s">
+        <v>914</v>
+      </c>
+      <c r="P56" s="90" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q56" s="90" t="s">
+        <v>830</v>
+      </c>
+      <c r="R56" s="90" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="91" t="s">
+        <v>776</v>
+      </c>
+      <c r="B57" s="91" t="s">
+        <v>793</v>
+      </c>
+      <c r="C57" s="91" t="s">
+        <v>909</v>
+      </c>
+      <c r="D57" s="91" t="s">
+        <v>779</v>
+      </c>
+      <c r="E57" s="91" t="s">
+        <v>910</v>
+      </c>
+      <c r="F57" s="91" t="s">
+        <v>951</v>
+      </c>
+      <c r="G57" s="91" t="s">
+        <v>797</v>
+      </c>
+      <c r="H57" s="91" t="s">
+        <v>794</v>
+      </c>
+      <c r="I57" s="91" t="s">
+        <v>912</v>
+      </c>
+      <c r="J57" s="91" t="s">
+        <v>784</v>
+      </c>
+      <c r="K57" s="91" t="s">
+        <v>785</v>
+      </c>
+      <c r="L57" s="91" t="s">
+        <v>913</v>
+      </c>
+      <c r="M57" s="91" t="s">
+        <v>914</v>
+      </c>
+      <c r="N57" s="91" t="s">
+        <v>914</v>
+      </c>
+      <c r="O57" s="91" t="s">
+        <v>914</v>
+      </c>
+      <c r="P57" s="91" t="s">
+        <v>790</v>
+      </c>
+      <c r="Q57" s="91" t="s">
+        <v>791</v>
+      </c>
+      <c r="R57" s="91" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="91" t="s">
+        <v>776</v>
+      </c>
+      <c r="B58" s="91" t="s">
+        <v>793</v>
+      </c>
+      <c r="C58" s="91" t="s">
+        <v>909</v>
+      </c>
+      <c r="D58" s="91" t="s">
+        <v>779</v>
+      </c>
+      <c r="E58" s="91" t="s">
+        <v>910</v>
+      </c>
+      <c r="F58" s="91" t="s">
+        <v>952</v>
+      </c>
+      <c r="G58" s="91" t="s">
+        <v>797</v>
+      </c>
+      <c r="H58" s="91" t="s">
+        <v>794</v>
+      </c>
+      <c r="I58" s="91" t="s">
+        <v>916</v>
+      </c>
+      <c r="J58" s="91" t="s">
+        <v>78</v>
+      </c>
+      <c r="K58" s="91" t="s">
+        <v>799</v>
+      </c>
+      <c r="L58" s="91" t="s">
+        <v>917</v>
+      </c>
+      <c r="M58" s="91" t="s">
+        <v>914</v>
+      </c>
+      <c r="N58" s="91" t="s">
+        <v>914</v>
+      </c>
+      <c r="O58" s="91" t="s">
+        <v>914</v>
+      </c>
+      <c r="P58" s="91" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q58" s="91" t="s">
+        <v>805</v>
+      </c>
+      <c r="R58" s="91" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="91" t="s">
+        <v>776</v>
+      </c>
+      <c r="B59" s="91" t="s">
+        <v>793</v>
+      </c>
+      <c r="C59" s="91" t="s">
+        <v>909</v>
+      </c>
+      <c r="D59" s="91" t="s">
+        <v>779</v>
+      </c>
+      <c r="E59" s="91" t="s">
+        <v>910</v>
+      </c>
+      <c r="F59" s="91" t="s">
+        <v>953</v>
+      </c>
+      <c r="G59" s="91" t="s">
+        <v>797</v>
+      </c>
+      <c r="H59" s="91" t="s">
+        <v>794</v>
+      </c>
+      <c r="I59" s="91" t="s">
+        <v>919</v>
+      </c>
+      <c r="J59" s="91" t="s">
+        <v>811</v>
+      </c>
+      <c r="K59" s="91" t="s">
+        <v>812</v>
+      </c>
+      <c r="L59" s="91" t="s">
+        <v>920</v>
+      </c>
+      <c r="M59" s="91" t="s">
+        <v>914</v>
+      </c>
+      <c r="N59" s="91" t="s">
+        <v>914</v>
+      </c>
+      <c r="O59" s="91" t="s">
+        <v>914</v>
+      </c>
+      <c r="P59" s="91" t="s">
+        <v>817</v>
+      </c>
+      <c r="Q59" s="91" t="s">
+        <v>818</v>
+      </c>
+      <c r="R59" s="91" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="91" t="s">
+        <v>776</v>
+      </c>
+      <c r="B60" s="91" t="s">
+        <v>793</v>
+      </c>
+      <c r="C60" s="91" t="s">
+        <v>909</v>
+      </c>
+      <c r="D60" s="91" t="s">
+        <v>779</v>
+      </c>
+      <c r="E60" s="91" t="s">
+        <v>910</v>
+      </c>
+      <c r="F60" s="91" t="s">
+        <v>954</v>
+      </c>
+      <c r="G60" s="91" t="s">
+        <v>797</v>
+      </c>
+      <c r="H60" s="91" t="s">
+        <v>794</v>
+      </c>
+      <c r="I60" s="91" t="s">
+        <v>922</v>
+      </c>
+      <c r="J60" s="91" t="s">
+        <v>835</v>
+      </c>
+      <c r="K60" s="91" t="s">
+        <v>836</v>
+      </c>
+      <c r="L60" s="91" t="s">
+        <v>837</v>
+      </c>
+      <c r="M60" s="91" t="s">
+        <v>914</v>
+      </c>
+      <c r="N60" s="91" t="s">
+        <v>914</v>
+      </c>
+      <c r="O60" s="91" t="s">
+        <v>914</v>
+      </c>
+      <c r="P60" s="91" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q60" s="91" t="s">
+        <v>923</v>
+      </c>
+      <c r="R60" s="91" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="91" t="s">
+        <v>776</v>
+      </c>
+      <c r="B61" s="91" t="s">
+        <v>793</v>
+      </c>
+      <c r="C61" s="91" t="s">
+        <v>909</v>
+      </c>
+      <c r="D61" s="91" t="s">
+        <v>779</v>
+      </c>
+      <c r="E61" s="91" t="s">
+        <v>910</v>
+      </c>
+      <c r="F61" s="91" t="s">
+        <v>955</v>
+      </c>
+      <c r="G61" s="91" t="s">
+        <v>797</v>
+      </c>
+      <c r="H61" s="91" t="s">
+        <v>794</v>
+      </c>
+      <c r="I61" s="91" t="s">
+        <v>925</v>
+      </c>
+      <c r="J61" s="91" t="s">
+        <v>823</v>
+      </c>
+      <c r="K61" s="91" t="s">
+        <v>824</v>
+      </c>
+      <c r="L61" s="91" t="s">
+        <v>825</v>
+      </c>
+      <c r="M61" s="91" t="s">
+        <v>914</v>
+      </c>
+      <c r="N61" s="91" t="s">
+        <v>914</v>
+      </c>
+      <c r="O61" s="91" t="s">
+        <v>914</v>
+      </c>
+      <c r="P61" s="91" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q61" s="91" t="s">
+        <v>830</v>
+      </c>
+      <c r="R61" s="91" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="92" t="s">
+        <v>776</v>
+      </c>
+      <c r="B62" s="92" t="s">
+        <v>777</v>
+      </c>
+      <c r="C62" s="92" t="s">
+        <v>956</v>
+      </c>
+      <c r="D62" s="92" t="s">
+        <v>957</v>
+      </c>
+      <c r="E62" s="92" t="s">
+        <v>958</v>
+      </c>
+      <c r="F62" s="92" t="s">
+        <v>959</v>
+      </c>
+      <c r="G62" s="92" t="s">
+        <v>782</v>
+      </c>
+      <c r="H62" s="92" t="s">
+        <v>778</v>
+      </c>
+      <c r="I62" s="92" t="s">
+        <v>914</v>
+      </c>
+      <c r="J62" s="92" t="s">
+        <v>18</v>
+      </c>
+      <c r="K62" s="92" t="s">
+        <v>785</v>
+      </c>
+      <c r="L62" s="92" t="s">
+        <v>960</v>
+      </c>
+      <c r="M62" s="92" t="s">
+        <v>891</v>
+      </c>
+      <c r="N62" s="92" t="s">
+        <v>815</v>
+      </c>
+      <c r="O62" s="92" t="s">
+        <v>961</v>
+      </c>
+      <c r="P62" s="92" t="s">
+        <v>790</v>
+      </c>
+      <c r="Q62" s="92" t="s">
+        <v>962</v>
+      </c>
+      <c r="R62" s="92" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="92" t="s">
+        <v>776</v>
+      </c>
+      <c r="B63" s="92" t="s">
+        <v>777</v>
+      </c>
+      <c r="C63" s="92" t="s">
+        <v>956</v>
+      </c>
+      <c r="D63" s="92" t="s">
+        <v>964</v>
+      </c>
+      <c r="E63" s="92" t="s">
+        <v>965</v>
+      </c>
+      <c r="F63" s="92" t="s">
+        <v>966</v>
+      </c>
+      <c r="G63" s="92" t="s">
+        <v>782</v>
+      </c>
+      <c r="H63" s="92" t="s">
+        <v>778</v>
+      </c>
+      <c r="I63" s="92" t="s">
+        <v>914</v>
+      </c>
+      <c r="J63" s="92" t="s">
+        <v>890</v>
+      </c>
+      <c r="K63" s="92" t="s">
+        <v>812</v>
+      </c>
+      <c r="L63" s="92" t="s">
+        <v>920</v>
+      </c>
+      <c r="M63" s="92" t="s">
+        <v>967</v>
+      </c>
+      <c r="N63" s="92" t="s">
+        <v>802</v>
+      </c>
+      <c r="O63" s="92" t="s">
+        <v>968</v>
+      </c>
+      <c r="P63" s="92" t="s">
+        <v>817</v>
+      </c>
+      <c r="Q63" s="92" t="s">
+        <v>969</v>
+      </c>
+      <c r="R63" s="92" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="92" t="s">
+        <v>776</v>
+      </c>
+      <c r="B64" s="92" t="s">
+        <v>777</v>
+      </c>
+      <c r="C64" s="92" t="s">
+        <v>971</v>
+      </c>
+      <c r="D64" s="92" t="s">
+        <v>972</v>
+      </c>
+      <c r="E64" s="92" t="s">
+        <v>973</v>
+      </c>
+      <c r="F64" s="92" t="s">
+        <v>974</v>
+      </c>
+      <c r="G64" s="92" t="s">
+        <v>797</v>
+      </c>
+      <c r="H64" s="92" t="s">
+        <v>794</v>
+      </c>
+      <c r="I64" s="92" t="s">
+        <v>914</v>
+      </c>
+      <c r="J64" s="92" t="s">
+        <v>78</v>
+      </c>
+      <c r="K64" s="92" t="s">
+        <v>799</v>
+      </c>
+      <c r="L64" s="92" t="s">
+        <v>975</v>
+      </c>
+      <c r="M64" s="92" t="s">
+        <v>976</v>
+      </c>
+      <c r="N64" s="92" t="s">
+        <v>977</v>
+      </c>
+      <c r="O64" s="92" t="s">
+        <v>978</v>
+      </c>
+      <c r="P64" s="92" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q64" s="92" t="s">
+        <v>979</v>
+      </c>
+      <c r="R64" s="92" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="92" t="s">
+        <v>776</v>
+      </c>
+      <c r="B65" s="92" t="s">
+        <v>777</v>
+      </c>
+      <c r="C65" s="92" t="s">
+        <v>820</v>
+      </c>
+      <c r="D65" s="92" t="s">
+        <v>981</v>
+      </c>
+      <c r="E65" s="92" t="s">
+        <v>982</v>
+      </c>
+      <c r="F65" s="92" t="s">
+        <v>983</v>
+      </c>
+      <c r="G65" s="92" t="s">
+        <v>797</v>
+      </c>
+      <c r="H65" s="92" t="s">
+        <v>794</v>
+      </c>
+      <c r="I65" s="92" t="s">
+        <v>914</v>
+      </c>
+      <c r="J65" s="92" t="s">
+        <v>823</v>
+      </c>
+      <c r="K65" s="92" t="s">
+        <v>824</v>
+      </c>
+      <c r="L65" s="92" t="s">
+        <v>825</v>
+      </c>
+      <c r="M65" s="92" t="s">
+        <v>984</v>
+      </c>
+      <c r="N65" s="92" t="s">
+        <v>827</v>
+      </c>
+      <c r="O65" s="92" t="s">
+        <v>985</v>
+      </c>
+      <c r="P65" s="92" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q65" s="92" t="s">
+        <v>986</v>
+      </c>
+      <c r="R65" s="92" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="92" t="s">
+        <v>776</v>
+      </c>
+      <c r="B66" s="92" t="s">
+        <v>777</v>
+      </c>
+      <c r="C66" s="92" t="s">
+        <v>956</v>
+      </c>
+      <c r="D66" s="92" t="s">
+        <v>988</v>
+      </c>
+      <c r="E66" s="92" t="s">
+        <v>989</v>
+      </c>
+      <c r="F66" s="92" t="s">
+        <v>990</v>
+      </c>
+      <c r="G66" s="92" t="s">
+        <v>782</v>
+      </c>
+      <c r="H66" s="92" t="s">
+        <v>778</v>
+      </c>
+      <c r="I66" s="92" t="s">
+        <v>914</v>
+      </c>
+      <c r="J66" s="92" t="s">
+        <v>835</v>
+      </c>
+      <c r="K66" s="92" t="s">
+        <v>836</v>
+      </c>
+      <c r="L66" s="92" t="s">
+        <v>837</v>
+      </c>
+      <c r="M66" s="92" t="s">
+        <v>991</v>
+      </c>
+      <c r="N66" s="92" t="s">
+        <v>992</v>
+      </c>
+      <c r="O66" s="92" t="s">
+        <v>993</v>
+      </c>
+      <c r="P66" s="92" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q66" s="92" t="s">
+        <v>994</v>
+      </c>
+      <c r="R66" s="92" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="93" t="s">
+        <v>776</v>
+      </c>
+      <c r="B67" s="93" t="s">
+        <v>793</v>
+      </c>
+      <c r="C67" s="93" t="s">
+        <v>909</v>
+      </c>
+      <c r="D67" s="93" t="s">
+        <v>779</v>
+      </c>
+      <c r="E67" s="93" t="s">
+        <v>910</v>
+      </c>
+      <c r="F67" s="93" t="s">
+        <v>996</v>
+      </c>
+      <c r="G67" s="93" t="s">
+        <v>797</v>
+      </c>
+      <c r="H67" s="93" t="s">
+        <v>794</v>
+      </c>
+      <c r="I67" s="93" t="s">
+        <v>912</v>
+      </c>
+      <c r="J67" s="93" t="s">
+        <v>784</v>
+      </c>
+      <c r="K67" s="93" t="s">
+        <v>785</v>
+      </c>
+      <c r="L67" s="93" t="s">
+        <v>913</v>
+      </c>
+      <c r="M67" s="93" t="s">
+        <v>914</v>
+      </c>
+      <c r="N67" s="93" t="s">
+        <v>914</v>
+      </c>
+      <c r="O67" s="93" t="s">
+        <v>914</v>
+      </c>
+      <c r="P67" s="93" t="s">
+        <v>790</v>
+      </c>
+      <c r="Q67" s="93" t="s">
+        <v>791</v>
+      </c>
+      <c r="R67" s="93" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="93" t="s">
+        <v>776</v>
+      </c>
+      <c r="B68" s="93" t="s">
+        <v>793</v>
+      </c>
+      <c r="C68" s="93" t="s">
+        <v>909</v>
+      </c>
+      <c r="D68" s="93" t="s">
+        <v>779</v>
+      </c>
+      <c r="E68" s="93" t="s">
+        <v>910</v>
+      </c>
+      <c r="F68" s="93" t="s">
+        <v>997</v>
+      </c>
+      <c r="G68" s="93" t="s">
+        <v>797</v>
+      </c>
+      <c r="H68" s="93" t="s">
+        <v>794</v>
+      </c>
+      <c r="I68" s="93" t="s">
+        <v>916</v>
+      </c>
+      <c r="J68" s="93" t="s">
+        <v>78</v>
+      </c>
+      <c r="K68" s="93" t="s">
+        <v>799</v>
+      </c>
+      <c r="L68" s="93" t="s">
+        <v>917</v>
+      </c>
+      <c r="M68" s="93" t="s">
+        <v>914</v>
+      </c>
+      <c r="N68" s="93" t="s">
+        <v>914</v>
+      </c>
+      <c r="O68" s="93" t="s">
+        <v>914</v>
+      </c>
+      <c r="P68" s="93" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q68" s="93" t="s">
+        <v>805</v>
+      </c>
+      <c r="R68" s="93" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="93" t="s">
+        <v>776</v>
+      </c>
+      <c r="B69" s="93" t="s">
+        <v>793</v>
+      </c>
+      <c r="C69" s="93" t="s">
+        <v>909</v>
+      </c>
+      <c r="D69" s="93" t="s">
+        <v>779</v>
+      </c>
+      <c r="E69" s="93" t="s">
+        <v>910</v>
+      </c>
+      <c r="F69" s="93" t="s">
+        <v>998</v>
+      </c>
+      <c r="G69" s="93" t="s">
+        <v>797</v>
+      </c>
+      <c r="H69" s="93" t="s">
+        <v>794</v>
+      </c>
+      <c r="I69" s="93" t="s">
+        <v>919</v>
+      </c>
+      <c r="J69" s="93" t="s">
+        <v>811</v>
+      </c>
+      <c r="K69" s="93" t="s">
+        <v>812</v>
+      </c>
+      <c r="L69" s="93" t="s">
+        <v>920</v>
+      </c>
+      <c r="M69" s="93" t="s">
+        <v>914</v>
+      </c>
+      <c r="N69" s="93" t="s">
+        <v>914</v>
+      </c>
+      <c r="O69" s="93" t="s">
+        <v>914</v>
+      </c>
+      <c r="P69" s="93" t="s">
+        <v>817</v>
+      </c>
+      <c r="Q69" s="93" t="s">
+        <v>818</v>
+      </c>
+      <c r="R69" s="93" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="93" t="s">
+        <v>776</v>
+      </c>
+      <c r="B70" s="93" t="s">
+        <v>793</v>
+      </c>
+      <c r="C70" s="93" t="s">
+        <v>909</v>
+      </c>
+      <c r="D70" s="93" t="s">
+        <v>779</v>
+      </c>
+      <c r="E70" s="93" t="s">
+        <v>910</v>
+      </c>
+      <c r="F70" s="93" t="s">
+        <v>999</v>
+      </c>
+      <c r="G70" s="93" t="s">
+        <v>797</v>
+      </c>
+      <c r="H70" s="93" t="s">
+        <v>794</v>
+      </c>
+      <c r="I70" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="J70" s="93" t="s">
+        <v>835</v>
+      </c>
+      <c r="K70" s="93" t="s">
+        <v>836</v>
+      </c>
+      <c r="L70" s="93" t="s">
+        <v>837</v>
+      </c>
+      <c r="M70" s="93" t="s">
+        <v>914</v>
+      </c>
+      <c r="N70" s="93" t="s">
+        <v>914</v>
+      </c>
+      <c r="O70" s="93" t="s">
+        <v>914</v>
+      </c>
+      <c r="P70" s="93" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q70" s="93" t="s">
+        <v>923</v>
+      </c>
+      <c r="R70" s="93" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="93" t="s">
+        <v>776</v>
+      </c>
+      <c r="B71" s="93" t="s">
+        <v>793</v>
+      </c>
+      <c r="C71" s="93" t="s">
+        <v>909</v>
+      </c>
+      <c r="D71" s="93" t="s">
+        <v>779</v>
+      </c>
+      <c r="E71" s="93" t="s">
+        <v>910</v>
+      </c>
+      <c r="F71" s="93" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G71" s="93" t="s">
+        <v>797</v>
+      </c>
+      <c r="H71" s="93" t="s">
+        <v>794</v>
+      </c>
+      <c r="I71" s="93" t="s">
+        <v>925</v>
+      </c>
+      <c r="J71" s="93" t="s">
+        <v>823</v>
+      </c>
+      <c r="K71" s="93" t="s">
+        <v>824</v>
+      </c>
+      <c r="L71" s="93" t="s">
+        <v>825</v>
+      </c>
+      <c r="M71" s="93" t="s">
+        <v>914</v>
+      </c>
+      <c r="N71" s="93" t="s">
+        <v>914</v>
+      </c>
+      <c r="O71" s="93" t="s">
+        <v>914</v>
+      </c>
+      <c r="P71" s="93" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q71" s="93" t="s">
+        <v>830</v>
+      </c>
+      <c r="R71" s="93" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="94" t="s">
+        <v>776</v>
+      </c>
+      <c r="B72" s="94" t="s">
+        <v>777</v>
+      </c>
+      <c r="C72" s="94" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D72" s="94" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E72" s="94" t="s">
+        <v>958</v>
+      </c>
+      <c r="F72" s="94" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G72" s="94" t="s">
+        <v>782</v>
+      </c>
+      <c r="H72" s="94" t="s">
+        <v>778</v>
+      </c>
+      <c r="I72" s="94" t="s">
+        <v>914</v>
+      </c>
+      <c r="J72" s="94" t="s">
+        <v>18</v>
+      </c>
+      <c r="K72" s="94" t="s">
+        <v>785</v>
+      </c>
+      <c r="L72" s="94" t="s">
+        <v>875</v>
+      </c>
+      <c r="M72" s="94" t="s">
+        <v>891</v>
+      </c>
+      <c r="N72" s="94" t="s">
+        <v>815</v>
+      </c>
+      <c r="O72" s="94" t="s">
+        <v>961</v>
+      </c>
+      <c r="P72" s="94" t="s">
+        <v>876</v>
+      </c>
+      <c r="Q72" s="94" t="s">
+        <v>1004</v>
+      </c>
+      <c r="R72" s="94" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="94" t="s">
+        <v>776</v>
+      </c>
+      <c r="B73" s="94" t="s">
+        <v>777</v>
+      </c>
+      <c r="C73" s="94" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D73" s="94" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E73" s="94" t="s">
+        <v>964</v>
+      </c>
+      <c r="F73" s="94" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G73" s="94" t="s">
+        <v>782</v>
+      </c>
+      <c r="H73" s="94" t="s">
+        <v>778</v>
+      </c>
+      <c r="I73" s="94" t="s">
+        <v>914</v>
+      </c>
+      <c r="J73" s="94" t="s">
+        <v>890</v>
+      </c>
+      <c r="K73" s="94" t="s">
+        <v>812</v>
+      </c>
+      <c r="L73" s="94" t="s">
+        <v>920</v>
+      </c>
+      <c r="M73" s="94" t="s">
+        <v>967</v>
+      </c>
+      <c r="N73" s="94" t="s">
+        <v>802</v>
+      </c>
+      <c r="O73" s="94" t="s">
+        <v>968</v>
+      </c>
+      <c r="P73" s="94" t="s">
+        <v>817</v>
+      </c>
+      <c r="Q73" s="94" t="s">
+        <v>1008</v>
+      </c>
+      <c r="R73" s="94" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="94" t="s">
+        <v>776</v>
+      </c>
+      <c r="B74" s="94" t="s">
+        <v>777</v>
+      </c>
+      <c r="C74" s="94" t="s">
+        <v>797</v>
+      </c>
+      <c r="D74" s="94" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E74" s="94" t="s">
+        <v>972</v>
+      </c>
+      <c r="F74" s="94" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G74" s="94" t="s">
+        <v>797</v>
+      </c>
+      <c r="H74" s="94" t="s">
+        <v>794</v>
+      </c>
+      <c r="I74" s="94" t="s">
+        <v>914</v>
+      </c>
+      <c r="J74" s="94" t="s">
+        <v>78</v>
+      </c>
+      <c r="K74" s="94" t="s">
+        <v>799</v>
+      </c>
+      <c r="L74" s="94" t="s">
+        <v>975</v>
+      </c>
+      <c r="M74" s="94" t="s">
+        <v>976</v>
+      </c>
+      <c r="N74" s="94" t="s">
+        <v>977</v>
+      </c>
+      <c r="O74" s="94" t="s">
+        <v>978</v>
+      </c>
+      <c r="P74" s="94" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q74" s="94" t="s">
+        <v>1012</v>
+      </c>
+      <c r="R74" s="94" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="94" t="s">
+        <v>776</v>
+      </c>
+      <c r="B75" s="94" t="s">
+        <v>777</v>
+      </c>
+      <c r="C75" s="94" t="s">
+        <v>797</v>
+      </c>
+      <c r="D75" s="94" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E75" s="94" t="s">
+        <v>981</v>
+      </c>
+      <c r="F75" s="94" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G75" s="94" t="s">
+        <v>797</v>
+      </c>
+      <c r="H75" s="94" t="s">
+        <v>794</v>
+      </c>
+      <c r="I75" s="94" t="s">
+        <v>914</v>
+      </c>
+      <c r="J75" s="94" t="s">
+        <v>823</v>
+      </c>
+      <c r="K75" s="94" t="s">
+        <v>824</v>
+      </c>
+      <c r="L75" s="94" t="s">
+        <v>825</v>
+      </c>
+      <c r="M75" s="94" t="s">
+        <v>984</v>
+      </c>
+      <c r="N75" s="94" t="s">
+        <v>827</v>
+      </c>
+      <c r="O75" s="94" t="s">
+        <v>985</v>
+      </c>
+      <c r="P75" s="94" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q75" s="94" t="s">
+        <v>1016</v>
+      </c>
+      <c r="R75" s="94" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="94" t="s">
+        <v>776</v>
+      </c>
+      <c r="B76" s="94" t="s">
+        <v>777</v>
+      </c>
+      <c r="C76" s="94" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D76" s="94" t="s">
+        <v>988</v>
+      </c>
+      <c r="E76" s="94" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F76" s="94" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G76" s="94" t="s">
+        <v>782</v>
+      </c>
+      <c r="H76" s="94" t="s">
+        <v>778</v>
+      </c>
+      <c r="I76" s="94" t="s">
+        <v>914</v>
+      </c>
+      <c r="J76" s="94" t="s">
+        <v>835</v>
+      </c>
+      <c r="K76" s="94" t="s">
+        <v>836</v>
+      </c>
+      <c r="L76" s="94" t="s">
+        <v>837</v>
+      </c>
+      <c r="M76" s="94" t="s">
+        <v>1020</v>
+      </c>
+      <c r="N76" s="94" t="s">
+        <v>1021</v>
+      </c>
+      <c r="O76" s="94" t="s">
+        <v>1022</v>
+      </c>
+      <c r="P76" s="94" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q76" s="94" t="s">
+        <v>1023</v>
+      </c>
+      <c r="R76" s="94" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="95" t="s">
+        <v>776</v>
+      </c>
+      <c r="B77" s="95" t="s">
+        <v>777</v>
+      </c>
+      <c r="C77" s="95" t="s">
+        <v>956</v>
+      </c>
+      <c r="D77" s="95" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E77" s="95" t="s">
+        <v>958</v>
+      </c>
+      <c r="F77" s="95" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G77" s="95" t="s">
+        <v>782</v>
+      </c>
+      <c r="H77" s="95" t="s">
+        <v>778</v>
+      </c>
+      <c r="I77" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="J77" s="95" t="s">
+        <v>18</v>
+      </c>
+      <c r="K77" s="95" t="s">
+        <v>785</v>
+      </c>
+      <c r="L77" s="95" t="s">
+        <v>913</v>
+      </c>
+      <c r="M77" s="95" t="s">
+        <v>891</v>
+      </c>
+      <c r="N77" s="95" t="s">
+        <v>815</v>
+      </c>
+      <c r="O77" s="95" t="s">
+        <v>961</v>
+      </c>
+      <c r="P77" s="95" t="s">
+        <v>790</v>
+      </c>
+      <c r="Q77" s="95" t="s">
+        <v>1026</v>
+      </c>
+      <c r="R77" s="95" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="95" t="s">
+        <v>776</v>
+      </c>
+      <c r="B78" s="95" t="s">
+        <v>777</v>
+      </c>
+      <c r="C78" s="95" t="s">
+        <v>956</v>
+      </c>
+      <c r="D78" s="95" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E78" s="95" t="s">
+        <v>964</v>
+      </c>
+      <c r="F78" s="95" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G78" s="95" t="s">
+        <v>782</v>
+      </c>
+      <c r="H78" s="95" t="s">
+        <v>778</v>
+      </c>
+      <c r="I78" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="J78" s="95" t="s">
+        <v>890</v>
+      </c>
+      <c r="K78" s="95" t="s">
+        <v>812</v>
+      </c>
+      <c r="L78" s="95" t="s">
+        <v>920</v>
+      </c>
+      <c r="M78" s="95" t="s">
+        <v>967</v>
+      </c>
+      <c r="N78" s="95" t="s">
+        <v>802</v>
+      </c>
+      <c r="O78" s="95" t="s">
+        <v>968</v>
+      </c>
+      <c r="P78" s="95" t="s">
+        <v>817</v>
+      </c>
+      <c r="Q78" s="95" t="s">
+        <v>1030</v>
+      </c>
+      <c r="R78" s="95" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="95" t="s">
+        <v>776</v>
+      </c>
+      <c r="B79" s="95" t="s">
+        <v>777</v>
+      </c>
+      <c r="C79" s="95" t="s">
+        <v>971</v>
+      </c>
+      <c r="D79" s="95" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E79" s="95" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F79" s="95" t="s">
+        <v>1033</v>
+      </c>
+      <c r="G79" s="95" t="s">
+        <v>797</v>
+      </c>
+      <c r="H79" s="95" t="s">
+        <v>794</v>
+      </c>
+      <c r="I79" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="J79" s="95" t="s">
+        <v>78</v>
+      </c>
+      <c r="K79" s="95" t="s">
+        <v>799</v>
+      </c>
+      <c r="L79" s="95" t="s">
+        <v>975</v>
+      </c>
+      <c r="M79" s="95" t="s">
+        <v>976</v>
+      </c>
+      <c r="N79" s="95" t="s">
+        <v>977</v>
+      </c>
+      <c r="O79" s="95" t="s">
+        <v>978</v>
+      </c>
+      <c r="P79" s="95" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q79" s="95" t="s">
+        <v>1034</v>
+      </c>
+      <c r="R79" s="95" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="95" t="s">
+        <v>776</v>
+      </c>
+      <c r="B80" s="95" t="s">
+        <v>777</v>
+      </c>
+      <c r="C80" s="95" t="s">
+        <v>820</v>
+      </c>
+      <c r="D80" s="95" t="s">
+        <v>981</v>
+      </c>
+      <c r="E80" s="95" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F80" s="95" t="s">
+        <v>1037</v>
+      </c>
+      <c r="G80" s="95" t="s">
+        <v>797</v>
+      </c>
+      <c r="H80" s="95" t="s">
+        <v>794</v>
+      </c>
+      <c r="I80" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="J80" s="95" t="s">
+        <v>823</v>
+      </c>
+      <c r="K80" s="95" t="s">
+        <v>824</v>
+      </c>
+      <c r="L80" s="95" t="s">
+        <v>825</v>
+      </c>
+      <c r="M80" s="95" t="s">
+        <v>984</v>
+      </c>
+      <c r="N80" s="95" t="s">
+        <v>827</v>
+      </c>
+      <c r="O80" s="95" t="s">
+        <v>985</v>
+      </c>
+      <c r="P80" s="95" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q80" s="95" t="s">
+        <v>1038</v>
+      </c>
+      <c r="R80" s="95" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="95" t="s">
+        <v>776</v>
+      </c>
+      <c r="B81" s="95" t="s">
+        <v>777</v>
+      </c>
+      <c r="C81" s="95" t="s">
+        <v>956</v>
+      </c>
+      <c r="D81" s="95" t="s">
+        <v>988</v>
+      </c>
+      <c r="E81" s="95" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F81" s="95" t="s">
+        <v>1039</v>
+      </c>
+      <c r="G81" s="95" t="s">
+        <v>782</v>
+      </c>
+      <c r="H81" s="95" t="s">
+        <v>778</v>
+      </c>
+      <c r="I81" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="J81" s="95" t="s">
+        <v>835</v>
+      </c>
+      <c r="K81" s="95" t="s">
+        <v>836</v>
+      </c>
+      <c r="L81" s="95" t="s">
+        <v>837</v>
+      </c>
+      <c r="M81" s="95" t="s">
+        <v>991</v>
+      </c>
+      <c r="N81" s="95" t="s">
+        <v>992</v>
+      </c>
+      <c r="O81" s="95" t="s">
+        <v>993</v>
+      </c>
+      <c r="P81" s="95" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q81" s="95" t="s">
+        <v>1040</v>
+      </c>
+      <c r="R81" s="95" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="96" t="s">
+        <v>776</v>
+      </c>
+      <c r="B82" s="96" t="s">
+        <v>793</v>
+      </c>
+      <c r="C82" s="96" t="s">
+        <v>909</v>
+      </c>
+      <c r="D82" s="96" t="s">
+        <v>779</v>
+      </c>
+      <c r="E82" s="96" t="s">
+        <v>910</v>
+      </c>
+      <c r="F82" s="96" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G82" s="96" t="s">
+        <v>797</v>
+      </c>
+      <c r="H82" s="96" t="s">
+        <v>794</v>
+      </c>
+      <c r="I82" s="96" t="s">
+        <v>912</v>
+      </c>
+      <c r="J82" s="96" t="s">
+        <v>784</v>
+      </c>
+      <c r="K82" s="96" t="s">
+        <v>785</v>
+      </c>
+      <c r="L82" s="96" t="s">
+        <v>913</v>
+      </c>
+      <c r="M82" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="N82" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="O82" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="P82" s="96" t="s">
+        <v>790</v>
+      </c>
+      <c r="Q82" s="96" t="s">
+        <v>791</v>
+      </c>
+      <c r="R82" s="96" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="96" t="s">
+        <v>776</v>
+      </c>
+      <c r="B83" s="96" t="s">
+        <v>793</v>
+      </c>
+      <c r="C83" s="96" t="s">
+        <v>909</v>
+      </c>
+      <c r="D83" s="96" t="s">
+        <v>779</v>
+      </c>
+      <c r="E83" s="96" t="s">
+        <v>910</v>
+      </c>
+      <c r="F83" s="96" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G83" s="96" t="s">
+        <v>797</v>
+      </c>
+      <c r="H83" s="96" t="s">
+        <v>794</v>
+      </c>
+      <c r="I83" s="96" t="s">
+        <v>916</v>
+      </c>
+      <c r="J83" s="96" t="s">
+        <v>78</v>
+      </c>
+      <c r="K83" s="96" t="s">
+        <v>799</v>
+      </c>
+      <c r="L83" s="96" t="s">
+        <v>917</v>
+      </c>
+      <c r="M83" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="N83" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="O83" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="P83" s="96" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q83" s="96" t="s">
+        <v>805</v>
+      </c>
+      <c r="R83" s="96" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="96" t="s">
+        <v>776</v>
+      </c>
+      <c r="B84" s="96" t="s">
+        <v>793</v>
+      </c>
+      <c r="C84" s="96" t="s">
+        <v>909</v>
+      </c>
+      <c r="D84" s="96" t="s">
+        <v>779</v>
+      </c>
+      <c r="E84" s="96" t="s">
+        <v>910</v>
+      </c>
+      <c r="F84" s="96" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G84" s="96" t="s">
+        <v>797</v>
+      </c>
+      <c r="H84" s="96" t="s">
+        <v>794</v>
+      </c>
+      <c r="I84" s="96" t="s">
+        <v>919</v>
+      </c>
+      <c r="J84" s="96" t="s">
+        <v>811</v>
+      </c>
+      <c r="K84" s="96" t="s">
+        <v>812</v>
+      </c>
+      <c r="L84" s="96" t="s">
+        <v>920</v>
+      </c>
+      <c r="M84" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="N84" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="O84" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="P84" s="96" t="s">
+        <v>817</v>
+      </c>
+      <c r="Q84" s="96" t="s">
+        <v>818</v>
+      </c>
+      <c r="R84" s="96" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="96" t="s">
+        <v>776</v>
+      </c>
+      <c r="B85" s="96" t="s">
+        <v>793</v>
+      </c>
+      <c r="C85" s="96" t="s">
+        <v>909</v>
+      </c>
+      <c r="D85" s="96" t="s">
+        <v>779</v>
+      </c>
+      <c r="E85" s="96" t="s">
+        <v>910</v>
+      </c>
+      <c r="F85" s="96" t="s">
+        <v>1044</v>
+      </c>
+      <c r="G85" s="96" t="s">
+        <v>797</v>
+      </c>
+      <c r="H85" s="96" t="s">
+        <v>794</v>
+      </c>
+      <c r="I85" s="96" t="s">
+        <v>922</v>
+      </c>
+      <c r="J85" s="96" t="s">
+        <v>835</v>
+      </c>
+      <c r="K85" s="96" t="s">
+        <v>836</v>
+      </c>
+      <c r="L85" s="96" t="s">
+        <v>837</v>
+      </c>
+      <c r="M85" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="N85" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="O85" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="P85" s="96" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q85" s="96" t="s">
+        <v>923</v>
+      </c>
+      <c r="R85" s="96" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="96" t="s">
+        <v>776</v>
+      </c>
+      <c r="B86" s="96" t="s">
+        <v>793</v>
+      </c>
+      <c r="C86" s="96" t="s">
+        <v>909</v>
+      </c>
+      <c r="D86" s="96" t="s">
+        <v>779</v>
+      </c>
+      <c r="E86" s="96" t="s">
+        <v>910</v>
+      </c>
+      <c r="F86" s="96" t="s">
+        <v>1045</v>
+      </c>
+      <c r="G86" s="96" t="s">
+        <v>797</v>
+      </c>
+      <c r="H86" s="96" t="s">
+        <v>794</v>
+      </c>
+      <c r="I86" s="96" t="s">
+        <v>925</v>
+      </c>
+      <c r="J86" s="96" t="s">
+        <v>823</v>
+      </c>
+      <c r="K86" s="96" t="s">
+        <v>824</v>
+      </c>
+      <c r="L86" s="96" t="s">
+        <v>825</v>
+      </c>
+      <c r="M86" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="N86" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="O86" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="P86" s="96" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q86" s="96" t="s">
+        <v>830</v>
+      </c>
+      <c r="R86" s="96" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="97" t="s">
+        <v>776</v>
+      </c>
+      <c r="B87" s="97" t="s">
+        <v>777</v>
+      </c>
+      <c r="C87" s="97" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D87" s="97" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E87" s="97" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F87" s="97" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G87" s="97" t="s">
+        <v>782</v>
+      </c>
+      <c r="H87" s="97" t="s">
+        <v>778</v>
+      </c>
+      <c r="I87" s="97" t="s">
+        <v>914</v>
+      </c>
+      <c r="J87" s="97" t="s">
+        <v>18</v>
+      </c>
+      <c r="K87" s="97" t="s">
+        <v>785</v>
+      </c>
+      <c r="L87" s="97" t="s">
+        <v>913</v>
+      </c>
+      <c r="M87" s="97" t="s">
+        <v>891</v>
+      </c>
+      <c r="N87" s="97" t="s">
+        <v>815</v>
+      </c>
+      <c r="O87" s="97" t="s">
+        <v>961</v>
+      </c>
+      <c r="P87" s="97" t="s">
+        <v>790</v>
+      </c>
+      <c r="Q87" s="97" t="s">
+        <v>962</v>
+      </c>
+      <c r="R87" s="97" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="97" t="s">
+        <v>776</v>
+      </c>
+      <c r="B88" s="97" t="s">
+        <v>777</v>
+      </c>
+      <c r="C88" s="97" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D88" s="97" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E88" s="97" t="s">
+        <v>964</v>
+      </c>
+      <c r="F88" s="97" t="s">
+        <v>1050</v>
+      </c>
+      <c r="G88" s="97" t="s">
+        <v>782</v>
+      </c>
+      <c r="H88" s="97" t="s">
+        <v>778</v>
+      </c>
+      <c r="I88" s="97" t="s">
+        <v>914</v>
+      </c>
+      <c r="J88" s="97" t="s">
+        <v>890</v>
+      </c>
+      <c r="K88" s="97" t="s">
+        <v>812</v>
+      </c>
+      <c r="L88" s="97" t="s">
+        <v>920</v>
+      </c>
+      <c r="M88" s="97" t="s">
+        <v>967</v>
+      </c>
+      <c r="N88" s="97" t="s">
+        <v>802</v>
+      </c>
+      <c r="O88" s="97" t="s">
+        <v>968</v>
+      </c>
+      <c r="P88" s="97" t="s">
+        <v>817</v>
+      </c>
+      <c r="Q88" s="97" t="s">
+        <v>969</v>
+      </c>
+      <c r="R88" s="97" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="97" t="s">
+        <v>776</v>
+      </c>
+      <c r="B89" s="97" t="s">
+        <v>777</v>
+      </c>
+      <c r="C89" s="97" t="s">
+        <v>797</v>
+      </c>
+      <c r="D89" s="97" t="s">
+        <v>794</v>
+      </c>
+      <c r="E89" s="97" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F89" s="97" t="s">
+        <v>1051</v>
+      </c>
+      <c r="G89" s="97" t="s">
+        <v>797</v>
+      </c>
+      <c r="H89" s="97" t="s">
+        <v>794</v>
+      </c>
+      <c r="I89" s="97" t="s">
+        <v>914</v>
+      </c>
+      <c r="J89" s="97" t="s">
+        <v>78</v>
+      </c>
+      <c r="K89" s="97" t="s">
+        <v>799</v>
+      </c>
+      <c r="L89" s="97" t="s">
+        <v>975</v>
+      </c>
+      <c r="M89" s="97" t="s">
+        <v>976</v>
+      </c>
+      <c r="N89" s="97" t="s">
+        <v>977</v>
+      </c>
+      <c r="O89" s="97" t="s">
+        <v>978</v>
+      </c>
+      <c r="P89" s="97" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q89" s="97" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R89" s="97" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="97" t="s">
+        <v>776</v>
+      </c>
+      <c r="B90" s="97" t="s">
+        <v>777</v>
+      </c>
+      <c r="C90" s="97" t="s">
+        <v>797</v>
+      </c>
+      <c r="D90" s="97" t="s">
+        <v>820</v>
+      </c>
+      <c r="E90" s="97" t="s">
+        <v>981</v>
+      </c>
+      <c r="F90" s="97" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G90" s="97" t="s">
+        <v>797</v>
+      </c>
+      <c r="H90" s="97" t="s">
+        <v>794</v>
+      </c>
+      <c r="I90" s="97" t="s">
+        <v>914</v>
+      </c>
+      <c r="J90" s="97" t="s">
+        <v>823</v>
+      </c>
+      <c r="K90" s="97" t="s">
+        <v>824</v>
+      </c>
+      <c r="L90" s="97" t="s">
+        <v>825</v>
+      </c>
+      <c r="M90" s="97" t="s">
+        <v>984</v>
+      </c>
+      <c r="N90" s="97" t="s">
+        <v>827</v>
+      </c>
+      <c r="O90" s="97" t="s">
+        <v>985</v>
+      </c>
+      <c r="P90" s="97" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q90" s="97" t="s">
+        <v>1055</v>
+      </c>
+      <c r="R90" s="97" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="97" t="s">
+        <v>776</v>
+      </c>
+      <c r="B91" s="97" t="s">
+        <v>777</v>
+      </c>
+      <c r="C91" s="97" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D91" s="97" t="s">
+        <v>988</v>
+      </c>
+      <c r="E91" s="97" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F91" s="97" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G91" s="97" t="s">
+        <v>782</v>
+      </c>
+      <c r="H91" s="97" t="s">
+        <v>778</v>
+      </c>
+      <c r="I91" s="97" t="s">
+        <v>914</v>
+      </c>
+      <c r="J91" s="97" t="s">
+        <v>835</v>
+      </c>
+      <c r="K91" s="97" t="s">
+        <v>836</v>
+      </c>
+      <c r="L91" s="97" t="s">
+        <v>837</v>
+      </c>
+      <c r="M91" s="97" t="s">
+        <v>1020</v>
+      </c>
+      <c r="N91" s="97" t="s">
+        <v>1021</v>
+      </c>
+      <c r="O91" s="97" t="s">
+        <v>1022</v>
+      </c>
+      <c r="P91" s="97" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q91" s="97" t="s">
+        <v>994</v>
+      </c>
+      <c r="R91" s="97" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="98" t="s">
+        <v>776</v>
+      </c>
+      <c r="B92" s="98" t="s">
+        <v>793</v>
+      </c>
+      <c r="C92" s="98" t="s">
+        <v>909</v>
+      </c>
+      <c r="D92" s="98" t="s">
+        <v>779</v>
+      </c>
+      <c r="E92" s="98" t="s">
+        <v>910</v>
+      </c>
+      <c r="F92" s="98" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G92" s="98" t="s">
+        <v>797</v>
+      </c>
+      <c r="H92" s="98" t="s">
+        <v>794</v>
+      </c>
+      <c r="I92" s="98" t="s">
+        <v>912</v>
+      </c>
+      <c r="J92" s="98" t="s">
+        <v>784</v>
+      </c>
+      <c r="K92" s="98" t="s">
+        <v>785</v>
+      </c>
+      <c r="L92" s="98" t="s">
+        <v>913</v>
+      </c>
+      <c r="M92" s="98" t="s">
+        <v>914</v>
+      </c>
+      <c r="N92" s="98" t="s">
+        <v>914</v>
+      </c>
+      <c r="O92" s="98" t="s">
+        <v>914</v>
+      </c>
+      <c r="P92" s="98" t="s">
+        <v>790</v>
+      </c>
+      <c r="Q92" s="98" t="s">
+        <v>791</v>
+      </c>
+      <c r="R92" s="98" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="98" t="s">
+        <v>776</v>
+      </c>
+      <c r="B93" s="98" t="s">
+        <v>793</v>
+      </c>
+      <c r="C93" s="98" t="s">
+        <v>909</v>
+      </c>
+      <c r="D93" s="98" t="s">
+        <v>779</v>
+      </c>
+      <c r="E93" s="98" t="s">
+        <v>910</v>
+      </c>
+      <c r="F93" s="98" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G93" s="98" t="s">
+        <v>797</v>
+      </c>
+      <c r="H93" s="98" t="s">
+        <v>794</v>
+      </c>
+      <c r="I93" s="98" t="s">
+        <v>916</v>
+      </c>
+      <c r="J93" s="98" t="s">
+        <v>78</v>
+      </c>
+      <c r="K93" s="98" t="s">
+        <v>799</v>
+      </c>
+      <c r="L93" s="98" t="s">
+        <v>917</v>
+      </c>
+      <c r="M93" s="98" t="s">
+        <v>914</v>
+      </c>
+      <c r="N93" s="98" t="s">
+        <v>914</v>
+      </c>
+      <c r="O93" s="98" t="s">
+        <v>914</v>
+      </c>
+      <c r="P93" s="98" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q93" s="98" t="s">
+        <v>805</v>
+      </c>
+      <c r="R93" s="98" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="98" t="s">
+        <v>776</v>
+      </c>
+      <c r="B94" s="98" t="s">
+        <v>793</v>
+      </c>
+      <c r="C94" s="98" t="s">
+        <v>909</v>
+      </c>
+      <c r="D94" s="98" t="s">
+        <v>779</v>
+      </c>
+      <c r="E94" s="98" t="s">
+        <v>910</v>
+      </c>
+      <c r="F94" s="98" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G94" s="98" t="s">
+        <v>797</v>
+      </c>
+      <c r="H94" s="98" t="s">
+        <v>794</v>
+      </c>
+      <c r="I94" s="98" t="s">
+        <v>919</v>
+      </c>
+      <c r="J94" s="98" t="s">
+        <v>811</v>
+      </c>
+      <c r="K94" s="98" t="s">
+        <v>812</v>
+      </c>
+      <c r="L94" s="98" t="s">
+        <v>920</v>
+      </c>
+      <c r="M94" s="98" t="s">
+        <v>914</v>
+      </c>
+      <c r="N94" s="98" t="s">
+        <v>914</v>
+      </c>
+      <c r="O94" s="98" t="s">
+        <v>914</v>
+      </c>
+      <c r="P94" s="98" t="s">
+        <v>817</v>
+      </c>
+      <c r="Q94" s="98" t="s">
+        <v>818</v>
+      </c>
+      <c r="R94" s="98" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="98" t="s">
+        <v>776</v>
+      </c>
+      <c r="B95" s="98" t="s">
+        <v>793</v>
+      </c>
+      <c r="C95" s="98" t="s">
+        <v>909</v>
+      </c>
+      <c r="D95" s="98" t="s">
+        <v>779</v>
+      </c>
+      <c r="E95" s="98" t="s">
+        <v>910</v>
+      </c>
+      <c r="F95" s="98" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G95" s="98" t="s">
+        <v>797</v>
+      </c>
+      <c r="H95" s="98" t="s">
+        <v>794</v>
+      </c>
+      <c r="I95" s="98" t="s">
+        <v>922</v>
+      </c>
+      <c r="J95" s="98" t="s">
+        <v>835</v>
+      </c>
+      <c r="K95" s="98" t="s">
+        <v>836</v>
+      </c>
+      <c r="L95" s="98" t="s">
+        <v>837</v>
+      </c>
+      <c r="M95" s="98" t="s">
+        <v>914</v>
+      </c>
+      <c r="N95" s="98" t="s">
+        <v>914</v>
+      </c>
+      <c r="O95" s="98" t="s">
+        <v>914</v>
+      </c>
+      <c r="P95" s="98" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q95" s="98" t="s">
+        <v>923</v>
+      </c>
+      <c r="R95" s="98" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="98" t="s">
+        <v>776</v>
+      </c>
+      <c r="B96" s="98" t="s">
+        <v>793</v>
+      </c>
+      <c r="C96" s="98" t="s">
+        <v>909</v>
+      </c>
+      <c r="D96" s="98" t="s">
+        <v>779</v>
+      </c>
+      <c r="E96" s="98" t="s">
+        <v>910</v>
+      </c>
+      <c r="F96" s="98" t="s">
+        <v>1063</v>
+      </c>
+      <c r="G96" s="98" t="s">
+        <v>797</v>
+      </c>
+      <c r="H96" s="98" t="s">
+        <v>794</v>
+      </c>
+      <c r="I96" s="98" t="s">
+        <v>925</v>
+      </c>
+      <c r="J96" s="98" t="s">
+        <v>823</v>
+      </c>
+      <c r="K96" s="98" t="s">
+        <v>824</v>
+      </c>
+      <c r="L96" s="98" t="s">
+        <v>825</v>
+      </c>
+      <c r="M96" s="98" t="s">
+        <v>914</v>
+      </c>
+      <c r="N96" s="98" t="s">
+        <v>914</v>
+      </c>
+      <c r="O96" s="98" t="s">
+        <v>914</v>
+      </c>
+      <c r="P96" s="98" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q96" s="98" t="s">
+        <v>830</v>
+      </c>
+      <c r="R96" s="98" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="99" t="s">
+        <v>776</v>
+      </c>
+      <c r="B97" s="99" t="s">
+        <v>777</v>
+      </c>
+      <c r="C97" s="99" t="s">
+        <v>956</v>
+      </c>
+      <c r="D97" s="99" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E97" s="99" t="s">
+        <v>958</v>
+      </c>
+      <c r="F97" s="99" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G97" s="99" t="s">
+        <v>782</v>
+      </c>
+      <c r="H97" s="99" t="s">
+        <v>778</v>
+      </c>
+      <c r="I97" s="99" t="s">
+        <v>914</v>
+      </c>
+      <c r="J97" s="99" t="s">
+        <v>18</v>
+      </c>
+      <c r="K97" s="99" t="s">
+        <v>785</v>
+      </c>
+      <c r="L97" s="99" t="s">
+        <v>875</v>
+      </c>
+      <c r="M97" s="99" t="s">
+        <v>891</v>
+      </c>
+      <c r="N97" s="99" t="s">
+        <v>815</v>
+      </c>
+      <c r="O97" s="99" t="s">
+        <v>961</v>
+      </c>
+      <c r="P97" s="99" t="s">
+        <v>876</v>
+      </c>
+      <c r="Q97" s="99" t="s">
+        <v>1004</v>
+      </c>
+      <c r="R97" s="99" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="99" t="s">
+        <v>776</v>
+      </c>
+      <c r="B98" s="99" t="s">
+        <v>777</v>
+      </c>
+      <c r="C98" s="99" t="s">
+        <v>956</v>
+      </c>
+      <c r="D98" s="99" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E98" s="99" t="s">
+        <v>964</v>
+      </c>
+      <c r="F98" s="99" t="s">
+        <v>1066</v>
+      </c>
+      <c r="G98" s="99" t="s">
+        <v>782</v>
+      </c>
+      <c r="H98" s="99" t="s">
+        <v>778</v>
+      </c>
+      <c r="I98" s="99" t="s">
+        <v>914</v>
+      </c>
+      <c r="J98" s="99" t="s">
+        <v>890</v>
+      </c>
+      <c r="K98" s="99" t="s">
+        <v>812</v>
+      </c>
+      <c r="L98" s="99" t="s">
+        <v>920</v>
+      </c>
+      <c r="M98" s="99" t="s">
+        <v>967</v>
+      </c>
+      <c r="N98" s="99" t="s">
+        <v>802</v>
+      </c>
+      <c r="O98" s="99" t="s">
+        <v>968</v>
+      </c>
+      <c r="P98" s="99" t="s">
+        <v>817</v>
+      </c>
+      <c r="Q98" s="99" t="s">
+        <v>1008</v>
+      </c>
+      <c r="R98" s="99" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="99" t="s">
+        <v>776</v>
+      </c>
+      <c r="B99" s="99" t="s">
+        <v>777</v>
+      </c>
+      <c r="C99" s="99" t="s">
+        <v>956</v>
+      </c>
+      <c r="D99" s="99" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E99" s="99" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F99" s="99" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G99" s="99" t="s">
+        <v>782</v>
+      </c>
+      <c r="H99" s="99" t="s">
+        <v>778</v>
+      </c>
+      <c r="I99" s="99" t="s">
+        <v>914</v>
+      </c>
+      <c r="J99" s="99" t="s">
+        <v>78</v>
+      </c>
+      <c r="K99" s="99" t="s">
+        <v>799</v>
+      </c>
+      <c r="L99" s="99" t="s">
+        <v>975</v>
+      </c>
+      <c r="M99" s="99" t="s">
+        <v>1070</v>
+      </c>
+      <c r="N99" s="99" t="s">
+        <v>977</v>
+      </c>
+      <c r="O99" s="99" t="s">
+        <v>1071</v>
+      </c>
+      <c r="P99" s="99" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q99" s="99" t="s">
+        <v>1072</v>
+      </c>
+      <c r="R99" s="99" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="99" t="s">
+        <v>776</v>
+      </c>
+      <c r="B100" s="99" t="s">
+        <v>777</v>
+      </c>
+      <c r="C100" s="99" t="s">
+        <v>971</v>
+      </c>
+      <c r="D100" s="99" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E100" s="99" t="s">
+        <v>972</v>
+      </c>
+      <c r="F100" s="99" t="s">
+        <v>1074</v>
+      </c>
+      <c r="G100" s="99" t="s">
+        <v>797</v>
+      </c>
+      <c r="H100" s="99" t="s">
+        <v>794</v>
+      </c>
+      <c r="I100" s="99" t="s">
+        <v>914</v>
+      </c>
+      <c r="J100" s="99" t="s">
+        <v>823</v>
+      </c>
+      <c r="K100" s="99" t="s">
+        <v>824</v>
+      </c>
+      <c r="L100" s="99" t="s">
+        <v>825</v>
+      </c>
+      <c r="M100" s="99" t="s">
+        <v>976</v>
+      </c>
+      <c r="N100" s="99" t="s">
+        <v>827</v>
+      </c>
+      <c r="O100" s="99" t="s">
+        <v>1075</v>
+      </c>
+      <c r="P100" s="99" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q100" s="99" t="s">
+        <v>1076</v>
+      </c>
+      <c r="R100" s="99" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="99" t="s">
+        <v>776</v>
+      </c>
+      <c r="B101" s="99" t="s">
+        <v>777</v>
+      </c>
+      <c r="C101" s="99" t="s">
+        <v>820</v>
+      </c>
+      <c r="D101" s="99" t="s">
+        <v>981</v>
+      </c>
+      <c r="E101" s="99" t="s">
+        <v>982</v>
+      </c>
+      <c r="F101" s="99" t="s">
+        <v>1077</v>
+      </c>
+      <c r="G101" s="99" t="s">
+        <v>797</v>
+      </c>
+      <c r="H101" s="99" t="s">
+        <v>794</v>
+      </c>
+      <c r="I101" s="99" t="s">
+        <v>914</v>
+      </c>
+      <c r="J101" s="99" t="s">
+        <v>835</v>
+      </c>
+      <c r="K101" s="99" t="s">
+        <v>836</v>
+      </c>
+      <c r="L101" s="99" t="s">
+        <v>837</v>
+      </c>
+      <c r="M101" s="99" t="s">
+        <v>991</v>
+      </c>
+      <c r="N101" s="99" t="s">
+        <v>992</v>
+      </c>
+      <c r="O101" s="99" t="s">
+        <v>993</v>
+      </c>
+      <c r="P101" s="99" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q101" s="99" t="s">
+        <v>994</v>
+      </c>
+      <c r="R101" s="99" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="100" t="s">
+        <v>776</v>
+      </c>
+      <c r="B102" s="100" t="s">
+        <v>777</v>
+      </c>
+      <c r="C102" s="100" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D102" s="100" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E102" s="100" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F102" s="100" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G102" s="100" t="s">
+        <v>782</v>
+      </c>
+      <c r="H102" s="100" t="s">
+        <v>778</v>
+      </c>
+      <c r="I102" s="100" t="s">
+        <v>914</v>
+      </c>
+      <c r="J102" s="100" t="s">
+        <v>18</v>
+      </c>
+      <c r="K102" s="100" t="s">
+        <v>785</v>
+      </c>
+      <c r="L102" s="100" t="s">
+        <v>913</v>
+      </c>
+      <c r="M102" s="100" t="s">
+        <v>891</v>
+      </c>
+      <c r="N102" s="100" t="s">
+        <v>815</v>
+      </c>
+      <c r="O102" s="100" t="s">
+        <v>961</v>
+      </c>
+      <c r="P102" s="100" t="s">
+        <v>790</v>
+      </c>
+      <c r="Q102" s="100" t="s">
+        <v>1026</v>
+      </c>
+      <c r="R102" s="100" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="100" t="s">
+        <v>776</v>
+      </c>
+      <c r="B103" s="100" t="s">
+        <v>777</v>
+      </c>
+      <c r="C103" s="100" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D103" s="100" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E103" s="100" t="s">
+        <v>964</v>
+      </c>
+      <c r="F103" s="100" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G103" s="100" t="s">
+        <v>782</v>
+      </c>
+      <c r="H103" s="100" t="s">
+        <v>778</v>
+      </c>
+      <c r="I103" s="100" t="s">
+        <v>914</v>
+      </c>
+      <c r="J103" s="100" t="s">
+        <v>890</v>
+      </c>
+      <c r="K103" s="100" t="s">
+        <v>812</v>
+      </c>
+      <c r="L103" s="100" t="s">
+        <v>920</v>
+      </c>
+      <c r="M103" s="100" t="s">
+        <v>967</v>
+      </c>
+      <c r="N103" s="100" t="s">
+        <v>802</v>
+      </c>
+      <c r="O103" s="100" t="s">
+        <v>968</v>
+      </c>
+      <c r="P103" s="100" t="s">
+        <v>817</v>
+      </c>
+      <c r="Q103" s="100" t="s">
+        <v>1030</v>
+      </c>
+      <c r="R103" s="100" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="100" t="s">
+        <v>776</v>
+      </c>
+      <c r="B104" s="100" t="s">
+        <v>777</v>
+      </c>
+      <c r="C104" s="100" t="s">
+        <v>797</v>
+      </c>
+      <c r="D104" s="100" t="s">
+        <v>794</v>
+      </c>
+      <c r="E104" s="100" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F104" s="100" t="s">
+        <v>1080</v>
+      </c>
+      <c r="G104" s="100" t="s">
+        <v>797</v>
+      </c>
+      <c r="H104" s="100" t="s">
+        <v>794</v>
+      </c>
+      <c r="I104" s="100" t="s">
+        <v>914</v>
+      </c>
+      <c r="J104" s="100" t="s">
+        <v>78</v>
+      </c>
+      <c r="K104" s="100" t="s">
+        <v>799</v>
+      </c>
+      <c r="L104" s="100" t="s">
+        <v>975</v>
+      </c>
+      <c r="M104" s="100" t="s">
+        <v>976</v>
+      </c>
+      <c r="N104" s="100" t="s">
+        <v>977</v>
+      </c>
+      <c r="O104" s="100" t="s">
+        <v>978</v>
+      </c>
+      <c r="P104" s="100" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q104" s="100" t="s">
+        <v>1034</v>
+      </c>
+      <c r="R104" s="100" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="100" t="s">
+        <v>776</v>
+      </c>
+      <c r="B105" s="100" t="s">
+        <v>777</v>
+      </c>
+      <c r="C105" s="100" t="s">
+        <v>797</v>
+      </c>
+      <c r="D105" s="100" t="s">
+        <v>820</v>
+      </c>
+      <c r="E105" s="100" t="s">
+        <v>981</v>
+      </c>
+      <c r="F105" s="100" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G105" s="100" t="s">
+        <v>797</v>
+      </c>
+      <c r="H105" s="100" t="s">
+        <v>794</v>
+      </c>
+      <c r="I105" s="100" t="s">
+        <v>914</v>
+      </c>
+      <c r="J105" s="100" t="s">
+        <v>823</v>
+      </c>
+      <c r="K105" s="100" t="s">
+        <v>824</v>
+      </c>
+      <c r="L105" s="100" t="s">
+        <v>825</v>
+      </c>
+      <c r="M105" s="100" t="s">
+        <v>984</v>
+      </c>
+      <c r="N105" s="100" t="s">
+        <v>827</v>
+      </c>
+      <c r="O105" s="100" t="s">
+        <v>985</v>
+      </c>
+      <c r="P105" s="100" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q105" s="100" t="s">
+        <v>1082</v>
+      </c>
+      <c r="R105" s="100" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="100" t="s">
+        <v>776</v>
+      </c>
+      <c r="B106" s="100" t="s">
+        <v>777</v>
+      </c>
+      <c r="C106" s="100" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D106" s="100" t="s">
+        <v>988</v>
+      </c>
+      <c r="E106" s="100" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F106" s="100" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G106" s="100" t="s">
+        <v>782</v>
+      </c>
+      <c r="H106" s="100" t="s">
+        <v>778</v>
+      </c>
+      <c r="I106" s="100" t="s">
+        <v>914</v>
+      </c>
+      <c r="J106" s="100" t="s">
+        <v>835</v>
+      </c>
+      <c r="K106" s="100" t="s">
+        <v>836</v>
+      </c>
+      <c r="L106" s="100" t="s">
+        <v>837</v>
+      </c>
+      <c r="M106" s="100" t="s">
+        <v>1020</v>
+      </c>
+      <c r="N106" s="100" t="s">
+        <v>1084</v>
+      </c>
+      <c r="O106" s="100" t="s">
+        <v>1085</v>
+      </c>
+      <c r="P106" s="100" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q106" s="100" t="s">
+        <v>1086</v>
+      </c>
+      <c r="R106" s="100" t="s">
+        <v>1024</v>
       </c>
     </row>
   </sheetData>
@@ -3845,38 +10489,38 @@
   <dimension ref="A1:L249"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="50" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="15.44140625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="13.109375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="16.5546875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="30.6640625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="40.88671875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="10.109375"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="18.77734375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="19.77734375"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="21.21875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="11.21875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="13.77734375"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="50.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="78" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="69" t="s">
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="79" t="s">
         <v>115</v>
       </c>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="70" t="s">
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="80" t="s">
         <v>116</v>
       </c>
-      <c r="K1" s="70"/>
+      <c r="K1" s="80"/>
       <c r="L1" s="13"/>
     </row>
     <row r="2" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -8984,18 +15628,18 @@
   <dimension ref="A1:L33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" customWidth="1"/>
-    <col min="3" max="3" width="15.77734375" customWidth="1"/>
-    <col min="4" max="4" width="27.109375" customWidth="1"/>
-    <col min="5" max="5" width="34.77734375" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="50" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="12.77734375"/>
+    <col min="2" max="2" customWidth="true" width="16.77734375"/>
+    <col min="3" max="3" customWidth="true" width="15.77734375"/>
+    <col min="4" max="4" customWidth="true" width="27.109375"/>
+    <col min="5" max="5" customWidth="true" width="34.77734375"/>
+    <col min="6" max="6" customWidth="true" width="13.5546875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="13.44140625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="13.6640625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="14.88671875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="7.88671875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="10.33203125"/>
+    <col min="12" max="12" customWidth="true" width="50.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="23" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
